--- a/data/reports/TEC22_Data/B1_final_predictions_comparison.xlsx
+++ b/data/reports/TEC22_Data/B1_final_predictions_comparison.xlsx
@@ -500,40 +500,40 @@
         <v>183.16</v>
       </c>
       <c r="B2" t="n">
-        <v>226.6277770996094</v>
+        <v>226.5949096679688</v>
       </c>
       <c r="C2" t="n">
-        <v>215.8866577148438</v>
+        <v>215.8891906738281</v>
       </c>
       <c r="D2" t="n">
-        <v>217.0471075816355</v>
+        <v>216.7095959015021</v>
       </c>
       <c r="E2" t="n">
-        <v>222.7721588611603</v>
+        <v>222.4828806509309</v>
       </c>
       <c r="F2" t="n">
-        <v>216.7295705547276</v>
+        <v>216.0107138907708</v>
       </c>
       <c r="G2" t="n">
-        <v>211.8826446533203</v>
+        <v>211.7947540283203</v>
       </c>
       <c r="H2" t="n">
-        <v>218.0741203176637</v>
+        <v>215.5347583536769</v>
       </c>
       <c r="I2" t="n">
-        <v>212.9480212424008</v>
+        <v>211.0772752728483</v>
       </c>
       <c r="J2" t="n">
-        <v>224.8250732421875</v>
+        <v>224.8588409423828</v>
       </c>
       <c r="K2" t="n">
-        <v>221.8053741455078</v>
+        <v>221.7633819580078</v>
       </c>
       <c r="L2" t="n">
-        <v>213.8886375633339</v>
+        <v>214.4311302692196</v>
       </c>
       <c r="M2" t="n">
-        <v>213.8886375633339</v>
+        <v>214.4311302692196</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>181.785</v>
       </c>
       <c r="B3" t="n">
-        <v>226.1313781738281</v>
+        <v>226.1383209228516</v>
       </c>
       <c r="C3" t="n">
-        <v>214.9836730957031</v>
+        <v>215.0085906982422</v>
       </c>
       <c r="D3" t="n">
-        <v>211.8529444022384</v>
+        <v>211.9706588038424</v>
       </c>
       <c r="E3" t="n">
-        <v>218.7941558361053</v>
+        <v>218.8887829212457</v>
       </c>
       <c r="F3" t="n">
-        <v>215.5114037327835</v>
+        <v>214.8164310629064</v>
       </c>
       <c r="G3" t="n">
-        <v>210.5201721191406</v>
+        <v>210.5829772949219</v>
       </c>
       <c r="H3" t="n">
-        <v>208.1972808051808</v>
+        <v>204.9489280166767</v>
       </c>
       <c r="I3" t="n">
-        <v>210.4782835381562</v>
+        <v>210.9014441594727</v>
       </c>
       <c r="J3" t="n">
-        <v>224.2858123779297</v>
+        <v>224.3322906494141</v>
       </c>
       <c r="K3" t="n">
-        <v>220.8377227783203</v>
+        <v>220.8724060058594</v>
       </c>
       <c r="L3" t="n">
-        <v>207.5528147382489</v>
+        <v>207.8826048875527</v>
       </c>
       <c r="M3" t="n">
-        <v>207.5528147382489</v>
+        <v>207.8826048875527</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>205.53</v>
       </c>
       <c r="B4" t="n">
-        <v>226.4717254638672</v>
+        <v>226.412353515625</v>
       </c>
       <c r="C4" t="n">
-        <v>216.8002319335938</v>
+        <v>216.7865295410156</v>
       </c>
       <c r="D4" t="n">
-        <v>215.4967019167927</v>
+        <v>215.3159497903451</v>
       </c>
       <c r="E4" t="n">
-        <v>222.3000962734222</v>
+        <v>222.1871907857209</v>
       </c>
       <c r="F4" t="n">
-        <v>215.7258637170619</v>
+        <v>211.9256221514066</v>
       </c>
       <c r="G4" t="n">
-        <v>213.2366333007812</v>
+        <v>213.2418518066406</v>
       </c>
       <c r="H4" t="n">
-        <v>207.48371973883</v>
+        <v>206.0197546562667</v>
       </c>
       <c r="I4" t="n">
-        <v>211.9313648158729</v>
+        <v>212.1833698586686</v>
       </c>
       <c r="J4" t="n">
-        <v>224.9883575439453</v>
+        <v>224.9826965332031</v>
       </c>
       <c r="K4" t="n">
-        <v>221.8111572265625</v>
+        <v>221.7197875976562</v>
       </c>
       <c r="L4" t="n">
-        <v>208.4768129685215</v>
+        <v>208.3818960604453</v>
       </c>
       <c r="M4" t="n">
-        <v>208.4768129685215</v>
+        <v>208.3818960604453</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>206.915</v>
       </c>
       <c r="B5" t="n">
-        <v>226.4505920410156</v>
+        <v>226.4481964111328</v>
       </c>
       <c r="C5" t="n">
-        <v>214.4355773925781</v>
+        <v>214.4061584472656</v>
       </c>
       <c r="D5" t="n">
-        <v>215.488943406955</v>
+        <v>215.506271376172</v>
       </c>
       <c r="E5" t="n">
-        <v>220.4286892414093</v>
+        <v>220.4480501852113</v>
       </c>
       <c r="F5" t="n">
-        <v>212.9718536952392</v>
+        <v>212.6538265571306</v>
       </c>
       <c r="G5" t="n">
-        <v>209.5498352050781</v>
+        <v>209.5357360839844</v>
       </c>
       <c r="H5" t="n">
-        <v>217.23618891211</v>
+        <v>215.7739245899264</v>
       </c>
       <c r="I5" t="n">
-        <v>210.6186171572491</v>
+        <v>209.7470504349967</v>
       </c>
       <c r="J5" t="n">
-        <v>224.3419189453125</v>
+        <v>224.3325500488281</v>
       </c>
       <c r="K5" t="n">
-        <v>221.6708526611328</v>
+        <v>221.66015625</v>
       </c>
       <c r="L5" t="n">
-        <v>213.3197500233195</v>
+        <v>215.0734356900983</v>
       </c>
       <c r="M5" t="n">
-        <v>213.3197500233195</v>
+        <v>215.0734356900983</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>187.415</v>
       </c>
       <c r="B6" t="n">
-        <v>217.3763275146484</v>
+        <v>217.3718872070312</v>
       </c>
       <c r="C6" t="n">
-        <v>191.7032623291016</v>
+        <v>191.7132110595703</v>
       </c>
       <c r="D6" t="n">
-        <v>131.4544796505652</v>
+        <v>131.4282453475199</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>177.5007903403177</v>
+        <v>163.9210988345854</v>
       </c>
       <c r="G6" t="n">
-        <v>187.8624877929688</v>
+        <v>187.8534088134766</v>
       </c>
       <c r="H6" t="n">
-        <v>166.047083244609</v>
+        <v>165.7263607211303</v>
       </c>
       <c r="I6" t="n">
-        <v>183.7829665563559</v>
+        <v>185.2203622488257</v>
       </c>
       <c r="J6" t="n">
-        <v>216.7624816894531</v>
+        <v>216.7525787353516</v>
       </c>
       <c r="K6" t="n">
-        <v>215.5361175537109</v>
+        <v>215.4526977539062</v>
       </c>
       <c r="L6" t="n">
-        <v>169.7801152335082</v>
+        <v>174.6891190492565</v>
       </c>
       <c r="M6" t="n">
-        <v>169.7801152335082</v>
+        <v>174.6891190492565</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>200.75</v>
       </c>
       <c r="B7" t="n">
-        <v>216.8384246826172</v>
+        <v>216.8282470703125</v>
       </c>
       <c r="C7" t="n">
-        <v>189.184814453125</v>
+        <v>189.2766876220703</v>
       </c>
       <c r="D7" t="n">
-        <v>126.3406569916356</v>
+        <v>126.3430535561427</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>174.4301143816083</v>
+        <v>155.5572057625802</v>
       </c>
       <c r="G7" t="n">
-        <v>185.5790710449219</v>
+        <v>185.5437622070312</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2722900928554</v>
+        <v>173.6583107696972</v>
       </c>
       <c r="I7" t="n">
-        <v>172.8224006958212</v>
+        <v>178.9773989139073</v>
       </c>
       <c r="J7" t="n">
-        <v>215.7820129394531</v>
+        <v>215.7575225830078</v>
       </c>
       <c r="K7" t="n">
-        <v>213.0592346191406</v>
+        <v>213.0639190673828</v>
       </c>
       <c r="L7" t="n">
-        <v>175.5058858421144</v>
+        <v>172.4176745094939</v>
       </c>
       <c r="M7" t="n">
-        <v>175.5058858421144</v>
+        <v>172.4176745094939</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>160.14</v>
       </c>
       <c r="B8" t="n">
-        <v>217.2870178222656</v>
+        <v>217.2836761474609</v>
       </c>
       <c r="C8" t="n">
-        <v>190.8206634521484</v>
+        <v>190.8505859375</v>
       </c>
       <c r="D8" t="n">
-        <v>130.5750068384756</v>
+        <v>130.4890469165907</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>174.6511847783061</v>
+        <v>157.6073285636812</v>
       </c>
       <c r="G8" t="n">
-        <v>187.0404663085938</v>
+        <v>186.9872283935547</v>
       </c>
       <c r="H8" t="n">
-        <v>167.9724861509659</v>
+        <v>169.7337794695461</v>
       </c>
       <c r="I8" t="n">
-        <v>171.4270905322404</v>
+        <v>178.1506643826972</v>
       </c>
       <c r="J8" t="n">
-        <v>216.0843505859375</v>
+        <v>216.0895233154297</v>
       </c>
       <c r="K8" t="n">
-        <v>213.1510772705078</v>
+        <v>213.0892944335938</v>
       </c>
       <c r="L8" t="n">
-        <v>174.3324194250936</v>
+        <v>176.7749498970008</v>
       </c>
       <c r="M8" t="n">
-        <v>174.3324194250936</v>
+        <v>176.7749498970008</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>220.125</v>
       </c>
       <c r="B9" t="n">
-        <v>207.1651458740234</v>
+        <v>207.1591949462891</v>
       </c>
       <c r="C9" t="n">
-        <v>205.0646209716797</v>
+        <v>205.0672149658203</v>
       </c>
       <c r="D9" t="n">
-        <v>209.837986509455</v>
+        <v>209.8280905829791</v>
       </c>
       <c r="E9" t="n">
-        <v>214.41319668293</v>
+        <v>214.3923401630862</v>
       </c>
       <c r="F9" t="n">
-        <v>214.0332742965687</v>
+        <v>216.0704739811264</v>
       </c>
       <c r="G9" t="n">
-        <v>196.1682586669922</v>
+        <v>196.1664428710938</v>
       </c>
       <c r="H9" t="n">
-        <v>214.3638364400165</v>
+        <v>216.0873802601506</v>
       </c>
       <c r="I9" t="n">
-        <v>204.5228729255572</v>
+        <v>207.5126063597621</v>
       </c>
       <c r="J9" t="n">
-        <v>210.5403442382812</v>
+        <v>210.5293579101562</v>
       </c>
       <c r="K9" t="n">
-        <v>208.0935211181641</v>
+        <v>208.10205078125</v>
       </c>
       <c r="L9" t="n">
-        <v>212.3369572648228</v>
+        <v>215.5685620341852</v>
       </c>
       <c r="M9" t="n">
-        <v>212.3369572648228</v>
+        <v>215.5685620341852</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>218.485</v>
       </c>
       <c r="B10" t="n">
-        <v>207.0814971923828</v>
+        <v>207.0701446533203</v>
       </c>
       <c r="C10" t="n">
-        <v>205.5039672851562</v>
+        <v>205.5125122070312</v>
       </c>
       <c r="D10" t="n">
-        <v>208.2706936936911</v>
+        <v>208.2820302516404</v>
       </c>
       <c r="E10" t="n">
-        <v>210.8011075258255</v>
+        <v>210.8268293184342</v>
       </c>
       <c r="F10" t="n">
-        <v>216.0322865730726</v>
+        <v>219.2483134294867</v>
       </c>
       <c r="G10" t="n">
-        <v>197.1146240234375</v>
+        <v>197.1307220458984</v>
       </c>
       <c r="H10" t="n">
-        <v>211.3573319862393</v>
+        <v>211.7638704366117</v>
       </c>
       <c r="I10" t="n">
-        <v>218.5674859942444</v>
+        <v>218.7646888360883</v>
       </c>
       <c r="J10" t="n">
-        <v>203.5956878662109</v>
+        <v>203.6039123535156</v>
       </c>
       <c r="K10" t="n">
-        <v>207.3187561035156</v>
+        <v>207.3174285888672</v>
       </c>
       <c r="L10" t="n">
-        <v>213.8619685058262</v>
+        <v>214.0873206421298</v>
       </c>
       <c r="M10" t="n">
-        <v>213.8619685058262</v>
+        <v>214.0873206421298</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>212.265</v>
       </c>
       <c r="B11" t="n">
-        <v>207.1707153320312</v>
+        <v>207.184814453125</v>
       </c>
       <c r="C11" t="n">
-        <v>204.9927368164062</v>
+        <v>204.9930877685547</v>
       </c>
       <c r="D11" t="n">
-        <v>210.6103143271806</v>
+        <v>210.6175646080068</v>
       </c>
       <c r="E11" t="n">
-        <v>216.1647864580154</v>
+        <v>216.1815335549467</v>
       </c>
       <c r="F11" t="n">
-        <v>214.018622322372</v>
+        <v>216.0704739811264</v>
       </c>
       <c r="G11" t="n">
-        <v>195.810546875</v>
+        <v>195.8008880615234</v>
       </c>
       <c r="H11" t="n">
-        <v>214.1218316643308</v>
+        <v>216.4557714899834</v>
       </c>
       <c r="I11" t="n">
-        <v>221.9314828397593</v>
+        <v>219.4358685120644</v>
       </c>
       <c r="J11" t="n">
-        <v>203.6059417724609</v>
+        <v>203.5867767333984</v>
       </c>
       <c r="K11" t="n">
-        <v>207.3539276123047</v>
+        <v>207.3738861083984</v>
       </c>
       <c r="L11" t="n">
-        <v>219.9947703631365</v>
+        <v>217.0112358495523</v>
       </c>
       <c r="M11" t="n">
-        <v>219.9947703631365</v>
+        <v>217.0112358495523</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>206.275</v>
       </c>
       <c r="B12" t="n">
-        <v>207.1545562744141</v>
+        <v>207.1817016601562</v>
       </c>
       <c r="C12" t="n">
-        <v>206.1166687011719</v>
+        <v>206.0913543701172</v>
       </c>
       <c r="D12" t="n">
-        <v>209.401165492856</v>
+        <v>209.3641331856833</v>
       </c>
       <c r="E12" t="n">
-        <v>213.2071982622147</v>
+        <v>213.1267718332593</v>
       </c>
       <c r="F12" t="n">
-        <v>215.4649748669061</v>
+        <v>219.2483134294867</v>
       </c>
       <c r="G12" t="n">
-        <v>197.6540985107422</v>
+        <v>197.7141876220703</v>
       </c>
       <c r="H12" t="n">
-        <v>211.9143945631249</v>
+        <v>213.1004773092091</v>
       </c>
       <c r="I12" t="n">
-        <v>217.924946740386</v>
+        <v>218.0048580811483</v>
       </c>
       <c r="J12" t="n">
-        <v>203.7111968994141</v>
+        <v>203.7201080322266</v>
       </c>
       <c r="K12" t="n">
-        <v>207.1842193603516</v>
+        <v>207.1515045166016</v>
       </c>
       <c r="L12" t="n">
-        <v>214.8271953292813</v>
+        <v>215.5552433331848</v>
       </c>
       <c r="M12" t="n">
-        <v>214.8271953292813</v>
+        <v>215.5552433331848</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>221.005</v>
       </c>
       <c r="B13" t="n">
-        <v>207.5698852539062</v>
+        <v>207.6025085449219</v>
       </c>
       <c r="C13" t="n">
-        <v>210.5965728759766</v>
+        <v>210.6224212646484</v>
       </c>
       <c r="D13" t="n">
-        <v>212.0404675099973</v>
+        <v>212.0805897697227</v>
       </c>
       <c r="E13" t="n">
-        <v>218.0674878358841</v>
+        <v>218.156564103403</v>
       </c>
       <c r="F13" t="n">
-        <v>222.8505470344487</v>
+        <v>225.825458504288</v>
       </c>
       <c r="G13" t="n">
-        <v>202.9288330078125</v>
+        <v>202.9588317871094</v>
       </c>
       <c r="H13" t="n">
-        <v>213.2872253536471</v>
+        <v>215.0826503209175</v>
       </c>
       <c r="I13" t="n">
-        <v>223.7984592484248</v>
+        <v>221.2885075953851</v>
       </c>
       <c r="J13" t="n">
-        <v>204.70556640625</v>
+        <v>204.7030639648438</v>
       </c>
       <c r="K13" t="n">
-        <v>209.2370300292969</v>
+        <v>209.1451110839844</v>
       </c>
       <c r="L13" t="n">
-        <v>215.805433758912</v>
+        <v>215.0987649852867</v>
       </c>
       <c r="M13" t="n">
-        <v>215.805433758912</v>
+        <v>215.0987649852867</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>227.085</v>
       </c>
       <c r="B14" t="n">
-        <v>207.5509796142578</v>
+        <v>207.6167755126953</v>
       </c>
       <c r="C14" t="n">
-        <v>210.5303497314453</v>
+        <v>210.5241241455078</v>
       </c>
       <c r="D14" t="n">
-        <v>212.081485426877</v>
+        <v>212.0680013855632</v>
       </c>
       <c r="E14" t="n">
-        <v>218.1772586107254</v>
+        <v>218.1484544473929</v>
       </c>
       <c r="F14" t="n">
-        <v>222.8505470344487</v>
+        <v>225.825458504288</v>
       </c>
       <c r="G14" t="n">
-        <v>202.8838348388672</v>
+        <v>202.9007263183594</v>
       </c>
       <c r="H14" t="n">
-        <v>213.2872253536471</v>
+        <v>215.0826503209175</v>
       </c>
       <c r="I14" t="n">
-        <v>225.4850695419437</v>
+        <v>223.2746052248023</v>
       </c>
       <c r="J14" t="n">
-        <v>204.9064178466797</v>
+        <v>204.8865356445312</v>
       </c>
       <c r="K14" t="n">
-        <v>211.3538665771484</v>
+        <v>211.3228302001953</v>
       </c>
       <c r="L14" t="n">
-        <v>215.6549952344332</v>
+        <v>215.5733997967628</v>
       </c>
       <c r="M14" t="n">
-        <v>215.6549952344332</v>
+        <v>215.5733997967628</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>230.495</v>
       </c>
       <c r="B15" t="n">
-        <v>207.4852447509766</v>
+        <v>207.4956970214844</v>
       </c>
       <c r="C15" t="n">
-        <v>209.9247894287109</v>
+        <v>209.9248809814453</v>
       </c>
       <c r="D15" t="n">
-        <v>211.5766539862061</v>
+        <v>211.7431142406073</v>
       </c>
       <c r="E15" t="n">
-        <v>217.2023516893387</v>
+        <v>217.5691382664104</v>
       </c>
       <c r="F15" t="n">
-        <v>222.5534787175068</v>
+        <v>225.825458504288</v>
       </c>
       <c r="G15" t="n">
-        <v>202.2056732177734</v>
+        <v>202.2247924804688</v>
       </c>
       <c r="H15" t="n">
-        <v>211.968530593147</v>
+        <v>214.3851275405437</v>
       </c>
       <c r="I15" t="n">
-        <v>224.68054756603</v>
+        <v>222.697532747017</v>
       </c>
       <c r="J15" t="n">
-        <v>204.700927734375</v>
+        <v>204.7336578369141</v>
       </c>
       <c r="K15" t="n">
-        <v>211.2435607910156</v>
+        <v>211.1827392578125</v>
       </c>
       <c r="L15" t="n">
-        <v>215.0825480057359</v>
+        <v>214.402723610489</v>
       </c>
       <c r="M15" t="n">
-        <v>215.0825480057359</v>
+        <v>214.402723610489</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>226.905</v>
       </c>
       <c r="B16" t="n">
-        <v>207.2608032226562</v>
+        <v>207.2761383056641</v>
       </c>
       <c r="C16" t="n">
-        <v>209.4291229248047</v>
+        <v>209.4466857910156</v>
       </c>
       <c r="D16" t="n">
-        <v>208.9821448484675</v>
+        <v>209.0057604335542</v>
       </c>
       <c r="E16" t="n">
-        <v>211.4453936815262</v>
+        <v>211.4981615841028</v>
       </c>
       <c r="F16" t="n">
-        <v>222.7704633531842</v>
+        <v>225.825458504288</v>
       </c>
       <c r="G16" t="n">
-        <v>202.1573791503906</v>
+        <v>202.1406097412109</v>
       </c>
       <c r="H16" t="n">
-        <v>209.282407994916</v>
+        <v>211.6811346324912</v>
       </c>
       <c r="I16" t="n">
-        <v>224.68054756603</v>
+        <v>222.7184341810104</v>
       </c>
       <c r="J16" t="n">
-        <v>204.4554901123047</v>
+        <v>204.4692535400391</v>
       </c>
       <c r="K16" t="n">
-        <v>210.99365234375</v>
+        <v>211.0253295898438</v>
       </c>
       <c r="L16" t="n">
-        <v>211.0667533833816</v>
+        <v>211.756604275683</v>
       </c>
       <c r="M16" t="n">
-        <v>211.0667533833816</v>
+        <v>211.756604275683</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>230.935</v>
       </c>
       <c r="B17" t="n">
-        <v>207.2480926513672</v>
+        <v>207.2549285888672</v>
       </c>
       <c r="C17" t="n">
-        <v>209.6763763427734</v>
+        <v>209.6988372802734</v>
       </c>
       <c r="D17" t="n">
-        <v>209.1615675220223</v>
+        <v>209.1660913741256</v>
       </c>
       <c r="E17" t="n">
-        <v>211.7934600114822</v>
+        <v>211.8042494193865</v>
       </c>
       <c r="F17" t="n">
-        <v>222.8505470344487</v>
+        <v>225.825458504288</v>
       </c>
       <c r="G17" t="n">
-        <v>202.4037170410156</v>
+        <v>202.3973693847656</v>
       </c>
       <c r="H17" t="n">
-        <v>209.3574198948891</v>
+        <v>211.6811346324912</v>
       </c>
       <c r="I17" t="n">
-        <v>225.4850695419437</v>
+        <v>223.3790956127014</v>
       </c>
       <c r="J17" t="n">
-        <v>204.5431060791016</v>
+        <v>204.5315704345703</v>
       </c>
       <c r="K17" t="n">
-        <v>211.1157684326172</v>
+        <v>211.1112976074219</v>
       </c>
       <c r="L17" t="n">
-        <v>210.8158697023017</v>
+        <v>211.6346898813368</v>
       </c>
       <c r="M17" t="n">
-        <v>210.8158697023017</v>
+        <v>211.6346898813368</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>229.575</v>
       </c>
       <c r="B18" t="n">
-        <v>207.4361114501953</v>
+        <v>207.4734954833984</v>
       </c>
       <c r="C18" t="n">
-        <v>211.5262603759766</v>
+        <v>211.5260925292969</v>
       </c>
       <c r="D18" t="n">
-        <v>210.5445622254296</v>
+        <v>210.5697194208312</v>
       </c>
       <c r="E18" t="n">
-        <v>214.4132043123245</v>
+        <v>214.4694108969824</v>
       </c>
       <c r="F18" t="n">
-        <v>225.3070209027899</v>
+        <v>227.626128905642</v>
       </c>
       <c r="G18" t="n">
-        <v>204.3785400390625</v>
+        <v>204.3887786865234</v>
       </c>
       <c r="H18" t="n">
-        <v>214.9957960415629</v>
+        <v>213.8848739885071</v>
       </c>
       <c r="I18" t="n">
-        <v>225.5884678276088</v>
+        <v>223.4619407460876</v>
       </c>
       <c r="J18" t="n">
-        <v>204.9821014404297</v>
+        <v>204.9869842529297</v>
       </c>
       <c r="K18" t="n">
-        <v>211.9142608642578</v>
+        <v>211.8353118896484</v>
       </c>
       <c r="L18" t="n">
-        <v>213.2590173890921</v>
+        <v>213.3004549282436</v>
       </c>
       <c r="M18" t="n">
-        <v>213.2590173890921</v>
+        <v>213.3004549282436</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>230.58</v>
       </c>
       <c r="B19" t="n">
-        <v>207.4128723144531</v>
+        <v>207.4453125</v>
       </c>
       <c r="C19" t="n">
-        <v>211.0072021484375</v>
+        <v>210.9470062255859</v>
       </c>
       <c r="D19" t="n">
-        <v>210.1469035642935</v>
+        <v>210.167058941075</v>
       </c>
       <c r="E19" t="n">
-        <v>213.6660424470901</v>
+        <v>213.7112275238669</v>
       </c>
       <c r="F19" t="n">
-        <v>225.2309958992031</v>
+        <v>227.0990270217395</v>
       </c>
       <c r="G19" t="n">
-        <v>203.8266296386719</v>
+        <v>203.8940277099609</v>
       </c>
       <c r="H19" t="n">
-        <v>214.0914319359045</v>
+        <v>213.7369893645641</v>
       </c>
       <c r="I19" t="n">
-        <v>227.442911602221</v>
+        <v>224.9279648303702</v>
       </c>
       <c r="J19" t="n">
-        <v>204.9251556396484</v>
+        <v>204.9591064453125</v>
       </c>
       <c r="K19" t="n">
-        <v>212.3567962646484</v>
+        <v>212.4122619628906</v>
       </c>
       <c r="L19" t="n">
-        <v>212.8620031886249</v>
+        <v>213.7802523574792</v>
       </c>
       <c r="M19" t="n">
-        <v>212.8620031886249</v>
+        <v>213.7802523574792</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>233.625</v>
       </c>
       <c r="B20" t="n">
-        <v>207.4278869628906</v>
+        <v>207.4404144287109</v>
       </c>
       <c r="C20" t="n">
-        <v>211.5123748779297</v>
+        <v>211.4735107421875</v>
       </c>
       <c r="D20" t="n">
-        <v>210.550743891372</v>
+        <v>210.5469403550054</v>
       </c>
       <c r="E20" t="n">
-        <v>214.4320756196976</v>
+        <v>214.4245521176435</v>
       </c>
       <c r="F20" t="n">
-        <v>225.4190287279687</v>
+        <v>227.626128905642</v>
       </c>
       <c r="G20" t="n">
-        <v>204.3404388427734</v>
+        <v>204.3641357421875</v>
       </c>
       <c r="H20" t="n">
-        <v>214.9957960415629</v>
+        <v>213.8848739885071</v>
       </c>
       <c r="I20" t="n">
-        <v>227.5463098878862</v>
+        <v>224.9279648303702</v>
       </c>
       <c r="J20" t="n">
-        <v>204.9935607910156</v>
+        <v>204.9705657958984</v>
       </c>
       <c r="K20" t="n">
-        <v>212.3709259033203</v>
+        <v>212.2982788085938</v>
       </c>
       <c r="L20" t="n">
-        <v>212.8620031886249</v>
+        <v>213.9564213066378</v>
       </c>
       <c r="M20" t="n">
-        <v>212.8620031886249</v>
+        <v>213.9564213066378</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>215.955</v>
       </c>
       <c r="B21" t="n">
-        <v>206.7574462890625</v>
+        <v>206.7343902587891</v>
       </c>
       <c r="C21" t="n">
-        <v>205.3047790527344</v>
+        <v>205.2737426757812</v>
       </c>
       <c r="D21" t="n">
-        <v>205.8223740566085</v>
+        <v>205.845430892105</v>
       </c>
       <c r="E21" t="n">
-        <v>205.3366652727127</v>
+        <v>205.3881204411704</v>
       </c>
       <c r="F21" t="n">
-        <v>214.7660715724464</v>
+        <v>218.7395485250316</v>
       </c>
       <c r="G21" t="n">
-        <v>197.4219512939453</v>
+        <v>197.4418640136719</v>
       </c>
       <c r="H21" t="n">
-        <v>203.6623233191853</v>
+        <v>203.9012394958478</v>
       </c>
       <c r="I21" t="n">
-        <v>225.202316857456</v>
+        <v>223.1092815364338</v>
       </c>
       <c r="J21" t="n">
-        <v>203.6408081054688</v>
+        <v>203.6475830078125</v>
       </c>
       <c r="K21" t="n">
-        <v>210.7164764404297</v>
+        <v>210.6279449462891</v>
       </c>
       <c r="L21" t="n">
-        <v>208.6708431065678</v>
+        <v>207.2729529050471</v>
       </c>
       <c r="M21" t="n">
-        <v>208.6708431065678</v>
+        <v>207.2729529050471</v>
       </c>
     </row>
     <row r="22">
@@ -1320,40 +1320,40 @@
         <v>215.4</v>
       </c>
       <c r="B22" t="n">
-        <v>206.2050018310547</v>
+        <v>206.2137451171875</v>
       </c>
       <c r="C22" t="n">
-        <v>200.3806762695312</v>
+        <v>200.3766021728516</v>
       </c>
       <c r="D22" t="n">
-        <v>201.9935934339298</v>
+        <v>202.0002849651659</v>
       </c>
       <c r="E22" t="n">
-        <v>197.7362090349197</v>
+        <v>197.7517125640858</v>
       </c>
       <c r="F22" t="n">
-        <v>207.8415743554432</v>
+        <v>206.0161993770081</v>
       </c>
       <c r="G22" t="n">
-        <v>192.0046844482422</v>
+        <v>192.0508270263672</v>
       </c>
       <c r="H22" t="n">
-        <v>200.568928932578</v>
+        <v>203.3661740650245</v>
       </c>
       <c r="I22" t="n">
-        <v>221.1397898766556</v>
+        <v>218.8471353248125</v>
       </c>
       <c r="J22" t="n">
-        <v>202.4520874023438</v>
+        <v>202.4393615722656</v>
       </c>
       <c r="K22" t="n">
-        <v>206.4655151367188</v>
+        <v>206.4193572998047</v>
       </c>
       <c r="L22" t="n">
-        <v>207.2412527219</v>
+        <v>206.8662746278517</v>
       </c>
       <c r="M22" t="n">
-        <v>207.2412527219</v>
+        <v>206.8662746278517</v>
       </c>
     </row>
     <row r="23">
@@ -1361,40 +1361,40 @@
         <v>207.785</v>
       </c>
       <c r="B23" t="n">
-        <v>206.3374633789062</v>
+        <v>206.320556640625</v>
       </c>
       <c r="C23" t="n">
-        <v>201.2035675048828</v>
+        <v>201.2554168701172</v>
       </c>
       <c r="D23" t="n">
-        <v>202.6950127593819</v>
+        <v>202.7177935860448</v>
       </c>
       <c r="E23" t="n">
-        <v>199.1388989686966</v>
+        <v>199.1896638935436</v>
       </c>
       <c r="F23" t="n">
-        <v>208.9570321795825</v>
+        <v>210.5329458100778</v>
       </c>
       <c r="G23" t="n">
-        <v>192.9094085693359</v>
+        <v>192.9059143066406</v>
       </c>
       <c r="H23" t="n">
-        <v>199.1484554470644</v>
+        <v>200.6613009684409</v>
       </c>
       <c r="I23" t="n">
-        <v>212.1473783426422</v>
+        <v>211.9912743852775</v>
       </c>
       <c r="J23" t="n">
-        <v>202.4506530761719</v>
+        <v>202.4180450439453</v>
       </c>
       <c r="K23" t="n">
-        <v>204.6400451660156</v>
+        <v>204.6021270751953</v>
       </c>
       <c r="L23" t="n">
-        <v>207.8561916863705</v>
+        <v>208.8542706951001</v>
       </c>
       <c r="M23" t="n">
-        <v>207.8561916863705</v>
+        <v>208.8542706951001</v>
       </c>
     </row>
     <row r="24">
@@ -1402,40 +1402,40 @@
         <v>166.37</v>
       </c>
       <c r="B24" t="n">
-        <v>205.9234619140625</v>
+        <v>205.9232940673828</v>
       </c>
       <c r="C24" t="n">
-        <v>198.29541015625</v>
+        <v>198.26513671875</v>
       </c>
       <c r="D24" t="n">
-        <v>200.3673305013912</v>
+        <v>200.3699155597359</v>
       </c>
       <c r="E24" t="n">
-        <v>194.4437733888626</v>
+        <v>194.4502751580677</v>
       </c>
       <c r="F24" t="n">
-        <v>207.8405617319084</v>
+        <v>206.0161993770081</v>
       </c>
       <c r="G24" t="n">
-        <v>190.2006378173828</v>
+        <v>190.2276000976562</v>
       </c>
       <c r="H24" t="n">
-        <v>202.7138895325729</v>
+        <v>204.2342983060051</v>
       </c>
       <c r="I24" t="n">
-        <v>207.7534584984898</v>
+        <v>208.3093831100871</v>
       </c>
       <c r="J24" t="n">
-        <v>201.7350006103516</v>
+        <v>201.7787933349609</v>
       </c>
       <c r="K24" t="n">
-        <v>203.85546875</v>
+        <v>203.8539276123047</v>
       </c>
       <c r="L24" t="n">
-        <v>202.6849752980947</v>
+        <v>202.7496160255643</v>
       </c>
       <c r="M24" t="n">
-        <v>202.6849752980947</v>
+        <v>202.7496160255643</v>
       </c>
     </row>
     <row r="25">
@@ -1443,40 +1443,40 @@
         <v>162.765</v>
       </c>
       <c r="B25" t="n">
-        <v>222.2178649902344</v>
+        <v>222.2372436523438</v>
       </c>
       <c r="C25" t="n">
-        <v>199.2236785888672</v>
+        <v>199.2203216552734</v>
       </c>
       <c r="D25" t="n">
-        <v>204.5828236607806</v>
+        <v>204.622353511302</v>
       </c>
       <c r="E25" t="n">
-        <v>201.2452366352081</v>
+        <v>201.303492848521</v>
       </c>
       <c r="F25" t="n">
-        <v>199.3271289185641</v>
+        <v>198.8043723093718</v>
       </c>
       <c r="G25" t="n">
-        <v>195.5059814453125</v>
+        <v>195.5425720214844</v>
       </c>
       <c r="H25" t="n">
-        <v>184.3080469429579</v>
+        <v>182.9018921245118</v>
       </c>
       <c r="I25" t="n">
-        <v>190.8612297148114</v>
+        <v>195.1589392656659</v>
       </c>
       <c r="J25" t="n">
-        <v>217.2637786865234</v>
+        <v>217.2319183349609</v>
       </c>
       <c r="K25" t="n">
-        <v>204.7106323242188</v>
+        <v>204.6732635498047</v>
       </c>
       <c r="L25" t="n">
-        <v>189.7155272183153</v>
+        <v>188.0238666961859</v>
       </c>
       <c r="M25" t="n">
-        <v>189.7155272183153</v>
+        <v>188.0238666961859</v>
       </c>
     </row>
     <row r="26">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1400143951177597</v>
+        <v>-0.1483899503946304</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.02640974521637</v>
+        <v>0.8656934499740601</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2022656500339508</v>
+        <v>-0.2069744765758514</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.4483871757984161</v>
+        <v>-0.365450531244278</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.06814568489789963</v>
+        <v>-0.09181804209947586</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4406933188438416</v>
+        <v>-0.3929970860481262</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.05612766370177269</v>
+        <v>-0.07733743637800217</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.006632176693528891</v>
+        <v>0.04788226261734962</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06423371285200119</v>
+        <v>-0.07854646444320679</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3396733999252319</v>
+        <v>0.3806073367595673</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.05581596493721008</v>
+        <v>-0.07542480528354645</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.229991614818573</v>
+        <v>0.281003475189209</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.03700536862015724</v>
+        <v>-0.05318901687860489</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3333414793014526</v>
+        <v>0.3595376908779144</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.01801596023142338</v>
+        <v>-0.04336874186992645</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.648188054561615</v>
+        <v>0.6640060544013977</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.005003157537430525</v>
+        <v>-0.01779261790215969</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8008073568344116</v>
+        <v>0.8269065618515015</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.01160222943872213</v>
+        <v>-0.02500832825899124</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1.001617193222046</v>
+        <v>1.013016939163208</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.05599081516265869</v>
+        <v>-0.07382458448410034</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6503216624259949</v>
+        <v>0.6690734624862671</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.05011981725692749</v>
+        <v>-0.07319465279579163</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3549492061138153</v>
+        <v>0.3788942694664001</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.02561167813837528</v>
+        <v>-0.03136890381574631</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.4612365663051605</v>
+        <v>0.5125095248222351</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3024936318397522</v>
+        <v>0.2891089916229248</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.335730642080307</v>
+        <v>0.3164369165897369</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2778861820697784</v>
+        <v>0.2600887715816498</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9487444758415222</v>
+        <v>0.95009845495224</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2563693821430206</v>
+        <v>0.2480910420417786</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6549946069717407</v>
+        <v>0.6716659069061279</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2807567417621613</v>
+        <v>0.2591851651668549</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6547278761863708</v>
+        <v>0.6733034253120422</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2954390347003937</v>
+        <v>0.2860964238643646</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9321407079696655</v>
+        <v>0.9090590476989746</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.282467246055603</v>
+        <v>0.2725907862186432</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9432210326194763</v>
+        <v>0.9372789263725281</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3087709844112396</v>
+        <v>0.288912445306778</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1.152288913726807</v>
+        <v>1.122209191322327</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.312200129032135</v>
+        <v>0.2972120046615601</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.336257696151733</v>
+        <v>1.326205015182495</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.290319412946701</v>
+        <v>0.272169291973114</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.106041312217712</v>
+        <v>1.094236373901367</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2881489396095276</v>
+        <v>0.277656763792038</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.9094517230987549</v>
+        <v>0.9116939306259155</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2840329706668854</v>
+        <v>0.2668428719043732</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1.11513078212738</v>
+        <v>1.091460704803467</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2685428857803345</v>
+        <v>0.2508804798126221</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9452996850013733</v>
+        <v>0.9476854801177979</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2520489394664764</v>
+        <v>0.2402081042528152</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3059278130531311</v>
+        <v>0.3307247459888458</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2748022973537445</v>
+        <v>0.254689633846283</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.238561600446701</v>
+        <v>0.2615601420402527</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2371391355991364</v>
+        <v>0.2318316251039505</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1732418388128281</v>
+        <v>0.1811678409576416</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2051129192113876</v>
+        <v>0.1988565474748611</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3345929384231567</v>
+        <v>0.3623287677764893</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2496595680713654</v>
+        <v>0.2429175823926926</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2241604924201965</v>
+        <v>0.251803994178772</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2075486928224564</v>
+        <v>0.203617125749588</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3605406880378723</v>
+        <v>0.3893283903598785</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2195853590965271</v>
+        <v>0.2088470160961151</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2228908389806747</v>
+        <v>0.2525896430015564</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2177697271108627</v>
+        <v>0.2069749534130096</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.168259784579277</v>
+        <v>0.2337063103914261</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2509975135326385</v>
+        <v>0.2341792732477188</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1378307491540909</v>
+        <v>0.1778573542833328</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2399826645851135</v>
+        <v>0.2257491797208786</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2680068016052246</v>
+        <v>0.2917779386043549</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3028415739536285</v>
+        <v>0.2861910760402679</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7627637386322021</v>
+        <v>0.7602658867835999</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3783491551876068</v>
+        <v>0.3704397678375244</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2689906358718872</v>
+        <v>0.2838458120822906</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3752380013465881</v>
+        <v>0.3607529401779175</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2677097916603088</v>
+        <v>0.2489103227853775</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4385621249675751</v>
+        <v>0.4244819283485413</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2269310504198074</v>
+        <v>0.2139878869056702</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3230355978012085</v>
+        <v>0.3113755583763123</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3222671747207642</v>
+        <v>0.33409583568573</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2742873132228851</v>
+        <v>0.2698081135749817</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1905920803546906</v>
+        <v>0.1864347904920578</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2142246961593628</v>
+        <v>0.2075954377651215</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.05664486810564995</v>
+        <v>0.07914264500141144</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3028415739536285</v>
+        <v>0.2861910760402679</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.01760576292872429</v>
+        <v>0.02057255804538727</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3407109379768372</v>
+        <v>0.3291899561882019</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1614727973937988</v>
+        <v>0.1603933423757553</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2720454931259155</v>
+        <v>0.2611103653907776</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1465322226285934</v>
+        <v>0.1351804286241531</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2209329903125763</v>
+        <v>0.2124671041965485</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3092201054096222</v>
+        <v>0.2844365835189819</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.222704216837883</v>
+        <v>0.2152374237775803</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2894569337368011</v>
+        <v>0.2713666558265686</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.222345307469368</v>
+        <v>0.2186194956302643</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2946945130825043</v>
+        <v>0.2725094854831696</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1714811027050018</v>
+        <v>0.1705791056156158</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2124436795711517</v>
+        <v>0.2233789712190628</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1954131722450256</v>
+        <v>0.1881000101566315</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.157813549041748</v>
+        <v>0.1507257670164108</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1736823469400406</v>
+        <v>0.1652655303478241</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1448469012975693</v>
+        <v>0.1442824304103851</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1993547528982162</v>
+        <v>0.1908990144729614</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1638913303613663</v>
+        <v>0.1606399863958359</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2940498888492584</v>
+        <v>0.2810134291648865</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.06660059839487076</v>
+        <v>0.03174617141485214</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2401282489299774</v>
+        <v>0.2294119298458099</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3873841166496277</v>
+        <v>0.3644819855690002</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2260095924139023</v>
+        <v>0.2164525240659714</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3049985468387604</v>
+        <v>0.2992918491363525</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1946501284837723</v>
+        <v>0.1870896071195602</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1678019016981125</v>
+        <v>0.1582165658473969</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1848157495260239</v>
+        <v>0.1772059202194214</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2443479746580124</v>
+        <v>0.2394306659698486</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1890621483325958</v>
+        <v>0.1742316037416458</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.2159406691789627</v>
+        <v>0.2152472734451294</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.165272057056427</v>
+        <v>0.1563801169395447</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.05953245982527733</v>
+        <v>0.06097806245088577</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1268591433763504</v>
+        <v>0.124823197722435</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.11860191822052</v>
+        <v>-0.1168366894125938</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1783417463302612</v>
+        <v>0.1719977259635925</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.1871881037950516</v>
+        <v>-0.1896066963672638</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1783417463302612</v>
+        <v>0.1719977259635925</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1268077492713928</v>
+        <v>0.1270725280046463</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2406657487154007</v>
+        <v>0.2324906885623932</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.07862234860658646</v>
+        <v>0.06978770345449448</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2425331473350525</v>
+        <v>0.2315376400947571</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3337783813476562</v>
+        <v>0.3158018887042999</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2308239042758942</v>
+        <v>0.2203050404787064</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.3334571123123169</v>
+        <v>0.3224307894706726</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2393202185630798</v>
+        <v>0.2305207103490829</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.3462379574775696</v>
+        <v>0.3229697942733765</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1795158088207245</v>
+        <v>0.1732212007045746</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.4849304854869843</v>
+        <v>-0.482627660036087</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1841695010662079</v>
+        <v>0.1788059175014496</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.1889946609735489</v>
+        <v>0.1496831923723221</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2139696478843689</v>
+        <v>0.207749530673027</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1676286906003952</v>
+        <v>0.1270172744989395</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2050744444131851</v>
+        <v>0.1988250762224197</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.2563515305519104</v>
+        <v>0.2112049758434296</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1624532490968704</v>
+        <v>0.1587604135274887</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.2610221207141876</v>
+        <v>0.2222673892974854</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1529895514249802</v>
+        <v>0.1500069499015808</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1635642349720001</v>
+        <v>0.129806712269783</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2029951363801956</v>
+        <v>0.1942701190710068</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.09697483479976654</v>
+        <v>0.05352035909891129</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2139696478843689</v>
+        <v>0.207749530673027</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2143481373786926</v>
+        <v>0.1728853136301041</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03414715453982353</v>
+        <v>0.03382787853479385</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.4792589247226715</v>
+        <v>0.4340100288391113</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0.009948382154107094</v>
+        <v>0.01172544062137604</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.2807808816432953</v>
+        <v>0.2349526435136795</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.06000968441367149</v>
+        <v>-0.05758987739682198</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2735868394374847</v>
+        <v>0.2396752238273621</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.04056158289313316</v>
+        <v>0.0396236889064312</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -4668,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0.03959466516971588</v>
+        <v>0.006978787947446108</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05951054394245148</v>
+        <v>0.05692742764949799</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2718761265277863</v>
+        <v>0.2192550748586655</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0.06943304836750031</v>
+        <v>0.06493625789880753</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2960238456726074</v>
+        <v>0.2502373158931732</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.008256999775767326</v>
+        <v>-0.007773830555379391</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0.3821584284305573</v>
+        <v>0.3402967154979706</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.005971476901322603</v>
+        <v>0.00537955155596137</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -4832,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1796322613954544</v>
+        <v>0.1391931176185608</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.006983800325542688</v>
+        <v>-0.009629514068365097</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>-0.5711761713027954</v>
+        <v>-0.5877258777618408</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.05738850682973862</v>
+        <v>0.0478011891245842</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-0.4159354865550995</v>
+        <v>-0.4306837916374207</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.03745129331946373</v>
+        <v>-0.04142545908689499</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2319268584251404</v>
+        <v>0.2207683473825455</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.183222621679306</v>
+        <v>-0.1813914775848389</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>-0.1983435302972794</v>
+        <v>-0.184470534324646</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.2038941532373428</v>
+        <v>-0.204514279961586</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>-0.3523749709129333</v>
+        <v>-0.3081256151199341</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1812974065542221</v>
+        <v>-0.17964006960392</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>-0.3853365182876587</v>
+        <v>-0.3358412086963654</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.1611548662185669</v>
+        <v>-0.1620019525289536</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>-0.3482421934604645</v>
+        <v>-0.3113773465156555</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.1645010262727737</v>
+        <v>-0.1614236682653427</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -5160,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>-0.3610197603702545</v>
+        <v>-0.3372064232826233</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.1413257718086243</v>
+        <v>-0.1433520466089249</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>-0.2622164785861969</v>
+        <v>-0.2408251464366913</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.1247797161340714</v>
+        <v>-0.1239709779620171</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>-0.2083244472742081</v>
+        <v>-0.1838431656360626</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.1284904927015305</v>
+        <v>-0.1342501193284988</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>-0.1483024060726166</v>
+        <v>-0.1252355426549911</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.1433691829442978</v>
+        <v>-0.1427886784076691</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>-0.3726039230823517</v>
+        <v>-0.3284837305545807</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.1512081176042557</v>
+        <v>-0.1527083814144135</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>-0.1935594081878662</v>
+        <v>-0.1702025383710861</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.1442067176103592</v>
+        <v>-0.1470611393451691</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>-0.2516070306301117</v>
+        <v>-0.2274731397628784</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5423,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.1697459518909454</v>
+        <v>-0.1713541597127914</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>-0.246939018368721</v>
+        <v>-0.2211554646492004</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.1941411346197128</v>
+        <v>-0.1961711496114731</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>-0.2841102480888367</v>
+        <v>-0.246437132358551</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.226250171661377</v>
+        <v>-0.2203885018825531</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>-0.3620560467243195</v>
+        <v>-0.3056080043315887</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.2013784646987915</v>
+        <v>-0.2016106694936752</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>-0.421012669801712</v>
+        <v>-0.37481689453125</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.2041774690151215</v>
+        <v>-0.1990975439548492</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-0.4299025237560272</v>
+        <v>-0.3908044695854187</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1981690376996994</v>
+        <v>-0.2005357444286346</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>-0.4726183712482452</v>
+        <v>-0.423912912607193</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.2231261879205704</v>
+        <v>-0.2202471047639847</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>-0.3922064900398254</v>
+        <v>-0.3557642996311188</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.240446075797081</v>
+        <v>-0.2403985112905502</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>-0.6969361901283264</v>
+        <v>-0.64247727394104</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.1633564084768295</v>
+        <v>-0.1630051285028458</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>-0.4259917140007019</v>
+        <v>-0.3803608119487762</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.3151248693466187</v>
+        <v>-0.3056452572345734</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -5816,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0.2287599742412567</v>
+        <v>0.2437499165534973</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.2220050543546677</v>
+        <v>-0.2211968451738358</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.5105605721473694</v>
+        <v>-0.4786355793476105</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.2865921258926392</v>
+        <v>-0.2835851311683655</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.2500939965248108</v>
+        <v>-0.2325358539819717</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.3177735507488251</v>
+        <v>-0.3154149353504181</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>-0.3506889343261719</v>
+        <v>-0.3091658651828766</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.2677688300609589</v>
+        <v>-0.2686958909034729</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>-0.3211154937744141</v>
+        <v>-0.3038788437843323</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2132652997970581</v>
+        <v>-0.2109213173389435</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>-0.2766131460666656</v>
+        <v>-0.2635603249073029</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.1697881370782852</v>
+        <v>-0.1716992557048798</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>-0.08153721690177917</v>
+        <v>-0.08025363832712173</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.1527547836303711</v>
+        <v>-0.1508381366729736</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0.006921728607267141</v>
+        <v>0.01078562159091234</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.1707455068826675</v>
+        <v>-0.165963888168335</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>0.007673350162804127</v>
+        <v>-0.001209787093102932</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.1752443909645081</v>
+        <v>-0.1772791892290115</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.1455169320106506</v>
+        <v>-0.1389188468456268</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.1707455068826675</v>
+        <v>-0.165963888168335</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>-0.1003617942333221</v>
+        <v>-0.09300509840250015</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.1626414954662323</v>
+        <v>-0.1664080619812012</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>-0.2176775187253952</v>
+        <v>-0.216228649020195</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1657613515853882</v>
+        <v>-0.1597691178321838</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>-0.07986308634281158</v>
+        <v>-0.08397584408521652</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.1816381961107254</v>
+        <v>-0.1813498139381409</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>-0.1775275319814682</v>
+        <v>-0.1688995510339737</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.2159420698881149</v>
+        <v>-0.2166347652673721</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>-0.1784943342208862</v>
+        <v>-0.1652661710977554</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.165179505944252</v>
+        <v>-0.1640118062496185</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>-0.06088463217020035</v>
+        <v>-0.06075436994433403</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.09244965761899948</v>
+        <v>-0.09294448792934418</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0.182890996336937</v>
+        <v>0.1738833636045456</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.1099095419049263</v>
+        <v>-0.1099346578121185</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0.2391145974397659</v>
+        <v>0.2363274246454239</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.1172222942113876</v>
+        <v>-0.1213080659508705</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0.2191208451986313</v>
+        <v>0.2135258167982101</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.04541134089231491</v>
+        <v>-0.04693824797868729</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0.2528373003005981</v>
+        <v>0.2333533465862274</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.01668733358383179</v>
+        <v>-0.02077211998403072</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0.3889395892620087</v>
+        <v>0.3583274781703949</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.05110970139503479</v>
+        <v>-0.05177016928792</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0.5007981061935425</v>
+        <v>0.4740583598613739</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.044997937977314</v>
+        <v>-0.04919049143791199</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0.3794522285461426</v>
+        <v>0.3629572987556458</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.03410542383790016</v>
+        <v>-0.03462851792573929</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0.472781777381897</v>
+        <v>0.445768803358078</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>9.978106390917674e-05</v>
+        <v>-0.004045853856950998</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>0.4810969531536102</v>
+        <v>0.4567002058029175</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.009404831565916538</v>
+        <v>-0.01829904317855835</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0.457381933927536</v>
+        <v>0.4366120398044586</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.0464535616338253</v>
+        <v>-0.05099756643176079</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0.4080952107906342</v>
+        <v>0.3806439340114594</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.07361651211977005</v>
+        <v>-0.07672907412052155</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0.4134750068187714</v>
+        <v>0.3911817967891693</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.0337514691054821</v>
+        <v>-0.03739190474152565</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0.2353970408439636</v>
+        <v>0.2112310826778412</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.104733981192112</v>
+        <v>-0.1123511418700218</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>0.2891981601715088</v>
+        <v>0.2712163031101227</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.1270377337932587</v>
+        <v>-0.1281847506761551</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>0.08628194034099579</v>
+        <v>0.08290448039770126</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.02340565249323845</v>
+        <v>-0.01796583645045757</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>1.014230489730835</v>
+        <v>1.000821113586426</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.008073407225310802</v>
+        <v>-0.001618294976651669</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0.04127299040555954</v>
+        <v>0.04163708537817001</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.03458066657185555</v>
+        <v>-0.03296563401818275</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0.07775905728340149</v>
+        <v>0.07131892442703247</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.07180728018283844</v>
+        <v>-0.07191382348537445</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>-0.01559755206108093</v>
+        <v>0.001191252958960831</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.1381911784410477</v>
+        <v>-0.1371997743844986</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>-0.1617784351110458</v>
+        <v>-0.1423603594303131</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.181612491607666</v>
+        <v>-0.1757143288850784</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>-0.2114225476980209</v>
+        <v>-0.1793914884328842</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.1562432795763016</v>
+        <v>-0.1483894735574722</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>-0.3538329601287842</v>
+        <v>-0.3320634961128235</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0.04100978374481201</v>
+        <v>0.04409751668572426</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>-0.6527749300003052</v>
+        <v>-0.6469542384147644</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0.05705378577113152</v>
+        <v>0.06589303910732269</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>-0.5520613193511963</v>
+        <v>-0.5388917922973633</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.02022023685276508</v>
+        <v>0.0239784624427557</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>-0.5470158457756042</v>
+        <v>-0.5384265780448914</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>0.02022023685276508</v>
+        <v>0.0239784624427557</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.5957061052322388</v>
+        <v>-0.5942947864532471</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0.06815046817064285</v>
+        <v>0.07271952927112579</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>-0.6015552878379822</v>
+        <v>-0.6001967787742615</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -7555,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0.1157520934939384</v>
+        <v>0.1188884377479553</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.529748260974884</v>
+        <v>-0.5382775068283081</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1122450679540634</v>
+        <v>0.1135607585310936</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>-0.4864888787269592</v>
+        <v>-0.4984760582447052</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1157311126589775</v>
+        <v>0.1221655905246735</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>-0.4893954396247864</v>
+        <v>-0.4980138540267944</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.02278027310967445</v>
+        <v>-0.01795278117060661</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -7702,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>-0.3237617909908295</v>
+        <v>-0.3220716416835785</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.02615581080317497</v>
+        <v>-0.02147484384477139</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>-0.3296782672405243</v>
+        <v>-0.3231538534164429</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0.02932729758322239</v>
+        <v>0.03112388215959072</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.1664222180843353</v>
+        <v>-0.1518710255622864</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0.04789502546191216</v>
+        <v>0.05267029628157616</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -7825,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>0.1681271195411682</v>
+        <v>0.1663599163293839</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>0.05565387755632401</v>
+        <v>0.05550070852041245</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0.2414347380399704</v>
+        <v>0.2362882643938065</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -7883,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.08101779222488403</v>
+        <v>-0.07702946662902832</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0.1654376983642578</v>
+        <v>0.1688323020935059</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.0518791601061821</v>
+        <v>-0.05157550051808357</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>-0.2547317147254944</v>
+        <v>-0.2294626981019974</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1407949328422546</v>
+        <v>0.1415304094552994</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0.09896719455718994</v>
+        <v>0.0868537649512291</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0.205926313996315</v>
+        <v>0.1970170140266418</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>0.538108766078949</v>
+        <v>0.5119173526763916</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1776996999979019</v>
+        <v>0.1717754304409027</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>0.690362811088562</v>
+        <v>0.6559438705444336</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1407949328422546</v>
+        <v>0.1415304094552994</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>0.6070654392242432</v>
+        <v>0.5768401026725769</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0.115066684782505</v>
+        <v>0.1093113198876381</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0.5262632966041565</v>
+        <v>0.5052553415298462</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1445007026195526</v>
+        <v>0.1424951702356339</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0.4845298528671265</v>
+        <v>0.4718219339847565</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2395601123571396</v>
+        <v>0.2411491423845291</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>0.5921217799186707</v>
+        <v>0.5628707408905029</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>0.03486683592200279</v>
+        <v>0.02419329434633255</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>1.547710061073303</v>
+        <v>1.54093337059021</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.03548953682184219</v>
+        <v>-0.04001208767294884</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1.261203765869141</v>
+        <v>1.233199238777161</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.01403567474335432</v>
+        <v>-0.0203300416469574</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>-0.05016656219959259</v>
+        <v>-0.05614975467324257</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.03483909368515015</v>
+        <v>-0.03617984429001808</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>-0.04276924207806587</v>
+        <v>-0.03675399348139763</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.01345470733940601</v>
+        <v>-0.01844539120793343</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0.2193654030561447</v>
+        <v>0.2149292826652527</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -8457,7 +8457,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.06496924161911011</v>
+        <v>-0.0784786194562912</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -8481,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>-0.07330410927534103</v>
+        <v>-0.06734481453895569</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -8498,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.09956203401088715</v>
+        <v>-0.1076405718922615</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-0.3406698107719421</v>
+        <v>-0.3103392124176025</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -8536,40 +8536,40 @@
         <v>177.985</v>
       </c>
       <c r="B198" t="n">
-        <v>222.1478118896484</v>
+        <v>222.2154998779297</v>
       </c>
       <c r="C198" t="n">
-        <v>202.2667236328125</v>
+        <v>202.2439727783203</v>
       </c>
       <c r="D198" t="n">
-        <v>204.4253146826161</v>
+        <v>204.4408519603756</v>
       </c>
       <c r="E198" t="n">
-        <v>200.5618703365326</v>
+        <v>200.5806022590245</v>
       </c>
       <c r="F198" t="n">
-        <v>195.2181129454804</v>
+        <v>188.1348535832635</v>
       </c>
       <c r="G198" t="n">
-        <v>203.1377258300781</v>
+        <v>203.1279754638672</v>
       </c>
       <c r="H198" t="n">
-        <v>189.7807327341721</v>
+        <v>184.5489260402543</v>
       </c>
       <c r="I198" t="n">
-        <v>171.6789435710253</v>
+        <v>172.5142200916615</v>
       </c>
       <c r="J198" t="n">
-        <v>201.7582244873047</v>
+        <v>201.7899627685547</v>
       </c>
       <c r="K198" t="n">
-        <v>190.6851654052734</v>
+        <v>190.6326751708984</v>
       </c>
       <c r="L198" t="n">
-        <v>176.0448491699436</v>
+        <v>179.1975281590969</v>
       </c>
       <c r="M198" t="n">
-        <v>176.0448491699436</v>
+        <v>179.1975281590969</v>
       </c>
     </row>
     <row r="199">
@@ -8577,40 +8577,40 @@
         <v>202.22</v>
       </c>
       <c r="B199" t="n">
-        <v>215.7759094238281</v>
+        <v>215.8196563720703</v>
       </c>
       <c r="C199" t="n">
-        <v>205.5288848876953</v>
+        <v>205.5852508544922</v>
       </c>
       <c r="D199" t="n">
-        <v>205.0216246361044</v>
+        <v>205.0165083747972</v>
       </c>
       <c r="E199" t="n">
-        <v>205.6332705020905</v>
+        <v>205.6271070230112</v>
       </c>
       <c r="F199" t="n">
-        <v>202.5054141158049</v>
+        <v>202.6045475377257</v>
       </c>
       <c r="G199" t="n">
-        <v>204.5014953613281</v>
+        <v>204.4525756835938</v>
       </c>
       <c r="H199" t="n">
-        <v>210.3097186840015</v>
+        <v>212.1956393324571</v>
       </c>
       <c r="I199" t="n">
-        <v>203.4464345569199</v>
+        <v>202.0072995476634</v>
       </c>
       <c r="J199" t="n">
-        <v>222.4732513427734</v>
+        <v>222.4751129150391</v>
       </c>
       <c r="K199" t="n">
-        <v>213.0293273925781</v>
+        <v>212.9975128173828</v>
       </c>
       <c r="L199" t="n">
-        <v>209.285256614939</v>
+        <v>205.6970309715444</v>
       </c>
       <c r="M199" t="n">
-        <v>209.285256614939</v>
+        <v>205.6970309715444</v>
       </c>
     </row>
     <row r="200">
@@ -8618,40 +8618,40 @@
         <v>196.915</v>
       </c>
       <c r="B200" t="n">
-        <v>215.7040100097656</v>
+        <v>215.6659698486328</v>
       </c>
       <c r="C200" t="n">
-        <v>205.2601318359375</v>
+        <v>205.2482604980469</v>
       </c>
       <c r="D200" t="n">
-        <v>204.6740980587049</v>
+        <v>204.6494053659746</v>
       </c>
       <c r="E200" t="n">
-        <v>204.8894238471985</v>
+        <v>204.8559367420652</v>
       </c>
       <c r="F200" t="n">
-        <v>202.1378274563818</v>
+        <v>201.9204129658523</v>
       </c>
       <c r="G200" t="n">
-        <v>204.1292114257812</v>
+        <v>204.0863800048828</v>
       </c>
       <c r="H200" t="n">
-        <v>206.7552294026441</v>
+        <v>210.7354296504379</v>
       </c>
       <c r="I200" t="n">
-        <v>204.1196151254984</v>
+        <v>204.3304713064431</v>
       </c>
       <c r="J200" t="n">
-        <v>215.8143157958984</v>
+        <v>215.8105621337891</v>
       </c>
       <c r="K200" t="n">
-        <v>212.9433135986328</v>
+        <v>212.9937744140625</v>
       </c>
       <c r="L200" t="n">
-        <v>209.0623126853026</v>
+        <v>207.9069619473025</v>
       </c>
       <c r="M200" t="n">
-        <v>209.0623126853026</v>
+        <v>207.9069619473025</v>
       </c>
     </row>
     <row r="201">
@@ -8659,40 +8659,40 @@
         <v>199.59</v>
       </c>
       <c r="B201" t="n">
-        <v>215.8950500488281</v>
+        <v>215.9075012207031</v>
       </c>
       <c r="C201" t="n">
-        <v>206.1314697265625</v>
+        <v>206.161376953125</v>
       </c>
       <c r="D201" t="n">
-        <v>205.8234792433114</v>
+        <v>205.8348965843339</v>
       </c>
       <c r="E201" t="n">
-        <v>207.395822763443</v>
+        <v>207.4115236863003</v>
       </c>
       <c r="F201" t="n">
-        <v>204.462934766358</v>
+        <v>202.6045475377257</v>
       </c>
       <c r="G201" t="n">
-        <v>205.2061004638672</v>
+        <v>205.1789398193359</v>
       </c>
       <c r="H201" t="n">
-        <v>213.6678581124197</v>
+        <v>212.7933135424686</v>
       </c>
       <c r="I201" t="n">
-        <v>204.8324512748733</v>
+        <v>204.1757833963583</v>
       </c>
       <c r="J201" t="n">
-        <v>215.9271697998047</v>
+        <v>215.9689483642578</v>
       </c>
       <c r="K201" t="n">
-        <v>212.8379516601562</v>
+        <v>212.8992004394531</v>
       </c>
       <c r="L201" t="n">
-        <v>210.5344046536293</v>
+        <v>206.7493818427743</v>
       </c>
       <c r="M201" t="n">
-        <v>210.5344046536293</v>
+        <v>206.7493818427743</v>
       </c>
     </row>
     <row r="202">
@@ -8700,40 +8700,40 @@
         <v>203.615</v>
       </c>
       <c r="B202" t="n">
-        <v>216.1147308349609</v>
+        <v>216.1446685791016</v>
       </c>
       <c r="C202" t="n">
-        <v>207.3292694091797</v>
+        <v>207.3740692138672</v>
       </c>
       <c r="D202" t="n">
-        <v>207.6347890979641</v>
+        <v>207.6354622902414</v>
       </c>
       <c r="E202" t="n">
-        <v>210.8790833950043</v>
+        <v>210.8806895643477</v>
       </c>
       <c r="F202" t="n">
-        <v>207.5905319362564</v>
+        <v>207.8749430653013</v>
       </c>
       <c r="G202" t="n">
-        <v>206.4677276611328</v>
+        <v>206.4479675292969</v>
       </c>
       <c r="H202" t="n">
-        <v>214.7238157287751</v>
+        <v>216.7433052072485</v>
       </c>
       <c r="I202" t="n">
-        <v>208.7359120079183</v>
+        <v>208.19273588889</v>
       </c>
       <c r="J202" t="n">
-        <v>216.4481811523438</v>
+        <v>216.4715118408203</v>
       </c>
       <c r="K202" t="n">
-        <v>213.2144622802734</v>
+        <v>213.288818359375</v>
       </c>
       <c r="L202" t="n">
-        <v>216.6147727792721</v>
+        <v>213.3145063592322</v>
       </c>
       <c r="M202" t="n">
-        <v>216.6147727792721</v>
+        <v>213.3145063592322</v>
       </c>
     </row>
     <row r="203">
@@ -8741,40 +8741,40 @@
         <v>197.925</v>
       </c>
       <c r="B203" t="n">
-        <v>216.4790191650391</v>
+        <v>216.4822387695312</v>
       </c>
       <c r="C203" t="n">
-        <v>209.1411895751953</v>
+        <v>209.1385345458984</v>
       </c>
       <c r="D203" t="n">
-        <v>210.1916054825137</v>
+        <v>210.2000203859796</v>
       </c>
       <c r="E203" t="n">
-        <v>214.821355342865</v>
+        <v>214.8302894065459</v>
       </c>
       <c r="F203" t="n">
-        <v>209.123543611154</v>
+        <v>212.4315589777559</v>
       </c>
       <c r="G203" t="n">
-        <v>208.0584564208984</v>
+        <v>207.96923828125</v>
       </c>
       <c r="H203" t="n">
-        <v>219.015317675196</v>
+        <v>219.4496347543065</v>
       </c>
       <c r="I203" t="n">
-        <v>213.9804945547255</v>
+        <v>214.2403972155818</v>
       </c>
       <c r="J203" t="n">
-        <v>216.9403686523438</v>
+        <v>216.9536743164062</v>
       </c>
       <c r="K203" t="n">
-        <v>214.7880096435547</v>
+        <v>214.8886871337891</v>
       </c>
       <c r="L203" t="n">
-        <v>220.4174911008434</v>
+        <v>220.9929612467994</v>
       </c>
       <c r="M203" t="n">
-        <v>220.4174911008434</v>
+        <v>220.9929612467994</v>
       </c>
     </row>
     <row r="204">
@@ -8782,40 +8782,40 @@
         <v>218.385</v>
       </c>
       <c r="B204" t="n">
-        <v>216.7548217773438</v>
+        <v>216.7701416015625</v>
       </c>
       <c r="C204" t="n">
-        <v>210.4825897216797</v>
+        <v>210.4998321533203</v>
       </c>
       <c r="D204" t="n">
-        <v>212.1447757870114</v>
+        <v>212.1525444258912</v>
       </c>
       <c r="E204" t="n">
-        <v>217.0114078521729</v>
+        <v>217.0185479750773</v>
       </c>
       <c r="F204" t="n">
-        <v>215.3580605113018</v>
+        <v>219.9899168141957</v>
       </c>
       <c r="G204" t="n">
-        <v>208.9014434814453</v>
+        <v>208.8824920654297</v>
       </c>
       <c r="H204" t="n">
-        <v>222.6434434423225</v>
+        <v>221.4182887912205</v>
       </c>
       <c r="I204" t="n">
-        <v>219.8824938627253</v>
+        <v>219.1244103277106</v>
       </c>
       <c r="J204" t="n">
-        <v>217.4212036132812</v>
+        <v>217.4006042480469</v>
       </c>
       <c r="K204" t="n">
-        <v>215.7796020507812</v>
+        <v>215.9126434326172</v>
       </c>
       <c r="L204" t="n">
-        <v>226.0260569150533</v>
+        <v>224.6255476638571</v>
       </c>
       <c r="M204" t="n">
-        <v>226.0260569150533</v>
+        <v>224.6255476638571</v>
       </c>
     </row>
     <row r="205">
@@ -8823,40 +8823,40 @@
         <v>208.135</v>
       </c>
       <c r="B205" t="n">
-        <v>216.7201538085938</v>
+        <v>216.7888641357422</v>
       </c>
       <c r="C205" t="n">
-        <v>210.5069122314453</v>
+        <v>210.5253753662109</v>
       </c>
       <c r="D205" t="n">
-        <v>212.2157108601544</v>
+        <v>212.2030817730327</v>
       </c>
       <c r="E205" t="n">
-        <v>217.0772092342377</v>
+        <v>217.067793206148</v>
       </c>
       <c r="F205" t="n">
-        <v>215.3580605113018</v>
+        <v>219.9899168141957</v>
       </c>
       <c r="G205" t="n">
-        <v>208.8745880126953</v>
+        <v>208.9090118408203</v>
       </c>
       <c r="H205" t="n">
-        <v>222.7024724492055</v>
+        <v>221.6963173153638</v>
       </c>
       <c r="I205" t="n">
-        <v>223.7371445862697</v>
+        <v>223.655610421185</v>
       </c>
       <c r="J205" t="n">
-        <v>217.5162963867188</v>
+        <v>217.5414886474609</v>
       </c>
       <c r="K205" t="n">
-        <v>216.6551666259766</v>
+        <v>216.8547515869141</v>
       </c>
       <c r="L205" t="n">
-        <v>228.6739137732083</v>
+        <v>227.1464991765997</v>
       </c>
       <c r="M205" t="n">
-        <v>228.6739137732083</v>
+        <v>227.1464991765997</v>
       </c>
     </row>
     <row r="206">
@@ -8864,40 +8864,40 @@
         <v>217.51</v>
       </c>
       <c r="B206" t="n">
-        <v>216.6551513671875</v>
+        <v>216.6590576171875</v>
       </c>
       <c r="C206" t="n">
-        <v>210.1584014892578</v>
+        <v>210.2319183349609</v>
       </c>
       <c r="D206" t="n">
-        <v>211.7055324016524</v>
+        <v>211.7258224168895</v>
       </c>
       <c r="E206" t="n">
-        <v>216.576366186142</v>
+        <v>216.5944052966901</v>
       </c>
       <c r="F206" t="n">
-        <v>215.2066030088082</v>
+        <v>219.9899168141957</v>
       </c>
       <c r="G206" t="n">
-        <v>208.7224731445312</v>
+        <v>208.6343841552734</v>
       </c>
       <c r="H206" t="n">
-        <v>221.8511065387312</v>
+        <v>221.5113571740643</v>
       </c>
       <c r="I206" t="n">
-        <v>222.7294486597425</v>
+        <v>222.5871615071714</v>
       </c>
       <c r="J206" t="n">
-        <v>217.5063934326172</v>
+        <v>217.5188751220703</v>
       </c>
       <c r="K206" t="n">
-        <v>216.5741424560547</v>
+        <v>216.5972595214844</v>
       </c>
       <c r="L206" t="n">
-        <v>228.3140722444744</v>
+        <v>226.6953902090478</v>
       </c>
       <c r="M206" t="n">
-        <v>228.3140722444744</v>
+        <v>226.6953902090478</v>
       </c>
     </row>
     <row r="207">
@@ -8905,40 +8905,40 @@
         <v>189.765</v>
       </c>
       <c r="B207" t="n">
-        <v>216.26220703125</v>
+        <v>216.2822418212891</v>
       </c>
       <c r="C207" t="n">
-        <v>208.2953033447266</v>
+        <v>208.2440795898438</v>
       </c>
       <c r="D207" t="n">
-        <v>208.9565161324657</v>
+        <v>208.951413335004</v>
       </c>
       <c r="E207" t="n">
-        <v>213.0705664157867</v>
+        <v>213.0659705869858</v>
       </c>
       <c r="F207" t="n">
-        <v>208.3396300658591</v>
+        <v>211.5648416846926</v>
       </c>
       <c r="G207" t="n">
-        <v>207.3642883300781</v>
+        <v>207.3328704833984</v>
       </c>
       <c r="H207" t="n">
-        <v>215.8990780303562</v>
+        <v>217.0937202466743</v>
       </c>
       <c r="I207" t="n">
-        <v>221.2746513195518</v>
+        <v>218.8782958073523</v>
       </c>
       <c r="J207" t="n">
-        <v>217.0172882080078</v>
+        <v>216.9993286132812</v>
       </c>
       <c r="K207" t="n">
-        <v>216.0299377441406</v>
+        <v>216.1200866699219</v>
       </c>
       <c r="L207" t="n">
-        <v>226.8044389654857</v>
+        <v>223.255095384155</v>
       </c>
       <c r="M207" t="n">
-        <v>226.8044389654857</v>
+        <v>223.255095384155</v>
       </c>
     </row>
     <row r="208">
@@ -8949,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>0.005691600497812033</v>
+        <v>-0.01151760201901197</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>4.266043663024902</v>
+        <v>4.053350448608398</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>0.0210900567471981</v>
+        <v>0.009266234003007412</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>0.5414726734161377</v>
+        <v>0.5271022915840149</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>0.01786302402615547</v>
+        <v>0.003601560136303306</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5970413684844971</v>
+        <v>0.5712894201278687</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.02357176132500172</v>
+        <v>-0.04237186536192894</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>0.3862650692462921</v>
+        <v>0.387249767780304</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.01282478030771017</v>
+        <v>-0.02523563243448734</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>0.1905146837234497</v>
+        <v>0.1990599036216736</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>0.01024702563881874</v>
+        <v>-0.005288746207952499</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>-0.04171221330761909</v>
+        <v>-0.04031720384955406</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.02196453884243965</v>
+        <v>-0.0311348382383585</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>0.3869341611862183</v>
+        <v>0.3760850131511688</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -9236,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.01904571056365967</v>
+        <v>-0.02927396818995476</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -9260,7 +9260,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>0.1784854680299759</v>
+        <v>0.189001590013504</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.09213510900735855</v>
+        <v>-0.1059512868523598</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>-0.05595759302377701</v>
+        <v>-0.05986589938402176</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.08429203182458878</v>
+        <v>-0.09106315672397614</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -9342,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>-0.3745007216930389</v>
+        <v>-0.3573743402957916</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.05062198638916016</v>
+        <v>-0.06752531975507736</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -9383,7 +9383,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>-0.2798145413398743</v>
+        <v>-0.2641718089580536</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -9400,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.01858597062528133</v>
+        <v>-0.03337478265166283</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>-0.04555704817175865</v>
+        <v>-0.02758579142391682</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.02408045716583729</v>
+        <v>-0.03055806644260883</v>
       </c>
       <c r="D220" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>0.0737437978386879</v>
+        <v>0.07698848843574524</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.03703147917985916</v>
+        <v>-0.04564902186393738</v>
       </c>
       <c r="D221" t="n">
         <v>0</v>
@@ -9506,7 +9506,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>0.07459520548582077</v>
+        <v>0.09119656682014465</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.01858597062528133</v>
+        <v>-0.03337478265166283</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>0.0653332844376564</v>
+        <v>0.05315107479691505</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.09100347757339478</v>
+        <v>-0.09669473022222519</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>0.1381706595420837</v>
+        <v>0.1470208168029785</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.1097028702497482</v>
+        <v>-0.1043811291456223</v>
       </c>
       <c r="D224" t="n">
         <v>0</v>
@@ -9629,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.7607327103614807</v>
+        <v>-0.7111788392066956</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.1190592050552368</v>
+        <v>-0.1262546330690384</v>
       </c>
       <c r="D225" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.8216942548751831</v>
+        <v>-0.8081114888191223</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.1410233974456787</v>
+        <v>-0.1479987502098083</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.8958017230033875</v>
+        <v>-0.8435733914375305</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.1674730777740479</v>
+        <v>-0.1726288199424744</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.9059197306632996</v>
+        <v>-0.8623998761177063</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.1669855862855911</v>
+        <v>-0.1716340333223343</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>-1.149800539016724</v>
+        <v>-1.07379949092865</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -9807,40 +9807,40 @@
         <v>203.03</v>
       </c>
       <c r="B229" t="n">
-        <v>220.3490600585938</v>
+        <v>220.3411560058594</v>
       </c>
       <c r="C229" t="n">
-        <v>217.2303619384766</v>
+        <v>217.2140960693359</v>
       </c>
       <c r="D229" t="n">
-        <v>210.5334378497152</v>
+        <v>210.5364537511174</v>
       </c>
       <c r="E229" t="n">
-        <v>221.9610528945923</v>
+        <v>221.9658315505162</v>
       </c>
       <c r="F229" t="n">
-        <v>221.633510370593</v>
+        <v>220.947296432421</v>
       </c>
       <c r="G229" t="n">
-        <v>217.7893981933594</v>
+        <v>217.7874145507812</v>
       </c>
       <c r="H229" t="n">
-        <v>226.2720957359074</v>
+        <v>223.7853975656166</v>
       </c>
       <c r="I229" t="n">
-        <v>190.2870484007844</v>
+        <v>191.487652556154</v>
       </c>
       <c r="J229" t="n">
-        <v>204.9290008544922</v>
+        <v>204.9675598144531</v>
       </c>
       <c r="K229" t="n">
-        <v>196.0857696533203</v>
+        <v>196.1784057617188</v>
       </c>
       <c r="L229" t="n">
-        <v>218.2812757945806</v>
+        <v>212.7008989605582</v>
       </c>
       <c r="M229" t="n">
-        <v>218.2812757945806</v>
+        <v>212.7008989605582</v>
       </c>
     </row>
     <row r="230">
@@ -9848,40 +9848,40 @@
         <v>200.305</v>
       </c>
       <c r="B230" t="n">
-        <v>220.6993865966797</v>
+        <v>220.6887969970703</v>
       </c>
       <c r="C230" t="n">
-        <v>219.4565887451172</v>
+        <v>219.4209136962891</v>
       </c>
       <c r="D230" t="n">
-        <v>213.8081620424249</v>
+        <v>213.837365123413</v>
       </c>
       <c r="E230" t="n">
-        <v>228.3873264789581</v>
+        <v>228.4189718066985</v>
       </c>
       <c r="F230" t="n">
-        <v>224.9427001505288</v>
+        <v>225.0486120107964</v>
       </c>
       <c r="G230" t="n">
-        <v>220.409912109375</v>
+        <v>220.4193115234375</v>
       </c>
       <c r="H230" t="n">
-        <v>230.4966591131746</v>
+        <v>229.5782894431879</v>
       </c>
       <c r="I230" t="n">
-        <v>218.3139863797273</v>
+        <v>222.3655236443533</v>
       </c>
       <c r="J230" t="n">
-        <v>222.6972503662109</v>
+        <v>222.7318420410156</v>
       </c>
       <c r="K230" t="n">
-        <v>221.0593872070312</v>
+        <v>221.1861572265625</v>
       </c>
       <c r="L230" t="n">
-        <v>225.1757628460868</v>
+        <v>228.5348686491658</v>
       </c>
       <c r="M230" t="n">
-        <v>225.1757628460868</v>
+        <v>228.5348686491658</v>
       </c>
     </row>
     <row r="231">
@@ -9889,40 +9889,40 @@
         <v>210.13</v>
       </c>
       <c r="B231" t="n">
-        <v>220.6311798095703</v>
+        <v>220.621337890625</v>
       </c>
       <c r="C231" t="n">
-        <v>219.015380859375</v>
+        <v>219.0086517333984</v>
       </c>
       <c r="D231" t="n">
-        <v>213.166871050228</v>
+        <v>213.1699542708579</v>
       </c>
       <c r="E231" t="n">
-        <v>227.2840931415558</v>
+        <v>227.2883200447088</v>
       </c>
       <c r="F231" t="n">
-        <v>225.0129186838547</v>
+        <v>225.2370347128935</v>
       </c>
       <c r="G231" t="n">
-        <v>219.9236602783203</v>
+        <v>219.9061279296875</v>
       </c>
       <c r="H231" t="n">
-        <v>229.0037110680106</v>
+        <v>226.0600854831529</v>
       </c>
       <c r="I231" t="n">
-        <v>225.3774103304622</v>
+        <v>223.9686314753133</v>
       </c>
       <c r="J231" t="n">
-        <v>222.8739166259766</v>
+        <v>222.8555297851562</v>
       </c>
       <c r="K231" t="n">
-        <v>221.2561492919922</v>
+        <v>221.3860321044922</v>
       </c>
       <c r="L231" t="n">
-        <v>230.322486610309</v>
+        <v>229.3892874201599</v>
       </c>
       <c r="M231" t="n">
-        <v>230.322486610309</v>
+        <v>229.3892874201599</v>
       </c>
     </row>
     <row r="232">
@@ -9930,40 +9930,40 @@
         <v>212.27</v>
       </c>
       <c r="B232" t="n">
-        <v>221.0173492431641</v>
+        <v>221.0265502929688</v>
       </c>
       <c r="C232" t="n">
-        <v>221.6054992675781</v>
+        <v>221.5538940429688</v>
       </c>
       <c r="D232" t="n">
-        <v>216.7765000322844</v>
+        <v>216.7691487726165</v>
       </c>
       <c r="E232" t="n">
-        <v>232.4847843647003</v>
+        <v>232.4794930101602</v>
       </c>
       <c r="F232" t="n">
-        <v>230.4084051171345</v>
+        <v>229.7474359169703</v>
       </c>
       <c r="G232" t="n">
-        <v>222.5202789306641</v>
+        <v>222.5422668457031</v>
       </c>
       <c r="H232" t="n">
-        <v>235.4550425818958</v>
+        <v>233.94107517545</v>
       </c>
       <c r="I232" t="n">
-        <v>226.1748111003868</v>
+        <v>227.6174771431057</v>
       </c>
       <c r="J232" t="n">
-        <v>223.3325653076172</v>
+        <v>223.4020080566406</v>
       </c>
       <c r="K232" t="n">
-        <v>222.3849182128906</v>
+        <v>222.6034698486328</v>
       </c>
       <c r="L232" t="n">
-        <v>232.6385408313804</v>
+        <v>232.3102320601541</v>
       </c>
       <c r="M232" t="n">
-        <v>232.6385408313804</v>
+        <v>232.3102320601541</v>
       </c>
     </row>
     <row r="233">
@@ -9971,40 +9971,40 @@
         <v>221.105</v>
       </c>
       <c r="B233" t="n">
-        <v>220.951171875</v>
+        <v>220.9587097167969</v>
       </c>
       <c r="C233" t="n">
-        <v>221.345703125</v>
+        <v>221.3587188720703</v>
       </c>
       <c r="D233" t="n">
-        <v>216.5470785437501</v>
+        <v>216.5647296452602</v>
       </c>
       <c r="E233" t="n">
-        <v>232.2296276092529</v>
+        <v>232.2453636406404</v>
       </c>
       <c r="F233" t="n">
-        <v>230.1994040329802</v>
+        <v>229.7474359169703</v>
       </c>
       <c r="G233" t="n">
-        <v>222.3908538818359</v>
+        <v>222.3613433837891</v>
       </c>
       <c r="H233" t="n">
-        <v>235.2621235974879</v>
+        <v>233.8084294255613</v>
       </c>
       <c r="I233" t="n">
-        <v>230.4963659981196</v>
+        <v>229.4201442706405</v>
       </c>
       <c r="J233" t="n">
-        <v>223.6437377929688</v>
+        <v>223.5868835449219</v>
       </c>
       <c r="K233" t="n">
-        <v>223.4375915527344</v>
+        <v>223.5370635986328</v>
       </c>
       <c r="L233" t="n">
-        <v>235.6481583819953</v>
+        <v>235.4830357774391</v>
       </c>
       <c r="M233" t="n">
-        <v>235.6481583819953</v>
+        <v>235.4830357774391</v>
       </c>
     </row>
     <row r="234">
@@ -10012,40 +10012,40 @@
         <v>220.26</v>
       </c>
       <c r="B234" t="n">
-        <v>220.8385162353516</v>
+        <v>220.8564758300781</v>
       </c>
       <c r="C234" t="n">
-        <v>220.1083679199219</v>
+        <v>220.1430969238281</v>
       </c>
       <c r="D234" t="n">
-        <v>214.8367954570345</v>
+        <v>214.8459508720054</v>
       </c>
       <c r="E234" t="n">
-        <v>229.9810523986816</v>
+        <v>229.9908147367792</v>
       </c>
       <c r="F234" t="n">
-        <v>228.2265252897448</v>
+        <v>229.0461269163228</v>
       </c>
       <c r="G234" t="n">
-        <v>221.1619415283203</v>
+        <v>221.1547546386719</v>
       </c>
       <c r="H234" t="n">
-        <v>233.5880735004098</v>
+        <v>232.0200629061556</v>
       </c>
       <c r="I234" t="n">
-        <v>227.9090564563993</v>
+        <v>227.8648199655562</v>
       </c>
       <c r="J234" t="n">
-        <v>223.3065795898438</v>
+        <v>223.2726287841797</v>
       </c>
       <c r="K234" t="n">
-        <v>223.0390014648438</v>
+        <v>223.1971588134766</v>
       </c>
       <c r="L234" t="n">
-        <v>235.3894290781824</v>
+        <v>234.9457656022039</v>
       </c>
       <c r="M234" t="n">
-        <v>235.3894290781824</v>
+        <v>234.9457656022039</v>
       </c>
     </row>
     <row r="235">
@@ -10053,40 +10053,40 @@
         <v>220.615</v>
       </c>
       <c r="B235" t="n">
-        <v>220.8528289794922</v>
+        <v>220.8826293945312</v>
       </c>
       <c r="C235" t="n">
-        <v>220.2764282226562</v>
+        <v>220.3114013671875</v>
       </c>
       <c r="D235" t="n">
-        <v>215.0193358353794</v>
+        <v>215.0302550141168</v>
       </c>
       <c r="E235" t="n">
-        <v>230.2594892978668</v>
+        <v>230.2708159505949</v>
       </c>
       <c r="F235" t="n">
-        <v>228.4994362971519</v>
+        <v>229.0461269163228</v>
       </c>
       <c r="G235" t="n">
-        <v>221.2538299560547</v>
+        <v>221.221923828125</v>
       </c>
       <c r="H235" t="n">
-        <v>234.2866712217233</v>
+        <v>232.4841772808774</v>
       </c>
       <c r="I235" t="n">
-        <v>227.3300346958458</v>
+        <v>227.9486532664008</v>
       </c>
       <c r="J235" t="n">
-        <v>223.1947937011719</v>
+        <v>223.2361602783203</v>
       </c>
       <c r="K235" t="n">
-        <v>222.5769195556641</v>
+        <v>222.6465148925781</v>
       </c>
       <c r="L235" t="n">
-        <v>235.2230989090335</v>
+        <v>234.4294037271934</v>
       </c>
       <c r="M235" t="n">
-        <v>235.2230989090335</v>
+        <v>234.4294037271934</v>
       </c>
     </row>
     <row r="236">
@@ -10094,40 +10094,40 @@
         <v>190.665</v>
       </c>
       <c r="B236" t="n">
-        <v>226.6047821044922</v>
+        <v>226.6255645751953</v>
       </c>
       <c r="C236" t="n">
-        <v>219.1562957763672</v>
+        <v>219.1747131347656</v>
       </c>
       <c r="D236" t="n">
-        <v>218.3950364284347</v>
+        <v>218.3978772998448</v>
       </c>
       <c r="E236" t="n">
-        <v>216.9952838420868</v>
+        <v>216.9974609275595</v>
       </c>
       <c r="F236" t="n">
-        <v>223.0488350581136</v>
+        <v>223.3315554232753</v>
       </c>
       <c r="G236" t="n">
-        <v>224.3338623046875</v>
+        <v>224.3224334716797</v>
       </c>
       <c r="H236" t="n">
-        <v>220.1720716129985</v>
+        <v>220.7809362762216</v>
       </c>
       <c r="I236" t="n">
-        <v>225.0086987613272</v>
+        <v>222.3771467805535</v>
       </c>
       <c r="J236" t="n">
-        <v>221.4244079589844</v>
+        <v>221.4142303466797</v>
       </c>
       <c r="K236" t="n">
-        <v>225.8503265380859</v>
+        <v>225.8616638183594</v>
       </c>
       <c r="L236" t="n">
-        <v>222.6181368354318</v>
+        <v>222.3360131121582</v>
       </c>
       <c r="M236" t="n">
-        <v>222.6181368354318</v>
+        <v>222.3360131121582</v>
       </c>
     </row>
     <row r="237">
@@ -10135,40 +10135,40 @@
         <v>200.085</v>
       </c>
       <c r="B237" t="n">
-        <v>222.3590087890625</v>
+        <v>222.3431854248047</v>
       </c>
       <c r="C237" t="n">
-        <v>222.3470001220703</v>
+        <v>222.3548126220703</v>
       </c>
       <c r="D237" t="n">
-        <v>217.6688956755805</v>
+        <v>217.6701882047528</v>
       </c>
       <c r="E237" t="n">
-        <v>228.0849514007568</v>
+        <v>228.08726742317</v>
       </c>
       <c r="F237" t="n">
-        <v>218.4675999207323</v>
+        <v>216.1171047308789</v>
       </c>
       <c r="G237" t="n">
-        <v>217.4334716796875</v>
+        <v>217.4579010009766</v>
       </c>
       <c r="H237" t="n">
-        <v>209.7288892530979</v>
+        <v>213.9276478590663</v>
       </c>
       <c r="I237" t="n">
-        <v>217.5508421632088</v>
+        <v>221.3788521569566</v>
       </c>
       <c r="J237" t="n">
-        <v>223.5445251464844</v>
+        <v>223.5855560302734</v>
       </c>
       <c r="K237" t="n">
-        <v>225.7919769287109</v>
+        <v>225.7300567626953</v>
       </c>
       <c r="L237" t="n">
-        <v>210.3167587368678</v>
+        <v>207.3792172119843</v>
       </c>
       <c r="M237" t="n">
-        <v>210.3167587368678</v>
+        <v>207.3792172119843</v>
       </c>
     </row>
     <row r="238">
@@ -10176,40 +10176,40 @@
         <v>203.45</v>
       </c>
       <c r="B238" t="n">
-        <v>222.23876953125</v>
+        <v>222.2634582519531</v>
       </c>
       <c r="C238" t="n">
-        <v>220.5362701416016</v>
+        <v>220.5726318359375</v>
       </c>
       <c r="D238" t="n">
-        <v>215.7380154565114</v>
+        <v>215.7326568459843</v>
       </c>
       <c r="E238" t="n">
-        <v>224.6771767139435</v>
+        <v>224.6713849416163</v>
       </c>
       <c r="F238" t="n">
-        <v>216.9631623720544</v>
+        <v>215.7911014136668</v>
       </c>
       <c r="G238" t="n">
-        <v>214.9874114990234</v>
+        <v>215.0099945068359</v>
       </c>
       <c r="H238" t="n">
-        <v>209.0702973492832</v>
+        <v>212.4952495113812</v>
       </c>
       <c r="I238" t="n">
-        <v>215.8906154278668</v>
+        <v>216.7535180517814</v>
       </c>
       <c r="J238" t="n">
-        <v>221.9491882324219</v>
+        <v>221.8933563232422</v>
       </c>
       <c r="K238" t="n">
-        <v>225.1461791992188</v>
+        <v>225.0088653564453</v>
       </c>
       <c r="L238" t="n">
-        <v>212.5309525608838</v>
+        <v>209.6141935466603</v>
       </c>
       <c r="M238" t="n">
-        <v>212.5309525608838</v>
+        <v>209.6141935466603</v>
       </c>
     </row>
     <row r="239">
@@ -10217,40 +10217,40 @@
         <v>214.06</v>
       </c>
       <c r="B239" t="n">
-        <v>222.3381195068359</v>
+        <v>222.3795776367188</v>
       </c>
       <c r="C239" t="n">
-        <v>222.2229309082031</v>
+        <v>222.2049865722656</v>
       </c>
       <c r="D239" t="n">
-        <v>217.5385539023586</v>
+        <v>217.5363054401525</v>
       </c>
       <c r="E239" t="n">
-        <v>227.8678729534149</v>
+        <v>227.8661165263412</v>
       </c>
       <c r="F239" t="n">
-        <v>218.5352833739171</v>
+        <v>216.1171047308789</v>
       </c>
       <c r="G239" t="n">
-        <v>217.4016418457031</v>
+        <v>217.3075103759766</v>
       </c>
       <c r="H239" t="n">
-        <v>210.008384090856</v>
+        <v>214.0384512296098</v>
       </c>
       <c r="I239" t="n">
-        <v>214.4305828029506</v>
+        <v>215.2644400814975</v>
       </c>
       <c r="J239" t="n">
-        <v>222.1556854248047</v>
+        <v>222.1468811035156</v>
       </c>
       <c r="K239" t="n">
-        <v>224.9926605224609</v>
+        <v>224.9128875732422</v>
       </c>
       <c r="L239" t="n">
-        <v>211.8742033261665</v>
+        <v>210.0390530099463</v>
       </c>
       <c r="M239" t="n">
-        <v>211.8742033261665</v>
+        <v>210.0390530099463</v>
       </c>
     </row>
     <row r="240">
@@ -10258,40 +10258,40 @@
         <v>217.625</v>
       </c>
       <c r="B240" t="n">
-        <v>222.3621063232422</v>
+        <v>222.4149932861328</v>
       </c>
       <c r="C240" t="n">
-        <v>222.9805450439453</v>
+        <v>222.9558410644531</v>
       </c>
       <c r="D240" t="n">
-        <v>218.2930999118084</v>
+        <v>218.2935442187114</v>
       </c>
       <c r="E240" t="n">
-        <v>229.144186258316</v>
+        <v>229.1455123326165</v>
       </c>
       <c r="F240" t="n">
-        <v>219.7879711128133</v>
+        <v>216.5215679842168</v>
       </c>
       <c r="G240" t="n">
-        <v>218.3323822021484</v>
+        <v>218.3814239501953</v>
       </c>
       <c r="H240" t="n">
-        <v>209.6114492948874</v>
+        <v>213.5340392356025</v>
       </c>
       <c r="I240" t="n">
-        <v>216.9048164781365</v>
+        <v>218.3017065792439</v>
       </c>
       <c r="J240" t="n">
-        <v>222.4792327880859</v>
+        <v>222.4474029541016</v>
       </c>
       <c r="K240" t="n">
-        <v>226.1135559082031</v>
+        <v>226.0337371826172</v>
       </c>
       <c r="L240" t="n">
-        <v>213.9609485285611</v>
+        <v>213.2580252796473</v>
       </c>
       <c r="M240" t="n">
-        <v>213.9609485285611</v>
+        <v>213.2580252796473</v>
       </c>
     </row>
     <row r="241">
@@ -10299,40 +10299,40 @@
         <v>223.375</v>
       </c>
       <c r="B241" t="n">
-        <v>222.471923828125</v>
+        <v>222.4850158691406</v>
       </c>
       <c r="C241" t="n">
-        <v>224.2445373535156</v>
+        <v>224.2175598144531</v>
       </c>
       <c r="D241" t="n">
-        <v>219.7336779972664</v>
+        <v>219.7360745617736</v>
       </c>
       <c r="E241" t="n">
-        <v>231.393705368042</v>
+        <v>231.3970334061448</v>
       </c>
       <c r="F241" t="n">
-        <v>220.6139587204574</v>
+        <v>217.0486698681192</v>
       </c>
       <c r="G241" t="n">
-        <v>220.3105621337891</v>
+        <v>220.2842712402344</v>
       </c>
       <c r="H241" t="n">
-        <v>208.8953646199139</v>
+        <v>214.6780151356868</v>
       </c>
       <c r="I241" t="n">
-        <v>218.1889211329875</v>
+        <v>220.7358908439342</v>
       </c>
       <c r="J241" t="n">
-        <v>222.8372192382812</v>
+        <v>222.891357421875</v>
       </c>
       <c r="K241" t="n">
-        <v>226.9578552246094</v>
+        <v>226.8618927001953</v>
       </c>
       <c r="L241" t="n">
-        <v>215.0099927595777</v>
+        <v>215.2868430277674</v>
       </c>
       <c r="M241" t="n">
-        <v>215.0099927595777</v>
+        <v>215.2868430277674</v>
       </c>
     </row>
     <row r="242">
@@ -10340,40 +10340,40 @@
         <v>223.06</v>
       </c>
       <c r="B242" t="n">
-        <v>222.3022003173828</v>
+        <v>222.2975311279297</v>
       </c>
       <c r="C242" t="n">
-        <v>221.4845123291016</v>
+        <v>221.500732421875</v>
       </c>
       <c r="D242" t="n">
-        <v>216.6945233078104</v>
+        <v>216.7145036545998</v>
       </c>
       <c r="E242" t="n">
-        <v>226.4255814552307</v>
+        <v>226.4501646798843</v>
       </c>
       <c r="F242" t="n">
-        <v>217.7567909730432</v>
+        <v>215.8256285531585</v>
       </c>
       <c r="G242" t="n">
-        <v>216.266845703125</v>
+        <v>216.3079833984375</v>
       </c>
       <c r="H242" t="n">
-        <v>209.6765954574454</v>
+        <v>213.9533702840756</v>
       </c>
       <c r="I242" t="n">
-        <v>218.1885000371702</v>
+        <v>220.3059536765133</v>
       </c>
       <c r="J242" t="n">
-        <v>222.3676910400391</v>
+        <v>222.4204254150391</v>
       </c>
       <c r="K242" t="n">
-        <v>226.7222442626953</v>
+        <v>226.6823577880859</v>
       </c>
       <c r="L242" t="n">
-        <v>214.696353484205</v>
+        <v>212.7597023812776</v>
       </c>
       <c r="M242" t="n">
-        <v>214.696353484205</v>
+        <v>212.7597023812776</v>
       </c>
     </row>
     <row r="243">
@@ -10381,40 +10381,40 @@
         <v>217.395</v>
       </c>
       <c r="B243" t="n">
-        <v>222.3022003173828</v>
+        <v>222.2975311279297</v>
       </c>
       <c r="C243" t="n">
-        <v>221.4845123291016</v>
+        <v>221.500732421875</v>
       </c>
       <c r="D243" t="n">
-        <v>216.6945233078104</v>
+        <v>216.7145036545998</v>
       </c>
       <c r="E243" t="n">
-        <v>226.4255814552307</v>
+        <v>226.4501646798843</v>
       </c>
       <c r="F243" t="n">
-        <v>217.7567909730432</v>
+        <v>215.8256285531585</v>
       </c>
       <c r="G243" t="n">
-        <v>216.266845703125</v>
+        <v>216.3079833984375</v>
       </c>
       <c r="H243" t="n">
-        <v>209.6765954574454</v>
+        <v>213.9533702840756</v>
       </c>
       <c r="I243" t="n">
-        <v>216.9046001522168</v>
+        <v>218.54124141325</v>
       </c>
       <c r="J243" t="n">
-        <v>222.1167907714844</v>
+        <v>222.1633758544922</v>
       </c>
       <c r="K243" t="n">
-        <v>225.5469818115234</v>
+        <v>225.4929504394531</v>
       </c>
       <c r="L243" t="n">
-        <v>212.6256604160996</v>
+        <v>210.5537457904148</v>
       </c>
       <c r="M243" t="n">
-        <v>212.6256604160996</v>
+        <v>210.5537457904148</v>
       </c>
     </row>
     <row r="244">
@@ -10422,40 +10422,40 @@
         <v>215.855</v>
       </c>
       <c r="B244" t="n">
-        <v>222.3391723632812</v>
+        <v>222.3432922363281</v>
       </c>
       <c r="C244" t="n">
-        <v>221.6480560302734</v>
+        <v>221.5860443115234</v>
       </c>
       <c r="D244" t="n">
-        <v>216.9022342117074</v>
+        <v>216.8804093180783</v>
       </c>
       <c r="E244" t="n">
-        <v>226.7790212631226</v>
+        <v>226.7541232580992</v>
       </c>
       <c r="F244" t="n">
-        <v>217.9107235033516</v>
+        <v>215.8256285531585</v>
       </c>
       <c r="G244" t="n">
-        <v>216.4851531982422</v>
+        <v>216.57373046875</v>
       </c>
       <c r="H244" t="n">
-        <v>210.0893136236205</v>
+        <v>213.9369229097988</v>
       </c>
       <c r="I244" t="n">
-        <v>215.9978145574075</v>
+        <v>217.6238856541769</v>
       </c>
       <c r="J244" t="n">
-        <v>222.1616058349609</v>
+        <v>222.0992736816406</v>
       </c>
       <c r="K244" t="n">
-        <v>225.4322052001953</v>
+        <v>225.388916015625</v>
       </c>
       <c r="L244" t="n">
-        <v>212.4824080020085</v>
+        <v>210.6933823021644</v>
       </c>
       <c r="M244" t="n">
-        <v>212.4824080020085</v>
+        <v>210.6933823021644</v>
       </c>
     </row>
     <row r="245">
@@ -10463,40 +10463,40 @@
         <v>216.095</v>
       </c>
       <c r="B245" t="n">
-        <v>222.2245788574219</v>
+        <v>222.2301940917969</v>
       </c>
       <c r="C245" t="n">
-        <v>221.0534362792969</v>
+        <v>221.0253143310547</v>
       </c>
       <c r="D245" t="n">
-        <v>216.2147902929526</v>
+        <v>216.2312700399002</v>
       </c>
       <c r="E245" t="n">
-        <v>225.563606262207</v>
+        <v>225.5844263066932</v>
       </c>
       <c r="F245" t="n">
-        <v>217.1676920276102</v>
+        <v>215.7714636271</v>
       </c>
       <c r="G245" t="n">
-        <v>215.6558074951172</v>
+        <v>215.6156158447266</v>
       </c>
       <c r="H245" t="n">
-        <v>208.5082560649161</v>
+        <v>213.796930923157</v>
       </c>
       <c r="I245" t="n">
-        <v>216.3924003970317</v>
+        <v>218.044403571725</v>
       </c>
       <c r="J245" t="n">
-        <v>221.9933929443359</v>
+        <v>222.0368499755859</v>
       </c>
       <c r="K245" t="n">
-        <v>225.385498046875</v>
+        <v>225.3667907714844</v>
       </c>
       <c r="L245" t="n">
-        <v>211.8180790139387</v>
+        <v>208.7254262345551</v>
       </c>
       <c r="M245" t="n">
-        <v>211.8180790139387</v>
+        <v>208.7254262345551</v>
       </c>
     </row>
     <row r="246">
@@ -10504,40 +10504,40 @@
         <v>221.595</v>
       </c>
       <c r="B246" t="n">
-        <v>222.3520660400391</v>
+        <v>222.3816528320312</v>
       </c>
       <c r="C246" t="n">
-        <v>222.3745727539062</v>
+        <v>222.3435211181641</v>
       </c>
       <c r="D246" t="n">
-        <v>217.6843907007677</v>
+        <v>217.7041556260284</v>
       </c>
       <c r="E246" t="n">
-        <v>228.1228778362274</v>
+        <v>228.1462582553675</v>
       </c>
       <c r="F246" t="n">
-        <v>218.4675999207323</v>
+        <v>216.1171047308789</v>
       </c>
       <c r="G246" t="n">
-        <v>217.5721893310547</v>
+        <v>217.5303649902344</v>
       </c>
       <c r="H246" t="n">
-        <v>209.7288892530979</v>
+        <v>213.9276478590663</v>
       </c>
       <c r="I246" t="n">
-        <v>216.9046001522168</v>
+        <v>218.5783454541057</v>
       </c>
       <c r="J246" t="n">
-        <v>222.2423095703125</v>
+        <v>222.2720336914062</v>
       </c>
       <c r="K246" t="n">
-        <v>225.5865936279297</v>
+        <v>225.4932098388672</v>
       </c>
       <c r="L246" t="n">
-        <v>212.4837815472026</v>
+        <v>210.7291296735013</v>
       </c>
       <c r="M246" t="n">
-        <v>212.4837815472026</v>
+        <v>210.7291296735013</v>
       </c>
     </row>
     <row r="247">
@@ -10545,40 +10545,40 @@
         <v>219.555</v>
       </c>
       <c r="B247" t="n">
-        <v>222.3991241455078</v>
+        <v>222.3860473632812</v>
       </c>
       <c r="C247" t="n">
-        <v>221.7957305908203</v>
+        <v>221.8556823730469</v>
       </c>
       <c r="D247" t="n">
-        <v>217.0702324998844</v>
+        <v>217.0727637028469</v>
       </c>
       <c r="E247" t="n">
-        <v>227.068470954895</v>
+        <v>227.0722746245218</v>
       </c>
       <c r="F247" t="n">
-        <v>218.0732347669249</v>
+        <v>216.2222764670553</v>
       </c>
       <c r="G247" t="n">
-        <v>216.7387542724609</v>
+        <v>216.7066955566406</v>
       </c>
       <c r="H247" t="n">
-        <v>209.2390946497477</v>
+        <v>213.9369229097988</v>
       </c>
       <c r="I247" t="n">
-        <v>217.4149946253544</v>
+        <v>219.5686716151622</v>
       </c>
       <c r="J247" t="n">
-        <v>222.3155822753906</v>
+        <v>222.3248596191406</v>
       </c>
       <c r="K247" t="n">
-        <v>226.0968322753906</v>
+        <v>226.0180816650391</v>
       </c>
       <c r="L247" t="n">
-        <v>213.8285817782875</v>
+        <v>212.2169500045904</v>
       </c>
       <c r="M247" t="n">
-        <v>213.8285817782875</v>
+        <v>212.2169500045904</v>
       </c>
     </row>
     <row r="248">
@@ -10586,40 +10586,40 @@
         <v>222.25</v>
       </c>
       <c r="B248" t="n">
-        <v>222.341552734375</v>
+        <v>222.385009765625</v>
       </c>
       <c r="C248" t="n">
-        <v>222.3705291748047</v>
+        <v>222.3694305419922</v>
       </c>
       <c r="D248" t="n">
-        <v>217.7108240971766</v>
+        <v>217.7086294903528</v>
       </c>
       <c r="E248" t="n">
-        <v>228.1597530841827</v>
+        <v>228.1580931024797</v>
       </c>
       <c r="F248" t="n">
-        <v>218.4675999207323</v>
+        <v>216.1171047308789</v>
       </c>
       <c r="G248" t="n">
-        <v>217.5540008544922</v>
+        <v>217.5212097167969</v>
       </c>
       <c r="H248" t="n">
-        <v>209.7288892530979</v>
+        <v>213.9276478590663</v>
       </c>
       <c r="I248" t="n">
-        <v>216.9046001522168</v>
+        <v>218.54124141325</v>
       </c>
       <c r="J248" t="n">
-        <v>222.2772674560547</v>
+        <v>222.2809143066406</v>
       </c>
       <c r="K248" t="n">
-        <v>225.9504699707031</v>
+        <v>225.9178009033203</v>
       </c>
       <c r="L248" t="n">
-        <v>212.9661877839191</v>
+        <v>211.593268926305</v>
       </c>
       <c r="M248" t="n">
-        <v>212.9661877839191</v>
+        <v>211.593268926305</v>
       </c>
     </row>
     <row r="249">
@@ -10627,40 +10627,40 @@
         <v>205.475</v>
       </c>
       <c r="B249" t="n">
-        <v>222.5114135742188</v>
+        <v>222.5417938232422</v>
       </c>
       <c r="C249" t="n">
-        <v>225.2598114013672</v>
+        <v>225.2377319335938</v>
       </c>
       <c r="D249" t="n">
-        <v>220.3566024282381</v>
+        <v>220.3547040260162</v>
       </c>
       <c r="E249" t="n">
-        <v>232.3074357509613</v>
+        <v>232.3062793887214</v>
       </c>
       <c r="F249" t="n">
-        <v>221.3753179465309</v>
+        <v>217.0486698681192</v>
       </c>
       <c r="G249" t="n">
-        <v>221.5724487304688</v>
+        <v>221.5012054443359</v>
       </c>
       <c r="H249" t="n">
-        <v>207.2874706448707</v>
+        <v>214.1028774687068</v>
       </c>
       <c r="I249" t="n">
-        <v>219.3533855407258</v>
+        <v>220.8777427928325</v>
       </c>
       <c r="J249" t="n">
-        <v>222.9745635986328</v>
+        <v>222.9902801513672</v>
       </c>
       <c r="K249" t="n">
-        <v>227.0604858398438</v>
+        <v>227.0396575927734</v>
       </c>
       <c r="L249" t="n">
-        <v>215.0673694751407</v>
+        <v>215.217731382564</v>
       </c>
       <c r="M249" t="n">
-        <v>215.0673694751407</v>
+        <v>215.217731382564</v>
       </c>
     </row>
     <row r="250">
@@ -10668,40 +10668,40 @@
         <v>203.56</v>
       </c>
       <c r="B250" t="n">
-        <v>222.3194274902344</v>
+        <v>222.3538208007812</v>
       </c>
       <c r="C250" t="n">
-        <v>222.1995391845703</v>
+        <v>222.1934509277344</v>
       </c>
       <c r="D250" t="n">
-        <v>217.5254631768851</v>
+        <v>217.5293946197843</v>
       </c>
       <c r="E250" t="n">
-        <v>227.8460147380829</v>
+        <v>227.8513618237541</v>
       </c>
       <c r="F250" t="n">
-        <v>218.5352833739171</v>
+        <v>216.1171047308789</v>
       </c>
       <c r="G250" t="n">
-        <v>217.3991851806641</v>
+        <v>217.3596496582031</v>
       </c>
       <c r="H250" t="n">
-        <v>210.008384090856</v>
+        <v>214.0384512296098</v>
       </c>
       <c r="I250" t="n">
-        <v>217.2853559055083</v>
+        <v>218.5691922566684</v>
       </c>
       <c r="J250" t="n">
-        <v>222.5397186279297</v>
+        <v>222.5839996337891</v>
       </c>
       <c r="K250" t="n">
-        <v>226.9762878417969</v>
+        <v>226.91552734375</v>
       </c>
       <c r="L250" t="n">
-        <v>214.3313555615671</v>
+        <v>212.6836801778997</v>
       </c>
       <c r="M250" t="n">
-        <v>214.3313555615671</v>
+        <v>212.6836801778997</v>
       </c>
     </row>
     <row r="251">
@@ -10709,40 +10709,40 @@
         <v>215.79</v>
       </c>
       <c r="B251" t="n">
-        <v>222.2682342529297</v>
+        <v>222.2603759765625</v>
       </c>
       <c r="C251" t="n">
-        <v>220.4304504394531</v>
+        <v>220.4230041503906</v>
       </c>
       <c r="D251" t="n">
-        <v>215.5792937579153</v>
+        <v>215.5953965171877</v>
       </c>
       <c r="E251" t="n">
-        <v>224.3799276351929</v>
+        <v>224.4008280508919</v>
       </c>
       <c r="F251" t="n">
-        <v>216.1730736428754</v>
+        <v>213.7601671479464</v>
       </c>
       <c r="G251" t="n">
-        <v>214.8539276123047</v>
+        <v>214.8319854736328</v>
       </c>
       <c r="H251" t="n">
-        <v>208.3197049556885</v>
+        <v>212.0335316254683</v>
       </c>
       <c r="I251" t="n">
-        <v>216.219962295514</v>
+        <v>216.330367480789</v>
       </c>
       <c r="J251" t="n">
-        <v>221.8681182861328</v>
+        <v>221.8985595703125</v>
       </c>
       <c r="K251" t="n">
-        <v>225.21728515625</v>
+        <v>225.1463928222656</v>
       </c>
       <c r="L251" t="n">
-        <v>211.9804052198384</v>
+        <v>209.4953056194246</v>
       </c>
       <c r="M251" t="n">
-        <v>211.9804052198384</v>
+        <v>209.4953056194246</v>
       </c>
     </row>
     <row r="252">
@@ -10750,40 +10750,40 @@
         <v>213.475</v>
       </c>
       <c r="B252" t="n">
-        <v>222.25390625</v>
+        <v>222.2212829589844</v>
       </c>
       <c r="C252" t="n">
-        <v>220.1458129882812</v>
+        <v>220.1148681640625</v>
       </c>
       <c r="D252" t="n">
-        <v>215.2290234987157</v>
+        <v>215.2279329272265</v>
       </c>
       <c r="E252" t="n">
-        <v>223.7056193351746</v>
+        <v>223.7050804268522</v>
       </c>
       <c r="F252" t="n">
-        <v>216.2714284592546</v>
+        <v>214.2549857687422</v>
       </c>
       <c r="G252" t="n">
-        <v>214.4071655273438</v>
+        <v>214.3831939697266</v>
       </c>
       <c r="H252" t="n">
-        <v>208.0513018003998</v>
+        <v>212.6634762745584</v>
       </c>
       <c r="I252" t="n">
-        <v>214.7817891925796</v>
+        <v>214.3322430864783</v>
       </c>
       <c r="J252" t="n">
-        <v>221.5661468505859</v>
+        <v>221.6203002929688</v>
       </c>
       <c r="K252" t="n">
-        <v>224.3103790283203</v>
+        <v>224.3204040527344</v>
       </c>
       <c r="L252" t="n">
-        <v>210.3563204963501</v>
+        <v>208.5857548974161</v>
       </c>
       <c r="M252" t="n">
-        <v>210.3563204963501</v>
+        <v>208.5857548974161</v>
       </c>
     </row>
     <row r="253">
@@ -10791,40 +10791,40 @@
         <v>218.55</v>
       </c>
       <c r="B253" t="n">
-        <v>225.2806091308594</v>
+        <v>225.3141326904297</v>
       </c>
       <c r="C253" t="n">
-        <v>226.6608123779297</v>
+        <v>226.6961822509766</v>
       </c>
       <c r="D253" t="n">
-        <v>217.527387355712</v>
+        <v>217.4974302993733</v>
       </c>
       <c r="E253" t="n">
-        <v>231.3085775375366</v>
+        <v>231.2673251325633</v>
       </c>
       <c r="F253" t="n">
-        <v>219.1755768231093</v>
+        <v>220.988261609265</v>
       </c>
       <c r="G253" t="n">
-        <v>214.3563842773438</v>
+        <v>214.244873046875</v>
       </c>
       <c r="H253" t="n">
-        <v>212.2806187334258</v>
+        <v>213.2683856500483</v>
       </c>
       <c r="I253" t="n">
-        <v>217.74590648457</v>
+        <v>217.2037002572562</v>
       </c>
       <c r="J253" t="n">
-        <v>223.2608947753906</v>
+        <v>223.2705078125</v>
       </c>
       <c r="K253" t="n">
-        <v>226.5758514404297</v>
+        <v>226.5009918212891</v>
       </c>
       <c r="L253" t="n">
-        <v>214.8442360321463</v>
+        <v>212.8152681701193</v>
       </c>
       <c r="M253" t="n">
-        <v>214.8442360321463</v>
+        <v>212.8152681701193</v>
       </c>
     </row>
     <row r="254">
@@ -10832,40 +10832,40 @@
         <v>217.99</v>
       </c>
       <c r="B254" t="n">
-        <v>225.1754760742188</v>
+        <v>225.2563171386719</v>
       </c>
       <c r="C254" t="n">
-        <v>225.7109680175781</v>
+        <v>225.6918334960938</v>
       </c>
       <c r="D254" t="n">
-        <v>216.3801658477653</v>
+        <v>216.3874363243598</v>
       </c>
       <c r="E254" t="n">
-        <v>228.7954170703888</v>
+        <v>228.8068704296151</v>
       </c>
       <c r="F254" t="n">
-        <v>218.3136442003547</v>
+        <v>221.2981811368331</v>
       </c>
       <c r="G254" t="n">
-        <v>213.0751953125</v>
+        <v>213.1349639892578</v>
       </c>
       <c r="H254" t="n">
-        <v>213.5821917751313</v>
+        <v>211.9957996865616</v>
       </c>
       <c r="I254" t="n">
-        <v>219.9202900804893</v>
+        <v>217.9348891730075</v>
       </c>
       <c r="J254" t="n">
-        <v>224.1864013671875</v>
+        <v>224.2343139648438</v>
       </c>
       <c r="K254" t="n">
-        <v>227.5337829589844</v>
+        <v>227.5044097900391</v>
       </c>
       <c r="L254" t="n">
-        <v>215.3084266760152</v>
+        <v>213.0970016586224</v>
       </c>
       <c r="M254" t="n">
-        <v>215.3084266760152</v>
+        <v>213.0970016586224</v>
       </c>
     </row>
     <row r="255">
@@ -10873,40 +10873,40 @@
         <v>212.355</v>
       </c>
       <c r="B255" t="n">
-        <v>225.4913330078125</v>
+        <v>225.5171508789062</v>
       </c>
       <c r="C255" t="n">
-        <v>227.5148010253906</v>
+        <v>227.5148468017578</v>
       </c>
       <c r="D255" t="n">
-        <v>218.4083147612257</v>
+        <v>218.4110075303348</v>
       </c>
       <c r="E255" t="n">
-        <v>233.1772556304932</v>
+        <v>233.1817563373275</v>
       </c>
       <c r="F255" t="n">
-        <v>221.4183210734641</v>
+        <v>223.8755413438178</v>
       </c>
       <c r="G255" t="n">
-        <v>215.450439453125</v>
+        <v>215.4519653320312</v>
       </c>
       <c r="H255" t="n">
-        <v>214.0678836678522</v>
+        <v>214.1218339018981</v>
       </c>
       <c r="I255" t="n">
-        <v>221.3858800004264</v>
+        <v>220.5913108471235</v>
       </c>
       <c r="J255" t="n">
-        <v>224.6066589355469</v>
+        <v>224.5917205810547</v>
       </c>
       <c r="K255" t="n">
-        <v>227.6933746337891</v>
+        <v>227.6285095214844</v>
       </c>
       <c r="L255" t="n">
-        <v>216.9956989303473</v>
+        <v>214.4999281494289</v>
       </c>
       <c r="M255" t="n">
-        <v>216.9956989303473</v>
+        <v>214.4999281494289</v>
       </c>
     </row>
     <row r="256">
@@ -10914,40 +10914,40 @@
         <v>215.54</v>
       </c>
       <c r="B256" t="n">
-        <v>225.4301910400391</v>
+        <v>225.429443359375</v>
       </c>
       <c r="C256" t="n">
-        <v>228.1584777832031</v>
+        <v>228.1854095458984</v>
       </c>
       <c r="D256" t="n">
-        <v>219.0668018158156</v>
+        <v>219.070787114097</v>
       </c>
       <c r="E256" t="n">
-        <v>234.5534210205078</v>
+        <v>234.5595501146208</v>
       </c>
       <c r="F256" t="n">
-        <v>221.8873756897527</v>
+        <v>223.9650397877154</v>
       </c>
       <c r="G256" t="n">
-        <v>216.2169189453125</v>
+        <v>216.2112121582031</v>
       </c>
       <c r="H256" t="n">
-        <v>213.7062323171135</v>
+        <v>215.9893768103568</v>
       </c>
       <c r="I256" t="n">
-        <v>219.818533159074</v>
+        <v>219.3008817328225</v>
       </c>
       <c r="J256" t="n">
-        <v>224.9183502197266</v>
+        <v>224.8804626464844</v>
       </c>
       <c r="K256" t="n">
-        <v>228.533935546875</v>
+        <v>228.5750732421875</v>
       </c>
       <c r="L256" t="n">
-        <v>216.7855298932611</v>
+        <v>216.5443546967184</v>
       </c>
       <c r="M256" t="n">
-        <v>216.7855298932611</v>
+        <v>216.5443546967184</v>
       </c>
     </row>
     <row r="257">
@@ -10955,40 +10955,40 @@
         <v>222.775</v>
       </c>
       <c r="B257" t="n">
-        <v>225.3227386474609</v>
+        <v>225.3806762695312</v>
       </c>
       <c r="C257" t="n">
-        <v>227.0536804199219</v>
+        <v>227.0479125976562</v>
       </c>
       <c r="D257" t="n">
-        <v>217.8581599599941</v>
+        <v>217.8457193667101</v>
       </c>
       <c r="E257" t="n">
-        <v>232.0154964923859</v>
+        <v>231.9990601516184</v>
       </c>
       <c r="F257" t="n">
-        <v>221.0526609380138</v>
+        <v>221.497050308451</v>
       </c>
       <c r="G257" t="n">
-        <v>214.6989440917969</v>
+        <v>214.6634674072266</v>
       </c>
       <c r="H257" t="n">
-        <v>212.3186289525577</v>
+        <v>213.2795888249886</v>
       </c>
       <c r="I257" t="n">
-        <v>222.2480300887707</v>
+        <v>221.4672845861631</v>
       </c>
       <c r="J257" t="n">
-        <v>224.7313842773438</v>
+        <v>224.6982421875</v>
       </c>
       <c r="K257" t="n">
-        <v>228.7364959716797</v>
+        <v>228.7198181152344</v>
       </c>
       <c r="L257" t="n">
-        <v>216.0580311418987</v>
+        <v>214.1683607980215</v>
       </c>
       <c r="M257" t="n">
-        <v>216.0580311418987</v>
+        <v>214.1683607980215</v>
       </c>
     </row>
     <row r="258">
@@ -10996,40 +10996,40 @@
         <v>214.195</v>
       </c>
       <c r="B258" t="n">
-        <v>225.3013763427734</v>
+        <v>225.3100738525391</v>
       </c>
       <c r="C258" t="n">
-        <v>226.1414947509766</v>
+        <v>226.0863494873047</v>
       </c>
       <c r="D258" t="n">
-        <v>216.8417610561057</v>
+        <v>216.861862577505</v>
       </c>
       <c r="E258" t="n">
-        <v>229.8121299743652</v>
+        <v>229.8418893814123</v>
       </c>
       <c r="F258" t="n">
-        <v>218.3874759010824</v>
+        <v>221.1611459490522</v>
       </c>
       <c r="G258" t="n">
-        <v>213.5644378662109</v>
+        <v>213.6079711914062</v>
       </c>
       <c r="H258" t="n">
-        <v>213.605072102052</v>
+        <v>212.8711489887174</v>
       </c>
       <c r="I258" t="n">
-        <v>221.2652765098176</v>
+        <v>220.5079599549361</v>
       </c>
       <c r="J258" t="n">
-        <v>224.3532104492188</v>
+        <v>224.3593902587891</v>
       </c>
       <c r="K258" t="n">
-        <v>227.9393463134766</v>
+        <v>227.8417358398438</v>
       </c>
       <c r="L258" t="n">
-        <v>215.8249219077741</v>
+        <v>213.6533881330068</v>
       </c>
       <c r="M258" t="n">
-        <v>215.8249219077741</v>
+        <v>213.6533881330068</v>
       </c>
     </row>
     <row r="259">
@@ -11037,40 +11037,40 @@
         <v>211.35</v>
       </c>
       <c r="B259" t="n">
-        <v>225.3059387207031</v>
+        <v>225.3380126953125</v>
       </c>
       <c r="C259" t="n">
-        <v>226.7670440673828</v>
+        <v>226.7653656005859</v>
       </c>
       <c r="D259" t="n">
-        <v>217.5875266316922</v>
+        <v>217.5900443708092</v>
       </c>
       <c r="E259" t="n">
-        <v>231.4498598575592</v>
+        <v>231.454222452123</v>
       </c>
       <c r="F259" t="n">
-        <v>219.1755768231093</v>
+        <v>220.988261609265</v>
       </c>
       <c r="G259" t="n">
-        <v>214.4506225585938</v>
+        <v>214.3735961914062</v>
       </c>
       <c r="H259" t="n">
-        <v>212.884853404728</v>
+        <v>213.5821510375683</v>
       </c>
       <c r="I259" t="n">
-        <v>220.9446705012082</v>
+        <v>219.659229457837</v>
       </c>
       <c r="J259" t="n">
-        <v>224.4197998046875</v>
+        <v>224.4306335449219</v>
       </c>
       <c r="K259" t="n">
-        <v>227.6139984130859</v>
+        <v>227.6363830566406</v>
       </c>
       <c r="L259" t="n">
-        <v>216.9963772147775</v>
+        <v>214.1970539357411</v>
       </c>
       <c r="M259" t="n">
-        <v>216.9963772147775</v>
+        <v>214.1970539357411</v>
       </c>
     </row>
     <row r="260">
@@ -11078,40 +11078,40 @@
         <v>223.325</v>
       </c>
       <c r="B260" t="n">
-        <v>225.4396362304688</v>
+        <v>225.4623565673828</v>
       </c>
       <c r="C260" t="n">
-        <v>228.6058197021484</v>
+        <v>228.6237487792969</v>
       </c>
       <c r="D260" t="n">
-        <v>219.568873357001</v>
+        <v>219.5532956877049</v>
       </c>
       <c r="E260" t="n">
-        <v>235.5853183269501</v>
+        <v>235.5658946759669</v>
       </c>
       <c r="F260" t="n">
-        <v>222.5645000808374</v>
+        <v>224.8932565718697</v>
       </c>
       <c r="G260" t="n">
-        <v>216.8339080810547</v>
+        <v>216.8419342041016</v>
       </c>
       <c r="H260" t="n">
-        <v>214.5860235228657</v>
+        <v>215.8071413173538</v>
       </c>
       <c r="I260" t="n">
-        <v>220.761339092297</v>
+        <v>220.2195506756684</v>
       </c>
       <c r="J260" t="n">
-        <v>224.9615478515625</v>
+        <v>224.9674530029297</v>
       </c>
       <c r="K260" t="n">
-        <v>228.4554901123047</v>
+        <v>228.4446411132812</v>
       </c>
       <c r="L260" t="n">
-        <v>217.7093105865816</v>
+        <v>215.8131604851658</v>
       </c>
       <c r="M260" t="n">
-        <v>217.7093105865816</v>
+        <v>215.8131604851658</v>
       </c>
     </row>
     <row r="261">
@@ -11119,40 +11119,40 @@
         <v>222.665</v>
       </c>
       <c r="B261" t="n">
-        <v>225.3008575439453</v>
+        <v>225.3424224853516</v>
       </c>
       <c r="C261" t="n">
-        <v>226.7416229248047</v>
+        <v>226.7181549072266</v>
       </c>
       <c r="D261" t="n">
-        <v>217.5766497055271</v>
+        <v>217.5445922892834</v>
       </c>
       <c r="E261" t="n">
-        <v>231.4061944484711</v>
+        <v>231.3620511492039</v>
       </c>
       <c r="F261" t="n">
-        <v>219.1755768231093</v>
+        <v>220.988261609265</v>
       </c>
       <c r="G261" t="n">
-        <v>214.3356475830078</v>
+        <v>214.2875061035156</v>
       </c>
       <c r="H261" t="n">
-        <v>212.7964391611544</v>
+        <v>213.5821510375683</v>
       </c>
       <c r="I261" t="n">
-        <v>222.2480300887707</v>
+        <v>221.4901487291818</v>
       </c>
       <c r="J261" t="n">
-        <v>224.6302185058594</v>
+        <v>224.6583404541016</v>
       </c>
       <c r="K261" t="n">
-        <v>228.8272552490234</v>
+        <v>228.8384704589844</v>
       </c>
       <c r="L261" t="n">
-        <v>216.4085349563443</v>
+        <v>214.5398954544944</v>
       </c>
       <c r="M261" t="n">
-        <v>216.4085349563443</v>
+        <v>214.5398954544944</v>
       </c>
     </row>
     <row r="262">
@@ -11160,40 +11160,40 @@
         <v>225.2</v>
       </c>
       <c r="B262" t="n">
-        <v>225.3592987060547</v>
+        <v>225.3582763671875</v>
       </c>
       <c r="C262" t="n">
-        <v>226.4379119873047</v>
+        <v>226.4904327392578</v>
       </c>
       <c r="D262" t="n">
-        <v>217.2657074846977</v>
+        <v>217.266057544682</v>
       </c>
       <c r="E262" t="n">
-        <v>230.7481050491333</v>
+        <v>230.7494306785578</v>
       </c>
       <c r="F262" t="n">
-        <v>219.1755768231093</v>
+        <v>221.1611459490522</v>
       </c>
       <c r="G262" t="n">
-        <v>213.9865417480469</v>
+        <v>214.0492858886719</v>
       </c>
       <c r="H262" t="n">
-        <v>213.4346639644976</v>
+        <v>213.0926684877802</v>
       </c>
       <c r="I262" t="n">
-        <v>221.3700986029888</v>
+        <v>220.7972192706105</v>
       </c>
       <c r="J262" t="n">
-        <v>224.4170074462891</v>
+        <v>224.4394836425781</v>
       </c>
       <c r="K262" t="n">
-        <v>227.9437866210938</v>
+        <v>227.8730316162109</v>
       </c>
       <c r="L262" t="n">
-        <v>216.5671085930837</v>
+        <v>214.1812437477693</v>
       </c>
       <c r="M262" t="n">
-        <v>216.5671085930837</v>
+        <v>214.1812437477693</v>
       </c>
     </row>
     <row r="263">
@@ -11201,40 +11201,40 @@
         <v>223.595</v>
       </c>
       <c r="B263" t="n">
-        <v>225.1365509033203</v>
+        <v>225.1588134765625</v>
       </c>
       <c r="C263" t="n">
-        <v>224.5069885253906</v>
+        <v>224.4456329345703</v>
       </c>
       <c r="D263" t="n">
-        <v>215.0496009897911</v>
+        <v>215.0322057013464</v>
       </c>
       <c r="E263" t="n">
-        <v>225.6890571117401</v>
+        <v>225.6633261095535</v>
       </c>
       <c r="F263" t="n">
-        <v>217.1364808901994</v>
+        <v>220.049196574601</v>
       </c>
       <c r="G263" t="n">
-        <v>211.8550415039062</v>
+        <v>211.8727111816406</v>
       </c>
       <c r="H263" t="n">
-        <v>214.1608986489687</v>
+        <v>211.7655748834138</v>
       </c>
       <c r="I263" t="n">
-        <v>219.8990713718291</v>
+        <v>219.6273100985846</v>
       </c>
       <c r="J263" t="n">
-        <v>223.9117736816406</v>
+        <v>223.9559936523438</v>
       </c>
       <c r="K263" t="n">
-        <v>227.1733551025391</v>
+        <v>227.1204376220703</v>
       </c>
       <c r="L263" t="n">
-        <v>215.5865076901059</v>
+        <v>212.9129073284452</v>
       </c>
       <c r="M263" t="n">
-        <v>215.5865076901059</v>
+        <v>212.9129073284452</v>
       </c>
     </row>
     <row r="264">
@@ -11242,40 +11242,40 @@
         <v>228.425</v>
       </c>
       <c r="B264" t="n">
-        <v>225.8903198242188</v>
+        <v>225.8877410888672</v>
       </c>
       <c r="C264" t="n">
-        <v>231.08935546875</v>
+        <v>231.0555419921875</v>
       </c>
       <c r="D264" t="n">
-        <v>222.2723295357409</v>
+        <v>222.3012229482814</v>
       </c>
       <c r="E264" t="n">
-        <v>240.618955373764</v>
+        <v>240.6535084757369</v>
       </c>
       <c r="F264" t="n">
-        <v>225.6421461685404</v>
+        <v>225.7196499729337</v>
       </c>
       <c r="G264" t="n">
-        <v>219.9173736572266</v>
+        <v>219.8449859619141</v>
       </c>
       <c r="H264" t="n">
-        <v>217.4589133471515</v>
+        <v>218.5936849128418</v>
       </c>
       <c r="I264" t="n">
-        <v>222.5757014009468</v>
+        <v>221.809909287133</v>
       </c>
       <c r="J264" t="n">
-        <v>225.3472442626953</v>
+        <v>225.3812866210938</v>
       </c>
       <c r="K264" t="n">
-        <v>228.4321746826172</v>
+        <v>228.4219818115234</v>
       </c>
       <c r="L264" t="n">
-        <v>219.7891332304798</v>
+        <v>217.8845171318661</v>
       </c>
       <c r="M264" t="n">
-        <v>219.7891332304798</v>
+        <v>217.8845171318661</v>
       </c>
     </row>
     <row r="265">
@@ -11283,40 +11283,40 @@
         <v>225.54</v>
       </c>
       <c r="B265" t="n">
-        <v>225.894775390625</v>
+        <v>225.8716735839844</v>
       </c>
       <c r="C265" t="n">
-        <v>235.0504150390625</v>
+        <v>235.0638580322266</v>
       </c>
       <c r="D265" t="n">
-        <v>225.1685220035625</v>
+        <v>225.1887985549539</v>
       </c>
       <c r="E265" t="n">
-        <v>244.3745820522308</v>
+        <v>244.3990913260843</v>
       </c>
       <c r="F265" t="n">
-        <v>226.8517970444561</v>
+        <v>226.9476128880331</v>
       </c>
       <c r="G265" t="n">
-        <v>225.1385345458984</v>
+        <v>225.0531005859375</v>
       </c>
       <c r="H265" t="n">
-        <v>217.7713374142553</v>
+        <v>217.3359953083459</v>
       </c>
       <c r="I265" t="n">
-        <v>226.6521538063624</v>
+        <v>226.1838063769983</v>
       </c>
       <c r="J265" t="n">
-        <v>226.6507415771484</v>
+        <v>226.6163024902344</v>
       </c>
       <c r="K265" t="n">
-        <v>232.5102233886719</v>
+        <v>232.5669708251953</v>
       </c>
       <c r="L265" t="n">
-        <v>221.841151324518</v>
+        <v>222.0091994559469</v>
       </c>
       <c r="M265" t="n">
-        <v>221.841151324518</v>
+        <v>222.0091994559469</v>
       </c>
     </row>
     <row r="266">
@@ -11324,40 +11324,40 @@
         <v>225.785</v>
       </c>
       <c r="B266" t="n">
-        <v>225.8744659423828</v>
+        <v>225.8909606933594</v>
       </c>
       <c r="C266" t="n">
-        <v>234.8845062255859</v>
+        <v>234.8843383789062</v>
       </c>
       <c r="D266" t="n">
-        <v>225.0206205222597</v>
+        <v>225.0248212420699</v>
       </c>
       <c r="E266" t="n">
-        <v>244.1899898052216</v>
+        <v>244.1957306431625</v>
       </c>
       <c r="F266" t="n">
-        <v>226.6738158507083</v>
+        <v>226.9476128880331</v>
       </c>
       <c r="G266" t="n">
-        <v>224.9312133789062</v>
+        <v>224.9198608398438</v>
       </c>
       <c r="H266" t="n">
-        <v>217.8134752276771</v>
+        <v>217.2290291868506</v>
       </c>
       <c r="I266" t="n">
-        <v>228.6515604501714</v>
+        <v>227.070793683155</v>
       </c>
       <c r="J266" t="n">
-        <v>226.9257659912109</v>
+        <v>226.9579467773438</v>
       </c>
       <c r="K266" t="n">
-        <v>234.1441650390625</v>
+        <v>234.1463928222656</v>
       </c>
       <c r="L266" t="n">
-        <v>222.1371524858064</v>
+        <v>221.5839955437442</v>
       </c>
       <c r="M266" t="n">
-        <v>222.1371524858064</v>
+        <v>221.5839955437442</v>
       </c>
     </row>
     <row r="267">
@@ -11365,40 +11365,40 @@
         <v>228.41</v>
       </c>
       <c r="B267" t="n">
-        <v>225.8669128417969</v>
+        <v>225.8232116699219</v>
       </c>
       <c r="C267" t="n">
-        <v>232.2936706542969</v>
+        <v>232.2931671142578</v>
       </c>
       <c r="D267" t="n">
-        <v>223.1811945730873</v>
+        <v>223.1909289334166</v>
       </c>
       <c r="E267" t="n">
-        <v>241.8220822811127</v>
+        <v>241.8342509757524</v>
       </c>
       <c r="F267" t="n">
-        <v>226.2338939537761</v>
+        <v>225.7196499729337</v>
       </c>
       <c r="G267" t="n">
-        <v>221.4546966552734</v>
+        <v>221.4268798828125</v>
       </c>
       <c r="H267" t="n">
-        <v>217.7139773220778</v>
+        <v>217.499094266328</v>
       </c>
       <c r="I267" t="n">
-        <v>227.5007564166809</v>
+        <v>226.1988917523204</v>
       </c>
       <c r="J267" t="n">
-        <v>226.5131530761719</v>
+        <v>226.5065612792969</v>
       </c>
       <c r="K267" t="n">
-        <v>233.3046569824219</v>
+        <v>233.2602081298828</v>
       </c>
       <c r="L267" t="n">
-        <v>222.0967378849887</v>
+        <v>221.8918939721746</v>
       </c>
       <c r="M267" t="n">
-        <v>222.0967378849887</v>
+        <v>221.8918939721746</v>
       </c>
     </row>
     <row r="268">
@@ -11406,40 +11406,40 @@
         <v>227.485</v>
       </c>
       <c r="B268" t="n">
-        <v>225.3190612792969</v>
+        <v>225.3536224365234</v>
       </c>
       <c r="C268" t="n">
-        <v>226.1988372802734</v>
+        <v>226.1731567382812</v>
       </c>
       <c r="D268" t="n">
-        <v>216.9243888217502</v>
+        <v>216.9356715243172</v>
       </c>
       <c r="E268" t="n">
-        <v>229.9994492530823</v>
+        <v>230.0164677155322</v>
       </c>
       <c r="F268" t="n">
-        <v>218.3874759010824</v>
+        <v>221.1611459490522</v>
       </c>
       <c r="G268" t="n">
-        <v>213.7118988037109</v>
+        <v>213.6320190429688</v>
       </c>
       <c r="H268" t="n">
-        <v>213.2456607468757</v>
+        <v>212.7938809520423</v>
       </c>
       <c r="I268" t="n">
-        <v>223.9095085326677</v>
+        <v>223.3663971954043</v>
       </c>
       <c r="J268" t="n">
-        <v>224.9176025390625</v>
+        <v>224.92431640625</v>
       </c>
       <c r="K268" t="n">
-        <v>230.3460388183594</v>
+        <v>230.2270660400391</v>
       </c>
       <c r="L268" t="n">
-        <v>217.5852102374901</v>
+        <v>216.2957710806603</v>
       </c>
       <c r="M268" t="n">
-        <v>217.5852102374901</v>
+        <v>216.2957710806603</v>
       </c>
     </row>
     <row r="269">
@@ -11447,40 +11447,40 @@
         <v>223.825</v>
       </c>
       <c r="B269" t="n">
-        <v>225.1754760742188</v>
+        <v>225.2563171386719</v>
       </c>
       <c r="C269" t="n">
-        <v>225.7109680175781</v>
+        <v>225.6918334960938</v>
       </c>
       <c r="D269" t="n">
-        <v>216.3729857504863</v>
+        <v>216.3802562270808</v>
       </c>
       <c r="E269" t="n">
-        <v>228.7748873233795</v>
+        <v>228.7863398430682</v>
       </c>
       <c r="F269" t="n">
-        <v>218.3136442003547</v>
+        <v>221.2981811368331</v>
       </c>
       <c r="G269" t="n">
-        <v>213.0751953125</v>
+        <v>213.1349639892578</v>
       </c>
       <c r="H269" t="n">
-        <v>213.5821917751313</v>
+        <v>211.8710413050158</v>
       </c>
       <c r="I269" t="n">
-        <v>221.0921245487771</v>
+        <v>219.5990929418357</v>
       </c>
       <c r="J269" t="n">
-        <v>224.2655487060547</v>
+        <v>224.3048706054688</v>
       </c>
       <c r="K269" t="n">
-        <v>227.5936431884766</v>
+        <v>227.5447082519531</v>
       </c>
       <c r="L269" t="n">
-        <v>215.7365058351653</v>
+        <v>213.0236405308589</v>
       </c>
       <c r="M269" t="n">
-        <v>215.7365058351653</v>
+        <v>213.0236405308589</v>
       </c>
     </row>
     <row r="270">
@@ -11488,40 +11488,40 @@
         <v>222.835</v>
       </c>
       <c r="B270" t="n">
-        <v>225.3465270996094</v>
+        <v>225.3585357666016</v>
       </c>
       <c r="C270" t="n">
-        <v>226.2294616699219</v>
+        <v>226.1902313232422</v>
       </c>
       <c r="D270" t="n">
-        <v>217.0029293069877</v>
+        <v>216.9750995382453</v>
       </c>
       <c r="E270" t="n">
-        <v>230.1608111858368</v>
+        <v>230.1218097993475</v>
       </c>
       <c r="F270" t="n">
-        <v>218.8393619691569</v>
+        <v>221.1611459490522</v>
       </c>
       <c r="G270" t="n">
-        <v>213.7928314208984</v>
+        <v>213.7090759277344</v>
       </c>
       <c r="H270" t="n">
-        <v>213.5351754259037</v>
+        <v>212.7938809520423</v>
       </c>
       <c r="I270" t="n">
-        <v>221.3764533858301</v>
+        <v>220.4451454357178</v>
       </c>
       <c r="J270" t="n">
-        <v>224.3522033691406</v>
+        <v>224.2737884521484</v>
       </c>
       <c r="K270" t="n">
-        <v>227.3888549804688</v>
+        <v>227.4673156738281</v>
       </c>
       <c r="L270" t="n">
-        <v>216.1988148029567</v>
+        <v>213.6058180734674</v>
       </c>
       <c r="M270" t="n">
-        <v>216.1988148029567</v>
+        <v>213.6058180734674</v>
       </c>
     </row>
     <row r="271">
@@ -11529,40 +11529,40 @@
         <v>224.56</v>
       </c>
       <c r="B271" t="n">
-        <v>225.3035583496094</v>
+        <v>225.3363189697266</v>
       </c>
       <c r="C271" t="n">
-        <v>226.2581939697266</v>
+        <v>226.2403411865234</v>
       </c>
       <c r="D271" t="n">
-        <v>217.0235944488644</v>
+        <v>217.0403434727229</v>
       </c>
       <c r="E271" t="n">
-        <v>230.2195782661438</v>
+        <v>230.2443448775543</v>
       </c>
       <c r="F271" t="n">
-        <v>218.8393619691569</v>
+        <v>221.1611459490522</v>
       </c>
       <c r="G271" t="n">
-        <v>213.8429260253906</v>
+        <v>213.7739410400391</v>
       </c>
       <c r="H271" t="n">
-        <v>213.4753007024523</v>
+        <v>212.9501469177744</v>
       </c>
       <c r="I271" t="n">
-        <v>221.3764533858301</v>
+        <v>220.7344047513922</v>
       </c>
       <c r="J271" t="n">
-        <v>224.3025360107422</v>
+        <v>224.3448333740234</v>
       </c>
       <c r="K271" t="n">
-        <v>227.5872802734375</v>
+        <v>227.6041564941406</v>
       </c>
       <c r="L271" t="n">
-        <v>216.1906739175896</v>
+        <v>213.6794082935584</v>
       </c>
       <c r="M271" t="n">
-        <v>216.1906739175896</v>
+        <v>213.6794082935584</v>
       </c>
     </row>
     <row r="272">
@@ -11570,40 +11570,40 @@
         <v>225.46</v>
       </c>
       <c r="B272" t="n">
-        <v>225.3134613037109</v>
+        <v>225.3081665039062</v>
       </c>
       <c r="C272" t="n">
-        <v>225.9383392333984</v>
+        <v>225.9476928710938</v>
       </c>
       <c r="D272" t="n">
-        <v>216.6534515536396</v>
+        <v>216.656521310424</v>
       </c>
       <c r="E272" t="n">
-        <v>229.3923602104187</v>
+        <v>229.3976410116397</v>
       </c>
       <c r="F272" t="n">
-        <v>218.3136442003547</v>
+        <v>221.2981811368331</v>
       </c>
       <c r="G272" t="n">
-        <v>213.4273376464844</v>
+        <v>213.3860778808594</v>
       </c>
       <c r="H272" t="n">
-        <v>213.5384667735883</v>
+        <v>211.6891902721572</v>
       </c>
       <c r="I272" t="n">
-        <v>220.6983719005509</v>
+        <v>220.4451454357178</v>
       </c>
       <c r="J272" t="n">
-        <v>224.2758636474609</v>
+        <v>224.2985534667969</v>
       </c>
       <c r="K272" t="n">
-        <v>227.6279144287109</v>
+        <v>227.6555633544922</v>
       </c>
       <c r="L272" t="n">
-        <v>215.9445867668754</v>
+        <v>213.1824223562674</v>
       </c>
       <c r="M272" t="n">
-        <v>215.9445867668754</v>
+        <v>213.1824223562674</v>
       </c>
     </row>
     <row r="273">
@@ -11611,40 +11611,40 @@
         <v>219.84</v>
       </c>
       <c r="B273" t="n">
-        <v>225.2118530273438</v>
+        <v>225.3140106201172</v>
       </c>
       <c r="C273" t="n">
-        <v>225.6002807617188</v>
+        <v>225.5791778564453</v>
       </c>
       <c r="D273" t="n">
-        <v>216.2848570006526</v>
+        <v>216.2971225639446</v>
       </c>
       <c r="E273" t="n">
-        <v>228.5552804470062</v>
+        <v>228.5741027902469</v>
       </c>
       <c r="F273" t="n">
-        <v>218.7543792671181</v>
+        <v>223.0073142409902</v>
       </c>
       <c r="G273" t="n">
-        <v>213.0508728027344</v>
+        <v>213.0807952880859</v>
       </c>
       <c r="H273" t="n">
-        <v>213.5499373503526</v>
+        <v>211.7315008065735</v>
       </c>
       <c r="I273" t="n">
-        <v>221.0397404765074</v>
+        <v>219.7284271266413</v>
       </c>
       <c r="J273" t="n">
-        <v>224.1344146728516</v>
+        <v>224.2046508789062</v>
       </c>
       <c r="K273" t="n">
-        <v>227.3473052978516</v>
+        <v>227.4597625732422</v>
       </c>
       <c r="L273" t="n">
-        <v>216.0567515686165</v>
+        <v>212.9670584755222</v>
       </c>
       <c r="M273" t="n">
-        <v>216.0567515686165</v>
+        <v>212.9670584755222</v>
       </c>
     </row>
     <row r="274">
@@ -11652,40 +11652,40 @@
         <v>229.025</v>
       </c>
       <c r="B274" t="n">
-        <v>225.8621673583984</v>
+        <v>225.8878784179688</v>
       </c>
       <c r="C274" t="n">
-        <v>231.1444091796875</v>
+        <v>231.1606292724609</v>
       </c>
       <c r="D274" t="n">
-        <v>222.3660380462692</v>
+        <v>222.3745202689628</v>
       </c>
       <c r="E274" t="n">
-        <v>240.7787544727325</v>
+        <v>240.7894504489016</v>
       </c>
       <c r="F274" t="n">
-        <v>225.3622728555578</v>
+        <v>225.7196499729337</v>
       </c>
       <c r="G274" t="n">
-        <v>220.0269012451172</v>
+        <v>219.9502258300781</v>
       </c>
       <c r="H274" t="n">
-        <v>217.4978334904301</v>
+        <v>218.1790443365178</v>
       </c>
       <c r="I274" t="n">
-        <v>222.020868023285</v>
+        <v>222.3432178554466</v>
       </c>
       <c r="J274" t="n">
-        <v>225.4259185791016</v>
+        <v>225.4314575195312</v>
       </c>
       <c r="K274" t="n">
-        <v>228.8360748291016</v>
+        <v>228.8812713623047</v>
       </c>
       <c r="L274" t="n">
-        <v>220.0234618321107</v>
+        <v>218.6397593662399</v>
       </c>
       <c r="M274" t="n">
-        <v>220.0234618321107</v>
+        <v>218.6397593662399</v>
       </c>
     </row>
     <row r="275">
@@ -11693,40 +11693,40 @@
         <v>226.445</v>
       </c>
       <c r="B275" t="n">
-        <v>225.8711547851562</v>
+        <v>225.9312744140625</v>
       </c>
       <c r="C275" t="n">
-        <v>233.9893035888672</v>
+        <v>233.9709014892578</v>
       </c>
       <c r="D275" t="n">
-        <v>224.3222914607857</v>
+        <v>224.3231396830551</v>
       </c>
       <c r="E275" t="n">
-        <v>243.2915799617767</v>
+        <v>243.293406798912</v>
       </c>
       <c r="F275" t="n">
-        <v>226.6738158507083</v>
+        <v>226.9476128880331</v>
       </c>
       <c r="G275" t="n">
-        <v>223.5236511230469</v>
+        <v>223.4709777832031</v>
       </c>
       <c r="H275" t="n">
-        <v>216.9119620762514</v>
+        <v>217.2026090835029</v>
       </c>
       <c r="I275" t="n">
-        <v>225.8707832154134</v>
+        <v>225.6352190867733</v>
       </c>
       <c r="J275" t="n">
-        <v>226.4996795654297</v>
+        <v>226.4991912841797</v>
       </c>
       <c r="K275" t="n">
-        <v>232.2538909912109</v>
+        <v>232.272705078125</v>
       </c>
       <c r="L275" t="n">
-        <v>221.8677463472816</v>
+        <v>221.9167856535838</v>
       </c>
       <c r="M275" t="n">
-        <v>221.8677463472816</v>
+        <v>221.9167856535838</v>
       </c>
     </row>
     <row r="276">
@@ -11734,40 +11734,40 @@
         <v>231.41</v>
       </c>
       <c r="B276" t="n">
-        <v>225.8392028808594</v>
+        <v>225.8672180175781</v>
       </c>
       <c r="C276" t="n">
-        <v>231.4391937255859</v>
+        <v>231.4185638427734</v>
       </c>
       <c r="D276" t="n">
-        <v>222.5286033329173</v>
+        <v>222.5382030547912</v>
       </c>
       <c r="E276" t="n">
-        <v>240.9725472927094</v>
+        <v>240.984556562805</v>
       </c>
       <c r="F276" t="n">
-        <v>225.812256479899</v>
+        <v>225.7196499729337</v>
       </c>
       <c r="G276" t="n">
-        <v>220.2728576660156</v>
+        <v>220.2674560546875</v>
       </c>
       <c r="H276" t="n">
-        <v>217.3302452055586</v>
+        <v>217.9070287416506</v>
       </c>
       <c r="I276" t="n">
-        <v>225.7544641893078</v>
+        <v>224.6340695282394</v>
       </c>
       <c r="J276" t="n">
-        <v>226.2771301269531</v>
+        <v>226.2963104248047</v>
       </c>
       <c r="K276" t="n">
-        <v>232.4769134521484</v>
+        <v>232.4234313964844</v>
       </c>
       <c r="L276" t="n">
-        <v>222.0657575314347</v>
+        <v>221.7953986888273</v>
       </c>
       <c r="M276" t="n">
-        <v>222.0657575314347</v>
+        <v>221.7953986888273</v>
       </c>
     </row>
     <row r="277">
@@ -11775,40 +11775,40 @@
         <v>235.315</v>
       </c>
       <c r="B277" t="n">
-        <v>225.4361267089844</v>
+        <v>225.45849609375</v>
       </c>
       <c r="C277" t="n">
-        <v>227.5712890625</v>
+        <v>227.5854797363281</v>
       </c>
       <c r="D277" t="n">
-        <v>218.4724220040385</v>
+        <v>218.4985687920877</v>
       </c>
       <c r="E277" t="n">
-        <v>233.309757232666</v>
+        <v>233.3461017008447</v>
       </c>
       <c r="F277" t="n">
-        <v>221.4183210734641</v>
+        <v>223.8755413438178</v>
       </c>
       <c r="G277" t="n">
-        <v>215.5324096679688</v>
+        <v>215.493408203125</v>
       </c>
       <c r="H277" t="n">
-        <v>214.0678836678522</v>
+        <v>214.3935795627793</v>
       </c>
       <c r="I277" t="n">
-        <v>223.9523373098332</v>
+        <v>224.0979083986286</v>
       </c>
       <c r="J277" t="n">
-        <v>225.2185211181641</v>
+        <v>225.2199554443359</v>
       </c>
       <c r="K277" t="n">
-        <v>230.4111633300781</v>
+        <v>230.3513793945312</v>
       </c>
       <c r="L277" t="n">
-        <v>218.5571355569103</v>
+        <v>216.8216333670095</v>
       </c>
       <c r="M277" t="n">
-        <v>218.5571355569103</v>
+        <v>216.8216333670095</v>
       </c>
     </row>
     <row r="278">
@@ -11816,40 +11816,40 @@
         <v>231.43</v>
       </c>
       <c r="B278" t="n">
-        <v>225.4378356933594</v>
+        <v>225.5018310546875</v>
       </c>
       <c r="C278" t="n">
-        <v>227.7474060058594</v>
+        <v>227.7582702636719</v>
       </c>
       <c r="D278" t="n">
-        <v>218.6599736635507</v>
+        <v>218.6786749450133</v>
       </c>
       <c r="E278" t="n">
-        <v>233.6897468566895</v>
+        <v>233.7158187941453</v>
       </c>
       <c r="F278" t="n">
-        <v>221.8478977320351</v>
+        <v>223.8755413438178</v>
       </c>
       <c r="G278" t="n">
-        <v>215.6128540039062</v>
+        <v>215.6961364746094</v>
       </c>
       <c r="H278" t="n">
-        <v>213.9822141087977</v>
+        <v>215.143716098362</v>
       </c>
       <c r="I278" t="n">
-        <v>221.7614609581921</v>
+        <v>221.7180082090082</v>
       </c>
       <c r="J278" t="n">
-        <v>224.8163299560547</v>
+        <v>224.8572387695312</v>
       </c>
       <c r="K278" t="n">
-        <v>228.9582214355469</v>
+        <v>228.8843383789062</v>
       </c>
       <c r="L278" t="n">
-        <v>216.51055900356</v>
+        <v>214.9224132113385</v>
       </c>
       <c r="M278" t="n">
-        <v>216.51055900356</v>
+        <v>214.9224132113385</v>
       </c>
     </row>
     <row r="279">
@@ -11857,40 +11857,40 @@
         <v>227.845</v>
       </c>
       <c r="B279" t="n">
-        <v>225.50634765625</v>
+        <v>225.4845886230469</v>
       </c>
       <c r="C279" t="n">
-        <v>228.9663848876953</v>
+        <v>229.0084533691406</v>
       </c>
       <c r="D279" t="n">
-        <v>219.9613931635222</v>
+        <v>219.9665767440572</v>
       </c>
       <c r="E279" t="n">
-        <v>236.3455038070679</v>
+        <v>236.3529940730244</v>
       </c>
       <c r="F279" t="n">
-        <v>223.2033727998023</v>
+        <v>224.7880848356934</v>
       </c>
       <c r="G279" t="n">
-        <v>217.2812347412109</v>
+        <v>217.2977600097656</v>
       </c>
       <c r="H279" t="n">
-        <v>213.6934985017954</v>
+        <v>215.7721048103445</v>
       </c>
       <c r="I279" t="n">
-        <v>221.5046444576609</v>
+        <v>221.6199742274985</v>
       </c>
       <c r="J279" t="n">
-        <v>225.1858215332031</v>
+        <v>225.1492614746094</v>
       </c>
       <c r="K279" t="n">
-        <v>229.378173828125</v>
+        <v>229.3443908691406</v>
       </c>
       <c r="L279" t="n">
-        <v>217.9225200916035</v>
+        <v>216.619615587177</v>
       </c>
       <c r="M279" t="n">
-        <v>217.9225200916035</v>
+        <v>216.619615587177</v>
       </c>
     </row>
     <row r="280">
@@ -11898,40 +11898,40 @@
         <v>231.205</v>
       </c>
       <c r="B280" t="n">
-        <v>225.6083984375</v>
+        <v>225.6748657226562</v>
       </c>
       <c r="C280" t="n">
-        <v>230.2178192138672</v>
+        <v>230.1998138427734</v>
       </c>
       <c r="D280" t="n">
-        <v>221.3192184411226</v>
+        <v>221.3160679012649</v>
       </c>
       <c r="E280" t="n">
-        <v>238.9000449180603</v>
+        <v>238.8970464261986</v>
       </c>
       <c r="F280" t="n">
-        <v>224.6695446501374</v>
+        <v>225.4439494136717</v>
       </c>
       <c r="G280" t="n">
-        <v>218.7613372802734</v>
+        <v>218.7615203857422</v>
       </c>
       <c r="H280" t="n">
-        <v>217.8738253081011</v>
+        <v>218.9502651091577</v>
       </c>
       <c r="I280" t="n">
-        <v>222.8047502635254</v>
+        <v>222.6394984222862</v>
       </c>
       <c r="J280" t="n">
-        <v>225.6135559082031</v>
+        <v>225.6189270019531</v>
       </c>
       <c r="K280" t="n">
-        <v>230.0432434082031</v>
+        <v>230.0718688964844</v>
       </c>
       <c r="L280" t="n">
-        <v>220.6584179930582</v>
+        <v>219.8186568747063</v>
       </c>
       <c r="M280" t="n">
-        <v>220.6584179930582</v>
+        <v>219.8186568747063</v>
       </c>
     </row>
     <row r="281">
@@ -11939,40 +11939,40 @@
         <v>231.92</v>
       </c>
       <c r="B281" t="n">
-        <v>225.8026885986328</v>
+        <v>225.8368988037109</v>
       </c>
       <c r="C281" t="n">
-        <v>232.6156158447266</v>
+        <v>232.5637512207031</v>
       </c>
       <c r="D281" t="n">
-        <v>223.3628042411247</v>
+        <v>223.3730502275848</v>
       </c>
       <c r="E281" t="n">
-        <v>242.0555665493011</v>
+        <v>242.0683410939857</v>
       </c>
       <c r="F281" t="n">
-        <v>226.7346187562368</v>
+        <v>226.0974480457594</v>
       </c>
       <c r="G281" t="n">
-        <v>221.6919403076172</v>
+        <v>221.5956420898438</v>
       </c>
       <c r="H281" t="n">
-        <v>217.7139773220778</v>
+        <v>217.494141384708</v>
       </c>
       <c r="I281" t="n">
-        <v>224.7401227036759</v>
+        <v>224.7326348279501</v>
       </c>
       <c r="J281" t="n">
-        <v>226.2001647949219</v>
+        <v>226.1723785400391</v>
       </c>
       <c r="K281" t="n">
-        <v>231.4412841796875</v>
+        <v>231.4264221191406</v>
       </c>
       <c r="L281" t="n">
-        <v>221.5828756643247</v>
+        <v>221.8036066125695</v>
       </c>
       <c r="M281" t="n">
-        <v>221.5828756643247</v>
+        <v>221.8036066125695</v>
       </c>
     </row>
     <row r="282">
@@ -11980,40 +11980,40 @@
         <v>233.105</v>
       </c>
       <c r="B282" t="n">
-        <v>225.7997436523438</v>
+        <v>225.8172760009766</v>
       </c>
       <c r="C282" t="n">
-        <v>232.6308288574219</v>
+        <v>232.6451721191406</v>
       </c>
       <c r="D282" t="n">
-        <v>223.3813556594493</v>
+        <v>223.3882626122141</v>
       </c>
       <c r="E282" t="n">
-        <v>242.0793540477753</v>
+        <v>242.0882317614626</v>
       </c>
       <c r="F282" t="n">
-        <v>226.7346187562368</v>
+        <v>226.0974480457594</v>
       </c>
       <c r="G282" t="n">
-        <v>221.7514801025391</v>
+        <v>221.7169647216797</v>
       </c>
       <c r="H282" t="n">
-        <v>217.7139773220778</v>
+        <v>217.494141384708</v>
       </c>
       <c r="I282" t="n">
-        <v>226.252579332703</v>
+        <v>225.9456627995693</v>
       </c>
       <c r="J282" t="n">
-        <v>226.4094085693359</v>
+        <v>226.4056701660156</v>
       </c>
       <c r="K282" t="n">
-        <v>232.3967742919922</v>
+        <v>232.3971710205078</v>
       </c>
       <c r="L282" t="n">
-        <v>222.3393212362664</v>
+        <v>222.1173413216087</v>
       </c>
       <c r="M282" t="n">
-        <v>222.3393212362664</v>
+        <v>222.1173413216087</v>
       </c>
     </row>
     <row r="283">
@@ -12021,40 +12021,40 @@
         <v>230.065</v>
       </c>
       <c r="B283" t="n">
-        <v>225.921142578125</v>
+        <v>225.9567108154297</v>
       </c>
       <c r="C283" t="n">
-        <v>237.0601959228516</v>
+        <v>237.0548706054688</v>
       </c>
       <c r="D283" t="n">
-        <v>226.5439307104234</v>
+        <v>226.5527360654101</v>
       </c>
       <c r="E283" t="n">
-        <v>246.1058576107025</v>
+        <v>246.1169928993879</v>
       </c>
       <c r="F283" t="n">
-        <v>227.4665748052554</v>
+        <v>226.9476128880331</v>
       </c>
       <c r="G283" t="n">
-        <v>227.648681640625</v>
+        <v>227.6424407958984</v>
       </c>
       <c r="H283" t="n">
-        <v>217.3305322625486</v>
+        <v>217.0593248032279</v>
       </c>
       <c r="I283" t="n">
-        <v>227.1200875222702</v>
+        <v>226.5331546584636</v>
       </c>
       <c r="J283" t="n">
-        <v>227.0156402587891</v>
+        <v>227.0544128417969</v>
       </c>
       <c r="K283" t="n">
-        <v>233.7501068115234</v>
+        <v>233.7612152099609</v>
       </c>
       <c r="L283" t="n">
-        <v>222.6593150385674</v>
+        <v>221.7938906465006</v>
       </c>
       <c r="M283" t="n">
-        <v>222.6593150385674</v>
+        <v>221.7938906465006</v>
       </c>
     </row>
     <row r="284">
@@ -12062,40 +12062,40 @@
         <v>209.345</v>
       </c>
       <c r="B284" t="n">
-        <v>227.3645935058594</v>
+        <v>227.3999176025391</v>
       </c>
       <c r="C284" t="n">
-        <v>242.0722351074219</v>
+        <v>241.9859924316406</v>
       </c>
       <c r="D284" t="n">
-        <v>230.0370033456742</v>
+        <v>230.047734030574</v>
       </c>
       <c r="E284" t="n">
         <v>250</v>
       </c>
       <c r="F284" t="n">
-        <v>225.51473185895</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G284" t="n">
-        <v>228.7969055175781</v>
+        <v>228.7870635986328</v>
       </c>
       <c r="H284" t="n">
-        <v>221.2967957685444</v>
+        <v>222.7516374038327</v>
       </c>
       <c r="I284" t="n">
-        <v>224.7238281255963</v>
+        <v>224.2906081517048</v>
       </c>
       <c r="J284" t="n">
-        <v>229.6980438232422</v>
+        <v>229.7376861572266</v>
       </c>
       <c r="K284" t="n">
-        <v>236.6418762207031</v>
+        <v>236.5631713867188</v>
       </c>
       <c r="L284" t="n">
-        <v>224.1348145665077</v>
+        <v>224.7094815667138</v>
       </c>
       <c r="M284" t="n">
-        <v>224.1348145665077</v>
+        <v>224.7094815667138</v>
       </c>
     </row>
     <row r="285">
@@ -12103,40 +12103,40 @@
         <v>227.035</v>
       </c>
       <c r="B285" t="n">
-        <v>227.2550659179688</v>
+        <v>227.2126770019531</v>
       </c>
       <c r="C285" t="n">
-        <v>240.3787841796875</v>
+        <v>240.3842620849609</v>
       </c>
       <c r="D285" t="n">
-        <v>228.7940683139581</v>
+        <v>228.7877941619339</v>
       </c>
       <c r="E285" t="n">
         <v>250</v>
       </c>
       <c r="F285" t="n">
-        <v>225.3595763226451</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G285" t="n">
-        <v>226.7145080566406</v>
+        <v>226.7047424316406</v>
       </c>
       <c r="H285" t="n">
-        <v>221.0679654241715</v>
+        <v>222.3340995789887</v>
       </c>
       <c r="I285" t="n">
-        <v>215.9793133964849</v>
+        <v>217.325066992429</v>
       </c>
       <c r="J285" t="n">
-        <v>228.2962951660156</v>
+        <v>228.3039398193359</v>
       </c>
       <c r="K285" t="n">
-        <v>236.9799957275391</v>
+        <v>236.9454650878906</v>
       </c>
       <c r="L285" t="n">
-        <v>224.123468491914</v>
+        <v>223.0939387512289</v>
       </c>
       <c r="M285" t="n">
-        <v>224.123468491914</v>
+        <v>223.0939387512289</v>
       </c>
     </row>
     <row r="286">
@@ -12144,40 +12144,40 @@
         <v>227.135</v>
       </c>
       <c r="B286" t="n">
-        <v>227.1821746826172</v>
+        <v>227.1908111572266</v>
       </c>
       <c r="C286" t="n">
-        <v>239.7593383789062</v>
+        <v>239.7270202636719</v>
       </c>
       <c r="D286" t="n">
-        <v>228.3370546011604</v>
+        <v>228.3379701426575</v>
       </c>
       <c r="E286" t="n">
-        <v>249.9798181056976</v>
+        <v>249.9818063367441</v>
       </c>
       <c r="F286" t="n">
-        <v>225.3595763226451</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G286" t="n">
-        <v>225.9299163818359</v>
+        <v>225.9295043945312</v>
       </c>
       <c r="H286" t="n">
-        <v>220.6346917726755</v>
+        <v>222.066399225431</v>
       </c>
       <c r="I286" t="n">
-        <v>222.2950100121263</v>
+        <v>223.0104783922336</v>
       </c>
       <c r="J286" t="n">
-        <v>228.0829010009766</v>
+        <v>228.1812591552734</v>
       </c>
       <c r="K286" t="n">
-        <v>236.8149261474609</v>
+        <v>236.8729705810547</v>
       </c>
       <c r="L286" t="n">
-        <v>225.8775729988054</v>
+        <v>225.1033940829257</v>
       </c>
       <c r="M286" t="n">
-        <v>225.8775729988054</v>
+        <v>225.1033940829257</v>
       </c>
     </row>
     <row r="287">
@@ -12185,40 +12185,40 @@
         <v>225.965</v>
       </c>
       <c r="B287" t="n">
-        <v>227.1485290527344</v>
+        <v>227.1470489501953</v>
       </c>
       <c r="C287" t="n">
-        <v>235.990478515625</v>
+        <v>235.9924926757812</v>
       </c>
       <c r="D287" t="n">
-        <v>225.5709756070873</v>
+        <v>225.5826083696386</v>
       </c>
       <c r="E287" t="n">
-        <v>246.6893985271454</v>
+        <v>246.704808126696</v>
       </c>
       <c r="F287" t="n">
-        <v>224.0294817582733</v>
+        <v>223.4472994914166</v>
       </c>
       <c r="G287" t="n">
-        <v>221.5933837890625</v>
+        <v>221.5461730957031</v>
       </c>
       <c r="H287" t="n">
-        <v>220.3452459630463</v>
+        <v>221.3147102425118</v>
       </c>
       <c r="I287" t="n">
-        <v>221.8425457294459</v>
+        <v>222.5133383391772</v>
       </c>
       <c r="J287" t="n">
-        <v>227.5479125976562</v>
+        <v>227.5785369873047</v>
       </c>
       <c r="K287" t="n">
-        <v>235.4154052734375</v>
+        <v>235.3735198974609</v>
       </c>
       <c r="L287" t="n">
-        <v>225.3435254545824</v>
+        <v>224.827428666702</v>
       </c>
       <c r="M287" t="n">
-        <v>225.3435254545824</v>
+        <v>224.827428666702</v>
       </c>
     </row>
     <row r="288">
@@ -12226,40 +12226,40 @@
         <v>224.57</v>
       </c>
       <c r="B288" t="n">
-        <v>227.3920593261719</v>
+        <v>227.3769683837891</v>
       </c>
       <c r="C288" t="n">
-        <v>242.7498779296875</v>
+        <v>242.7256469726562</v>
       </c>
       <c r="D288" t="n">
-        <v>230.5092575626363</v>
+        <v>230.5031719044498</v>
       </c>
       <c r="E288" t="n">
         <v>250</v>
       </c>
       <c r="F288" t="n">
-        <v>225.51473185895</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G288" t="n">
-        <v>229.5944366455078</v>
+        <v>229.5193786621094</v>
       </c>
       <c r="H288" t="n">
-        <v>221.4013591903733</v>
+        <v>222.9346673971066</v>
       </c>
       <c r="I288" t="n">
-        <v>221.7881053697053</v>
+        <v>222.4694468203442</v>
       </c>
       <c r="J288" t="n">
-        <v>228.4007110595703</v>
+        <v>228.4087066650391</v>
       </c>
       <c r="K288" t="n">
-        <v>235.9597015380859</v>
+        <v>235.9480285644531</v>
       </c>
       <c r="L288" t="n">
-        <v>226.2032483391304</v>
+        <v>225.1428643589946</v>
       </c>
       <c r="M288" t="n">
-        <v>226.2032483391304</v>
+        <v>225.1428643589946</v>
       </c>
     </row>
     <row r="289">
@@ -12267,40 +12267,40 @@
         <v>226.085</v>
       </c>
       <c r="B289" t="n">
-        <v>227.2507934570312</v>
+        <v>227.3065643310547</v>
       </c>
       <c r="C289" t="n">
-        <v>241.7616729736328</v>
+        <v>241.7544555664062</v>
       </c>
       <c r="D289" t="n">
-        <v>229.7982829975141</v>
+        <v>229.8005853151024</v>
       </c>
       <c r="E289" t="n">
         <v>250</v>
       </c>
       <c r="F289" t="n">
-        <v>225.5346082442766</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G289" t="n">
-        <v>228.4472045898438</v>
+        <v>228.4003448486328</v>
       </c>
       <c r="H289" t="n">
-        <v>221.1068154342278</v>
+        <v>222.6368507286699</v>
       </c>
       <c r="I289" t="n">
-        <v>222.2950100121263</v>
+        <v>223.1255910953192</v>
       </c>
       <c r="J289" t="n">
-        <v>228.6339721679688</v>
+        <v>228.7454986572266</v>
       </c>
       <c r="K289" t="n">
-        <v>238.4007263183594</v>
+        <v>238.3531341552734</v>
       </c>
       <c r="L289" t="n">
-        <v>225.8954047709845</v>
+        <v>225.1818743460835</v>
       </c>
       <c r="M289" t="n">
-        <v>225.8954047709845</v>
+        <v>225.1818743460835</v>
       </c>
     </row>
     <row r="290">
@@ -12308,40 +12308,40 @@
         <v>226.385</v>
       </c>
       <c r="B290" t="n">
-        <v>227.2590179443359</v>
+        <v>227.2684020996094</v>
       </c>
       <c r="C290" t="n">
-        <v>240.1087188720703</v>
+        <v>240.1515655517578</v>
       </c>
       <c r="D290" t="n">
-        <v>228.591806867691</v>
+        <v>228.6078692354267</v>
       </c>
       <c r="E290" t="n">
         <v>250</v>
       </c>
       <c r="F290" t="n">
-        <v>225.3595763226451</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G290" t="n">
-        <v>226.4232330322266</v>
+        <v>226.4081268310547</v>
       </c>
       <c r="H290" t="n">
-        <v>221.1995095139312</v>
+        <v>222.4242617952772</v>
       </c>
       <c r="I290" t="n">
-        <v>222.2950100121263</v>
+        <v>223.1255910953192</v>
       </c>
       <c r="J290" t="n">
-        <v>228.4002990722656</v>
+        <v>228.4243621826172</v>
       </c>
       <c r="K290" t="n">
-        <v>237.5493621826172</v>
+        <v>237.5771789550781</v>
       </c>
       <c r="L290" t="n">
-        <v>225.974410269631</v>
+        <v>225.1135232980088</v>
       </c>
       <c r="M290" t="n">
-        <v>225.974410269631</v>
+        <v>225.1135232980088</v>
       </c>
     </row>
     <row r="291">
@@ -12349,40 +12349,40 @@
         <v>224.225</v>
       </c>
       <c r="B291" t="n">
-        <v>227.3313140869141</v>
+        <v>227.3921508789062</v>
       </c>
       <c r="C291" t="n">
-        <v>241.1664581298828</v>
+        <v>241.1455078125</v>
       </c>
       <c r="D291" t="n">
-        <v>229.3667106702861</v>
+        <v>229.3919149891472</v>
       </c>
       <c r="E291" t="n">
         <v>250</v>
       </c>
       <c r="F291" t="n">
-        <v>225.5346082442766</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G291" t="n">
-        <v>227.7660369873047</v>
+        <v>227.7088012695312</v>
       </c>
       <c r="H291" t="n">
-        <v>221.5303838339328</v>
+        <v>222.3099822373481</v>
       </c>
       <c r="I291" t="n">
-        <v>222.2950100121263</v>
+        <v>223.1255910953192</v>
       </c>
       <c r="J291" t="n">
-        <v>228.3796081542969</v>
+        <v>228.3776397705078</v>
       </c>
       <c r="K291" t="n">
-        <v>237.1755218505859</v>
+        <v>237.2019195556641</v>
       </c>
       <c r="L291" t="n">
-        <v>225.9922420418102</v>
+        <v>225.1135232980088</v>
       </c>
       <c r="M291" t="n">
-        <v>225.9922420418102</v>
+        <v>225.1135232980088</v>
       </c>
     </row>
     <row r="292">
@@ -12390,40 +12390,40 @@
         <v>224.51</v>
       </c>
       <c r="B292" t="n">
-        <v>227.1500854492188</v>
+        <v>227.1853637695312</v>
       </c>
       <c r="C292" t="n">
-        <v>238.9461059570312</v>
+        <v>238.9189910888672</v>
       </c>
       <c r="D292" t="n">
-        <v>227.6777033186826</v>
+        <v>227.6991781523276</v>
       </c>
       <c r="E292" t="n">
-        <v>249.1997449398041</v>
+        <v>249.2275466605927</v>
       </c>
       <c r="F292" t="n">
-        <v>224.7447985618458</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G292" t="n">
-        <v>224.9898529052734</v>
+        <v>225.0101470947266</v>
       </c>
       <c r="H292" t="n">
-        <v>220.15349539678</v>
+        <v>221.6382205983726</v>
       </c>
       <c r="I292" t="n">
-        <v>222.2950100121263</v>
+        <v>223.0104783922336</v>
       </c>
       <c r="J292" t="n">
-        <v>228.1433868408203</v>
+        <v>228.1372680664062</v>
       </c>
       <c r="K292" t="n">
-        <v>236.8496551513672</v>
+        <v>236.9181671142578</v>
       </c>
       <c r="L292" t="n">
-        <v>225.832404186513</v>
+        <v>224.8666405671919</v>
       </c>
       <c r="M292" t="n">
-        <v>225.832404186513</v>
+        <v>224.8666405671919</v>
       </c>
     </row>
     <row r="293">
@@ -12431,40 +12431,40 @@
         <v>223.58</v>
       </c>
       <c r="B293" t="n">
-        <v>227.1695861816406</v>
+        <v>227.2061920166016</v>
       </c>
       <c r="C293" t="n">
-        <v>238.5087585449219</v>
+        <v>238.4734954833984</v>
       </c>
       <c r="D293" t="n">
-        <v>227.4430467220471</v>
+        <v>227.4609940281592</v>
       </c>
       <c r="E293" t="n">
-        <v>248.9282071590424</v>
+        <v>248.9515807292094</v>
       </c>
       <c r="F293" t="n">
-        <v>224.7447985618458</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G293" t="n">
-        <v>224.5134735107422</v>
+        <v>224.493896484375</v>
       </c>
       <c r="H293" t="n">
-        <v>220.6882043622246</v>
+        <v>221.8751368992317</v>
       </c>
       <c r="I293" t="n">
-        <v>222.2950100121263</v>
+        <v>223.0104783922336</v>
       </c>
       <c r="J293" t="n">
-        <v>227.8871765136719</v>
+        <v>227.9044647216797</v>
       </c>
       <c r="K293" t="n">
-        <v>235.8501586914062</v>
+        <v>235.8171234130859</v>
       </c>
       <c r="L293" t="n">
-        <v>225.832404186513</v>
+        <v>224.7982895191171</v>
       </c>
       <c r="M293" t="n">
-        <v>225.832404186513</v>
+        <v>224.7982895191171</v>
       </c>
     </row>
     <row r="294">
@@ -12472,40 +12472,40 @@
         <v>223.98</v>
       </c>
       <c r="B294" t="n">
-        <v>218.2698516845703</v>
+        <v>218.3144226074219</v>
       </c>
       <c r="C294" t="n">
-        <v>238.8325805664062</v>
+        <v>238.8223876953125</v>
       </c>
       <c r="D294" t="n">
-        <v>221.6518015412992</v>
+        <v>221.6551136473034</v>
       </c>
       <c r="E294" t="n">
-        <v>235.5604611635208</v>
+        <v>235.5689820618122</v>
       </c>
       <c r="F294" t="n">
-        <v>235.8854021549742</v>
+        <v>236.0075668822406</v>
       </c>
       <c r="G294" t="n">
-        <v>237.9728698730469</v>
+        <v>237.9856719970703</v>
       </c>
       <c r="H294" t="n">
-        <v>235.8891615580124</v>
+        <v>236.9402041463583</v>
       </c>
       <c r="I294" t="n">
-        <v>230.9950299265932</v>
+        <v>229.120004833559</v>
       </c>
       <c r="J294" t="n">
-        <v>219.9455261230469</v>
+        <v>219.9008483886719</v>
       </c>
       <c r="K294" t="n">
-        <v>233.9762420654297</v>
+        <v>234.0846405029297</v>
       </c>
       <c r="L294" t="n">
-        <v>235.3090545097558</v>
+        <v>235.4566529281732</v>
       </c>
       <c r="M294" t="n">
-        <v>235.3090545097558</v>
+        <v>235.4566529281732</v>
       </c>
     </row>
     <row r="295">
@@ -12513,40 +12513,40 @@
         <v>224.355</v>
       </c>
       <c r="B295" t="n">
-        <v>218.28955078125</v>
+        <v>218.3417510986328</v>
       </c>
       <c r="C295" t="n">
-        <v>239.1233978271484</v>
+        <v>239.0926055908203</v>
       </c>
       <c r="D295" t="n">
-        <v>221.8999029795559</v>
+        <v>221.9232829473455</v>
       </c>
       <c r="E295" t="n">
-        <v>235.9418612718582</v>
+        <v>235.9967790129481</v>
       </c>
       <c r="F295" t="n">
-        <v>235.8854021549742</v>
+        <v>236.0075668822406</v>
       </c>
       <c r="G295" t="n">
-        <v>238.3628082275391</v>
+        <v>238.4029235839844</v>
       </c>
       <c r="H295" t="n">
-        <v>235.909509903988</v>
+        <v>237.0013323079812</v>
       </c>
       <c r="I295" t="n">
-        <v>236.9039442224426</v>
+        <v>236.845082479932</v>
       </c>
       <c r="J295" t="n">
-        <v>216.8438262939453</v>
+        <v>216.8668823242188</v>
       </c>
       <c r="K295" t="n">
-        <v>232.4024047851562</v>
+        <v>232.4894104003906</v>
       </c>
       <c r="L295" t="n">
-        <v>234.7118644589393</v>
+        <v>234.4987784956232</v>
       </c>
       <c r="M295" t="n">
-        <v>234.7118644589393</v>
+        <v>234.4987784956232</v>
       </c>
     </row>
     <row r="296">
@@ -12554,40 +12554,40 @@
         <v>226.19</v>
       </c>
       <c r="B296" t="n">
-        <v>218.2412261962891</v>
+        <v>218.2779846191406</v>
       </c>
       <c r="C296" t="n">
-        <v>238.5734100341797</v>
+        <v>238.6083679199219</v>
       </c>
       <c r="D296" t="n">
-        <v>221.4778999248365</v>
+        <v>221.4875535020927</v>
       </c>
       <c r="E296" t="n">
-        <v>235.3003093004227</v>
+        <v>235.3234894479589</v>
       </c>
       <c r="F296" t="n">
-        <v>234.9982425102632</v>
+        <v>236.0075668822406</v>
       </c>
       <c r="G296" t="n">
-        <v>237.7542877197266</v>
+        <v>237.6975402832031</v>
       </c>
       <c r="H296" t="n">
-        <v>235.8891615580124</v>
+        <v>236.8212732029399</v>
       </c>
       <c r="I296" t="n">
-        <v>236.9039442224426</v>
+        <v>236.7622373465458</v>
       </c>
       <c r="J296" t="n">
-        <v>216.6967926025391</v>
+        <v>216.6852264404297</v>
       </c>
       <c r="K296" t="n">
-        <v>232.3367614746094</v>
+        <v>232.3549499511719</v>
       </c>
       <c r="L296" t="n">
-        <v>234.21509894809</v>
+        <v>234.2467608940788</v>
       </c>
       <c r="M296" t="n">
-        <v>234.21509894809</v>
+        <v>234.2467608940788</v>
       </c>
     </row>
     <row r="297">
@@ -12595,40 +12595,40 @@
         <v>225.355</v>
       </c>
       <c r="B297" t="n">
-        <v>227.0412750244141</v>
+        <v>227.1239166259766</v>
       </c>
       <c r="C297" t="n">
-        <v>237.3463897705078</v>
+        <v>237.3424682617188</v>
       </c>
       <c r="D297" t="n">
-        <v>226.5821639936428</v>
+        <v>226.5781652315158</v>
       </c>
       <c r="E297" t="n">
-        <v>247.9056260585785</v>
+        <v>247.9014487967117</v>
       </c>
       <c r="F297" t="n">
-        <v>224.9755017668443</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G297" t="n">
-        <v>223.1098480224609</v>
+        <v>223.1337738037109</v>
       </c>
       <c r="H297" t="n">
-        <v>219.2644258996596</v>
+        <v>221.4342199173299</v>
       </c>
       <c r="I297" t="n">
-        <v>224.9327665670352</v>
+        <v>226.1939264573737</v>
       </c>
       <c r="J297" t="n">
-        <v>224.9758911132812</v>
+        <v>224.9794158935547</v>
       </c>
       <c r="K297" t="n">
-        <v>233.080078125</v>
+        <v>233.1067962646484</v>
       </c>
       <c r="L297" t="n">
-        <v>229.1745421161447</v>
+        <v>228.328925311286</v>
       </c>
       <c r="M297" t="n">
-        <v>229.1745421161447</v>
+        <v>228.328925311286</v>
       </c>
     </row>
     <row r="298">
@@ -12636,40 +12636,40 @@
         <v>220.98</v>
       </c>
       <c r="B298" t="n">
-        <v>227.1407318115234</v>
+        <v>227.1369171142578</v>
       </c>
       <c r="C298" t="n">
-        <v>236.7667541503906</v>
+        <v>236.7006072998047</v>
       </c>
       <c r="D298" t="n">
-        <v>226.1388646569447</v>
+        <v>226.1317018911145</v>
       </c>
       <c r="E298" t="n">
-        <v>247.3743226528168</v>
+        <v>247.3661721308665</v>
       </c>
       <c r="F298" t="n">
-        <v>224.9755017668443</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G298" t="n">
-        <v>222.5183715820312</v>
+        <v>222.4660034179688</v>
       </c>
       <c r="H298" t="n">
-        <v>218.9320466197397</v>
+        <v>221.1252715464726</v>
       </c>
       <c r="I298" t="n">
-        <v>215.4414364925967</v>
+        <v>213.8877106063579</v>
       </c>
       <c r="J298" t="n">
-        <v>227.3611450195312</v>
+        <v>227.3812561035156</v>
       </c>
       <c r="K298" t="n">
-        <v>233.5788116455078</v>
+        <v>233.5457611083984</v>
       </c>
       <c r="L298" t="n">
-        <v>223.6812163030051</v>
+        <v>220.7215517937811</v>
       </c>
       <c r="M298" t="n">
-        <v>223.6812163030051</v>
+        <v>220.7215517937811</v>
       </c>
     </row>
     <row r="299">
@@ -12677,40 +12677,40 @@
         <v>226.065</v>
       </c>
       <c r="B299" t="n">
-        <v>227.1718597412109</v>
+        <v>227.2105102539062</v>
       </c>
       <c r="C299" t="n">
-        <v>238.5493316650391</v>
+        <v>238.5218200683594</v>
       </c>
       <c r="D299" t="n">
-        <v>227.4922728711914</v>
+        <v>227.4942924480232</v>
       </c>
       <c r="E299" t="n">
-        <v>248.9868953227997</v>
+        <v>248.9902624856034</v>
       </c>
       <c r="F299" t="n">
-        <v>224.7447985618458</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G299" t="n">
-        <v>224.6070861816406</v>
+        <v>224.5862731933594</v>
       </c>
       <c r="H299" t="n">
-        <v>220.6882043622246</v>
+        <v>221.8751368992317</v>
       </c>
       <c r="I299" t="n">
-        <v>222.2021098310933</v>
+        <v>222.8919731419502</v>
       </c>
       <c r="J299" t="n">
-        <v>227.7408447265625</v>
+        <v>227.7809295654297</v>
       </c>
       <c r="K299" t="n">
-        <v>234.9071960449219</v>
+        <v>234.8426208496094</v>
       </c>
       <c r="L299" t="n">
-        <v>225.8515092941261</v>
+        <v>225.1612945981024</v>
       </c>
       <c r="M299" t="n">
-        <v>225.8515092941261</v>
+        <v>225.1612945981024</v>
       </c>
     </row>
     <row r="300">
@@ -12718,40 +12718,40 @@
         <v>225.565</v>
       </c>
       <c r="B300" t="n">
-        <v>227.2091674804688</v>
+        <v>227.2399444580078</v>
       </c>
       <c r="C300" t="n">
-        <v>239.4371185302734</v>
+        <v>239.4159698486328</v>
       </c>
       <c r="D300" t="n">
-        <v>228.0621264506545</v>
+        <v>228.0597029584563</v>
       </c>
       <c r="E300" t="n">
-        <v>249.6538560390472</v>
+        <v>249.6516522278564</v>
       </c>
       <c r="F300" t="n">
-        <v>225.3595763226451</v>
+        <v>224.4794496597791</v>
       </c>
       <c r="G300" t="n">
-        <v>225.6149749755859</v>
+        <v>225.5016479492188</v>
       </c>
       <c r="H300" t="n">
-        <v>220.4859054262785</v>
+        <v>222.066399225431</v>
       </c>
       <c r="I300" t="n">
-        <v>222.2950100121263</v>
+        <v>223.0104783922336</v>
       </c>
       <c r="J300" t="n">
-        <v>227.9480438232422</v>
+        <v>228.0558013916016</v>
       </c>
       <c r="K300" t="n">
-        <v>236.0944671630859</v>
+        <v>236.1367645263672</v>
       </c>
       <c r="L300" t="n">
-        <v>226.1520821388632</v>
+        <v>225.0963347381351</v>
       </c>
       <c r="M300" t="n">
-        <v>226.1520821388632</v>
+        <v>225.0963347381351</v>
       </c>
     </row>
     <row r="301">
@@ -12759,40 +12759,40 @@
         <v>226.165</v>
       </c>
       <c r="B301" t="n">
-        <v>227.0386962890625</v>
+        <v>227.0477752685547</v>
       </c>
       <c r="C301" t="n">
-        <v>234.9338531494141</v>
+        <v>234.9408264160156</v>
       </c>
       <c r="D301" t="n">
-        <v>224.8116418614469</v>
+        <v>224.7951486506537</v>
       </c>
       <c r="E301" t="n">
-        <v>245.7691161632538</v>
+        <v>245.7492848191516</v>
       </c>
       <c r="F301" t="n">
-        <v>223.8881518611603</v>
+        <v>222.5971346491428</v>
       </c>
       <c r="G301" t="n">
-        <v>220.3256378173828</v>
+        <v>220.3002777099609</v>
       </c>
       <c r="H301" t="n">
-        <v>221.2712832029389</v>
+        <v>222.0998190360202</v>
       </c>
       <c r="I301" t="n">
-        <v>221.7419411946207</v>
+        <v>222.4229865333394</v>
       </c>
       <c r="J301" t="n">
-        <v>227.2871856689453</v>
+        <v>227.3402252197266</v>
       </c>
       <c r="K301" t="n">
-        <v>235.120849609375</v>
+        <v>235.0493621826172</v>
       </c>
       <c r="L301" t="n">
-        <v>225.8869654782619</v>
+        <v>225.2182195995026</v>
       </c>
       <c r="M301" t="n">
-        <v>225.8869654782619</v>
+        <v>225.2182195995026</v>
       </c>
     </row>
     <row r="302">
@@ -12800,40 +12800,40 @@
         <v>223.85</v>
       </c>
       <c r="B302" t="n">
-        <v>227.4608001708984</v>
+        <v>227.4234771728516</v>
       </c>
       <c r="C302" t="n">
-        <v>224.53466796875</v>
+        <v>224.4819183349609</v>
       </c>
       <c r="D302" t="n">
-        <v>210.1882860220019</v>
+        <v>210.1874781912692</v>
       </c>
       <c r="E302" t="n">
-        <v>233.3115866184235</v>
+        <v>233.3112253980229</v>
       </c>
       <c r="F302" t="n">
-        <v>221.9997984686722</v>
+        <v>222.9508275470674</v>
       </c>
       <c r="G302" t="n">
-        <v>224.2758636474609</v>
+        <v>224.3371429443359</v>
       </c>
       <c r="H302" t="n">
-        <v>222.0272741673784</v>
+        <v>223.6646589934915</v>
       </c>
       <c r="I302" t="n">
-        <v>221.5981351443886</v>
+        <v>219.9303780338755</v>
       </c>
       <c r="J302" t="n">
-        <v>222.0157470703125</v>
+        <v>222.1386871337891</v>
       </c>
       <c r="K302" t="n">
-        <v>228.0810394287109</v>
+        <v>228.0201416015625</v>
       </c>
       <c r="L302" t="n">
-        <v>224.0714642116654</v>
+        <v>225.1365710243427</v>
       </c>
       <c r="M302" t="n">
-        <v>224.0714642116654</v>
+        <v>225.1365710243427</v>
       </c>
     </row>
     <row r="303">
@@ -12841,40 +12841,40 @@
         <v>234.67</v>
       </c>
       <c r="B303" t="n">
-        <v>227.5012359619141</v>
+        <v>227.4146270751953</v>
       </c>
       <c r="C303" t="n">
-        <v>223.691162109375</v>
+        <v>223.6496429443359</v>
       </c>
       <c r="D303" t="n">
-        <v>209.6136120240037</v>
+        <v>209.6174761476752</v>
       </c>
       <c r="E303" t="n">
-        <v>232.4482119083405</v>
+        <v>232.4548152731641</v>
       </c>
       <c r="F303" t="n">
-        <v>222.2846788426918</v>
+        <v>222.9508275470674</v>
       </c>
       <c r="G303" t="n">
-        <v>223.3580017089844</v>
+        <v>223.3851623535156</v>
       </c>
       <c r="H303" t="n">
-        <v>222.241260500899</v>
+        <v>224.0451547896541</v>
       </c>
       <c r="I303" t="n">
-        <v>218.6820526731982</v>
+        <v>217.3278463206848</v>
       </c>
       <c r="J303" t="n">
-        <v>225.5467681884766</v>
+        <v>225.5637054443359</v>
       </c>
       <c r="K303" t="n">
-        <v>223.588134765625</v>
+        <v>223.498291015625</v>
       </c>
       <c r="L303" t="n">
-        <v>221.5354838143376</v>
+        <v>222.3744352828148</v>
       </c>
       <c r="M303" t="n">
-        <v>221.5354838143376</v>
+        <v>222.3744352828148</v>
       </c>
     </row>
     <row r="304">
@@ -12882,40 +12882,40 @@
         <v>238.04</v>
       </c>
       <c r="B304" t="n">
-        <v>227.4017028808594</v>
+        <v>227.3964996337891</v>
       </c>
       <c r="C304" t="n">
-        <v>225.5810241699219</v>
+        <v>225.5129547119141</v>
       </c>
       <c r="D304" t="n">
-        <v>210.9786041669095</v>
+        <v>210.9973189122177</v>
       </c>
       <c r="E304" t="n">
-        <v>234.3923017978668</v>
+        <v>234.4209390934824</v>
       </c>
       <c r="F304" t="n">
-        <v>223.9802433502756</v>
+        <v>223.3286256198932</v>
       </c>
       <c r="G304" t="n">
-        <v>225.5581665039062</v>
+        <v>225.5681762695312</v>
       </c>
       <c r="H304" t="n">
-        <v>221.9572467824088</v>
+        <v>223.3862132023825</v>
       </c>
       <c r="I304" t="n">
-        <v>224.323748712494</v>
+        <v>224.6349228591343</v>
       </c>
       <c r="J304" t="n">
-        <v>225.9647216796875</v>
+        <v>225.9482879638672</v>
       </c>
       <c r="K304" t="n">
-        <v>224.7871856689453</v>
+        <v>224.6410064697266</v>
       </c>
       <c r="L304" t="n">
-        <v>225.7511160863299</v>
+        <v>226.1105573972424</v>
       </c>
       <c r="M304" t="n">
-        <v>225.7511160863299</v>
+        <v>226.1105573972424</v>
       </c>
     </row>
     <row r="305">
@@ -12923,40 +12923,40 @@
         <v>236.03</v>
       </c>
       <c r="B305" t="n">
-        <v>227.4247741699219</v>
+        <v>227.3246917724609</v>
       </c>
       <c r="C305" t="n">
-        <v>229.1682586669922</v>
+        <v>229.1750183105469</v>
       </c>
       <c r="D305" t="n">
-        <v>213.6651451819974</v>
+        <v>213.6826751088976</v>
       </c>
       <c r="E305" t="n">
-        <v>237.9886724948883</v>
+        <v>238.0156075028239</v>
       </c>
       <c r="F305" t="n">
-        <v>224.1215732473887</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G305" t="n">
-        <v>230.2192230224609</v>
+        <v>230.2180328369141</v>
       </c>
       <c r="H305" t="n">
-        <v>220.8278747405392</v>
+        <v>220.3855252064265</v>
       </c>
       <c r="I305" t="n">
-        <v>227.2585092124515</v>
+        <v>226.5249933598046</v>
       </c>
       <c r="J305" t="n">
-        <v>226.2933654785156</v>
+        <v>226.2805328369141</v>
       </c>
       <c r="K305" t="n">
-        <v>226.6007690429688</v>
+        <v>226.4918060302734</v>
       </c>
       <c r="L305" t="n">
-        <v>225.1357160576339</v>
+        <v>226.6198106982049</v>
       </c>
       <c r="M305" t="n">
-        <v>225.1357160576339</v>
+        <v>226.6198106982049</v>
       </c>
     </row>
     <row r="306">
@@ -12964,40 +12964,40 @@
         <v>226.42</v>
       </c>
       <c r="B306" t="n">
-        <v>227.2642364501953</v>
+        <v>227.2260131835938</v>
       </c>
       <c r="C306" t="n">
-        <v>229.9765930175781</v>
+        <v>229.9856872558594</v>
       </c>
       <c r="D306" t="n">
-        <v>214.2771312248394</v>
+        <v>214.3085019849602</v>
       </c>
       <c r="E306" t="n">
-        <v>238.7913935184479</v>
+        <v>238.8389635757879</v>
       </c>
       <c r="F306" t="n">
-        <v>225.056597233272</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G306" t="n">
-        <v>231.4460296630859</v>
+        <v>231.4111480712891</v>
       </c>
       <c r="H306" t="n">
-        <v>222.0997744250689</v>
+        <v>221.7298275180384</v>
       </c>
       <c r="I306" t="n">
-        <v>229.0687577390897</v>
+        <v>227.4508707900187</v>
       </c>
       <c r="J306" t="n">
-        <v>226.5168151855469</v>
+        <v>226.4528656005859</v>
       </c>
       <c r="K306" t="n">
-        <v>228.3764190673828</v>
+        <v>228.1901550292969</v>
       </c>
       <c r="L306" t="n">
-        <v>224.4269602044709</v>
+        <v>224.9922382760269</v>
       </c>
       <c r="M306" t="n">
-        <v>224.4269602044709</v>
+        <v>224.9922382760269</v>
       </c>
     </row>
     <row r="307">
@@ -13005,40 +13005,40 @@
         <v>225.48</v>
       </c>
       <c r="B307" t="n">
-        <v>227.3019409179688</v>
+        <v>227.2999114990234</v>
       </c>
       <c r="C307" t="n">
-        <v>231.6358184814453</v>
+        <v>231.6051940917969</v>
       </c>
       <c r="D307" t="n">
-        <v>215.4846235635756</v>
+        <v>215.521164440386</v>
       </c>
       <c r="E307" t="n">
-        <v>240.3548376560211</v>
+        <v>240.4101601280321</v>
       </c>
       <c r="F307" t="n">
-        <v>225.1190292511751</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G307" t="n">
-        <v>233.9368743896484</v>
+        <v>233.9100341796875</v>
       </c>
       <c r="H307" t="n">
-        <v>220.5482383473724</v>
+        <v>220.677101762064</v>
       </c>
       <c r="I307" t="n">
-        <v>229.9732675013621</v>
+        <v>228.7452100617514</v>
       </c>
       <c r="J307" t="n">
-        <v>226.4708709716797</v>
+        <v>226.4863433837891</v>
       </c>
       <c r="K307" t="n">
-        <v>228.9833068847656</v>
+        <v>228.9535980224609</v>
       </c>
       <c r="L307" t="n">
-        <v>223.400302866365</v>
+        <v>225.3061662860697</v>
       </c>
       <c r="M307" t="n">
-        <v>223.400302866365</v>
+        <v>225.3061662860697</v>
       </c>
     </row>
     <row r="308">
@@ -13046,40 +13046,40 @@
         <v>224.705</v>
       </c>
       <c r="B308" t="n">
-        <v>227.3213958740234</v>
+        <v>227.2870635986328</v>
       </c>
       <c r="C308" t="n">
-        <v>232.5743865966797</v>
+        <v>232.5833282470703</v>
       </c>
       <c r="D308" t="n">
-        <v>216.1940193370949</v>
+        <v>216.217150223742</v>
       </c>
       <c r="E308" t="n">
-        <v>241.2699072360992</v>
+        <v>241.3052711379072</v>
       </c>
       <c r="F308" t="n">
-        <v>225.0991528658485</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G308" t="n">
-        <v>235.2801055908203</v>
+        <v>235.2864837646484</v>
       </c>
       <c r="H308" t="n">
-        <v>219.0101823235863</v>
+        <v>220.4085935108829</v>
       </c>
       <c r="I308" t="n">
-        <v>230.228035083531</v>
+        <v>229.0500294673346</v>
       </c>
       <c r="J308" t="n">
-        <v>226.5991821289062</v>
+        <v>226.6313323974609</v>
       </c>
       <c r="K308" t="n">
-        <v>230.0392303466797</v>
+        <v>229.9347534179688</v>
       </c>
       <c r="L308" t="n">
-        <v>223.1382119136029</v>
+        <v>224.4543227904188</v>
       </c>
       <c r="M308" t="n">
-        <v>223.1382119136029</v>
+        <v>224.4543227904188</v>
       </c>
     </row>
     <row r="309">
@@ -13087,40 +13087,40 @@
         <v>224.775</v>
       </c>
       <c r="B309" t="n">
-        <v>227.3103942871094</v>
+        <v>227.2895355224609</v>
       </c>
       <c r="C309" t="n">
-        <v>232.573974609375</v>
+        <v>232.5701446533203</v>
       </c>
       <c r="D309" t="n">
-        <v>216.1739734319148</v>
+        <v>216.1951789886489</v>
       </c>
       <c r="E309" t="n">
-        <v>241.2434637546539</v>
+        <v>241.2759454409401</v>
       </c>
       <c r="F309" t="n">
-        <v>225.0991528658485</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G309" t="n">
-        <v>235.2893218994141</v>
+        <v>235.31689453125</v>
       </c>
       <c r="H309" t="n">
-        <v>219.0101823235863</v>
+        <v>220.4085935108829</v>
       </c>
       <c r="I309" t="n">
-        <v>226.375690941352</v>
+        <v>226.2924456792517</v>
       </c>
       <c r="J309" t="n">
-        <v>226.3975830078125</v>
+        <v>226.4795227050781</v>
       </c>
       <c r="K309" t="n">
-        <v>229.9525299072266</v>
+        <v>229.8793640136719</v>
       </c>
       <c r="L309" t="n">
-        <v>217.3971051909016</v>
+        <v>220.5244972025591</v>
       </c>
       <c r="M309" t="n">
-        <v>217.3971051909016</v>
+        <v>220.5244972025591</v>
       </c>
     </row>
     <row r="310">
@@ -13128,40 +13128,40 @@
         <v>224.725</v>
       </c>
       <c r="B310" t="n">
-        <v>227.2973327636719</v>
+        <v>227.2886352539062</v>
       </c>
       <c r="C310" t="n">
-        <v>231.1292419433594</v>
+        <v>231.1341400146484</v>
       </c>
       <c r="D310" t="n">
-        <v>215.167937038543</v>
+        <v>215.2021082785373</v>
       </c>
       <c r="E310" t="n">
-        <v>239.950453042984</v>
+        <v>240.0022250727992</v>
       </c>
       <c r="F310" t="n">
-        <v>225.1190292511751</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G310" t="n">
-        <v>233.2507629394531</v>
+        <v>233.2635345458984</v>
       </c>
       <c r="H310" t="n">
-        <v>220.5336552355174</v>
+        <v>221.1837547020952</v>
       </c>
       <c r="I310" t="n">
-        <v>227.8704956141053</v>
+        <v>227.1880846919711</v>
       </c>
       <c r="J310" t="n">
-        <v>226.4275817871094</v>
+        <v>226.3936920166016</v>
       </c>
       <c r="K310" t="n">
-        <v>229.7187652587891</v>
+        <v>229.6968688964844</v>
       </c>
       <c r="L310" t="n">
-        <v>219.6618691227627</v>
+        <v>223.3195952309014</v>
       </c>
       <c r="M310" t="n">
-        <v>219.6618691227627</v>
+        <v>223.3195952309014</v>
       </c>
     </row>
     <row r="311">
@@ -13169,40 +13169,40 @@
         <v>226.85</v>
       </c>
       <c r="B311" t="n">
-        <v>227.3031921386719</v>
+        <v>227.2900390625</v>
       </c>
       <c r="C311" t="n">
-        <v>230.2249145507812</v>
+        <v>230.2125854492188</v>
       </c>
       <c r="D311" t="n">
-        <v>214.4667021162613</v>
+        <v>214.4903446290391</v>
       </c>
       <c r="E311" t="n">
-        <v>239.0396864414215</v>
+        <v>239.0757442514599</v>
       </c>
       <c r="F311" t="n">
-        <v>225.056597233272</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G311" t="n">
-        <v>231.8834228515625</v>
+        <v>231.8599853515625</v>
       </c>
       <c r="H311" t="n">
-        <v>222.0997744250689</v>
+        <v>221.7298275180384</v>
       </c>
       <c r="I311" t="n">
-        <v>229.122452424395</v>
+        <v>226.295647310669</v>
       </c>
       <c r="J311" t="n">
-        <v>226.3828582763672</v>
+        <v>226.4129028320312</v>
       </c>
       <c r="K311" t="n">
-        <v>228.9729614257812</v>
+        <v>228.9490509033203</v>
       </c>
       <c r="L311" t="n">
-        <v>221.9988690707069</v>
+        <v>223.5634620569452</v>
       </c>
       <c r="M311" t="n">
-        <v>221.9988690707069</v>
+        <v>223.5634620569452</v>
       </c>
     </row>
     <row r="312">
@@ -13210,40 +13210,40 @@
         <v>225.235</v>
       </c>
       <c r="B312" t="n">
-        <v>227.2254028320312</v>
+        <v>227.2594451904297</v>
       </c>
       <c r="C312" t="n">
-        <v>231.2241973876953</v>
+        <v>231.2520904541016</v>
       </c>
       <c r="D312" t="n">
-        <v>215.2079714718468</v>
+        <v>215.2431525002571</v>
       </c>
       <c r="E312" t="n">
-        <v>239.9973738193512</v>
+        <v>240.0506552093133</v>
       </c>
       <c r="F312" t="n">
-        <v>225.1190292511751</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G312" t="n">
-        <v>233.4249420166016</v>
+        <v>233.4584045410156</v>
       </c>
       <c r="H312" t="n">
-        <v>220.5336552355174</v>
+        <v>220.7781115297172</v>
       </c>
       <c r="I312" t="n">
-        <v>230.228035083531</v>
+        <v>229.5176184398624</v>
       </c>
       <c r="J312" t="n">
-        <v>226.5146484375</v>
+        <v>226.5549926757812</v>
       </c>
       <c r="K312" t="n">
-        <v>229.0877532958984</v>
+        <v>228.9937286376953</v>
       </c>
       <c r="L312" t="n">
-        <v>224.0418285311136</v>
+        <v>225.0360852558843</v>
       </c>
       <c r="M312" t="n">
-        <v>224.0418285311136</v>
+        <v>225.0360852558843</v>
       </c>
     </row>
     <row r="313">
@@ -13251,40 +13251,40 @@
         <v>225.505</v>
       </c>
       <c r="B313" t="n">
-        <v>227.314208984375</v>
+        <v>227.2975921630859</v>
       </c>
       <c r="C313" t="n">
-        <v>231.6473693847656</v>
+        <v>231.6226043701172</v>
       </c>
       <c r="D313" t="n">
-        <v>215.4964969145096</v>
+        <v>215.538396401847</v>
       </c>
       <c r="E313" t="n">
-        <v>240.3692610263824</v>
+        <v>240.4325810041913</v>
       </c>
       <c r="F313" t="n">
-        <v>225.1190292511751</v>
+        <v>226.1113641976767</v>
       </c>
       <c r="G313" t="n">
-        <v>233.9915466308594</v>
+        <v>234.0229034423828</v>
       </c>
       <c r="H313" t="n">
-        <v>220.5482383473724</v>
+        <v>220.677101762064</v>
       </c>
       <c r="I313" t="n">
-        <v>229.5672590181459</v>
+        <v>229.1023509701436</v>
       </c>
       <c r="J313" t="n">
-        <v>226.517822265625</v>
+        <v>226.5530853271484</v>
       </c>
       <c r="K313" t="n">
-        <v>229.6893463134766</v>
+        <v>229.5148315429688</v>
       </c>
       <c r="L313" t="n">
-        <v>222.9809958298598</v>
+        <v>224.9971536950684</v>
       </c>
       <c r="M313" t="n">
-        <v>222.9809958298598</v>
+        <v>224.9971536950684</v>
       </c>
     </row>
     <row r="314">
@@ -13292,40 +13292,40 @@
         <v>224.51</v>
       </c>
       <c r="B314" t="n">
-        <v>227.3012237548828</v>
+        <v>227.3164978027344</v>
       </c>
       <c r="C314" t="n">
-        <v>234.9640045166016</v>
+        <v>234.9476013183594</v>
       </c>
       <c r="D314" t="n">
-        <v>217.9784642235708</v>
+        <v>217.9874176808585</v>
       </c>
       <c r="E314" t="n">
-        <v>243.5256826877594</v>
+        <v>243.5399041132163</v>
       </c>
       <c r="F314" t="n">
-        <v>226.5078109184103</v>
+        <v>229.6669387471375</v>
       </c>
       <c r="G314" t="n">
-        <v>238.9509735107422</v>
+        <v>238.9948883056641</v>
       </c>
       <c r="H314" t="n">
-        <v>218.8210786443768</v>
+        <v>222.9821424407627</v>
       </c>
       <c r="I314" t="n">
-        <v>231.2129794150723</v>
+        <v>229.8598040117457</v>
       </c>
       <c r="J314" t="n">
-        <v>226.845947265625</v>
+        <v>226.8038330078125</v>
       </c>
       <c r="K314" t="n">
-        <v>230.7930755615234</v>
+        <v>230.75244140625</v>
       </c>
       <c r="L314" t="n">
-        <v>221.5528431085903</v>
+        <v>223.9529585676226</v>
       </c>
       <c r="M314" t="n">
-        <v>221.5528431085903</v>
+        <v>223.9529585676226</v>
       </c>
     </row>
     <row r="315">
@@ -13333,40 +13333,40 @@
         <v>224.64</v>
       </c>
       <c r="B315" t="n">
-        <v>225.9428100585938</v>
+        <v>225.9393768310547</v>
       </c>
       <c r="C315" t="n">
-        <v>233.0835113525391</v>
+        <v>233.0396728515625</v>
       </c>
       <c r="D315" t="n">
-        <v>218.6337162942287</v>
+        <v>218.6643061513079</v>
       </c>
       <c r="E315" t="n">
-        <v>243.5770456790924</v>
+        <v>243.6244894841888</v>
       </c>
       <c r="F315" t="n">
-        <v>225.1341509642849</v>
+        <v>227.3582061554509</v>
       </c>
       <c r="G315" t="n">
-        <v>239.3648681640625</v>
+        <v>239.3966827392578</v>
       </c>
       <c r="H315" t="n">
-        <v>211.9257687090033</v>
+        <v>217.477916211093</v>
       </c>
       <c r="I315" t="n">
-        <v>226.8964393745713</v>
+        <v>226.2015230480635</v>
       </c>
       <c r="J315" t="n">
-        <v>227.5234680175781</v>
+        <v>227.5419769287109</v>
       </c>
       <c r="K315" t="n">
-        <v>229.7374267578125</v>
+        <v>229.6063842773438</v>
       </c>
       <c r="L315" t="n">
-        <v>215.4369313446033</v>
+        <v>220.3130477242296</v>
       </c>
       <c r="M315" t="n">
-        <v>215.4369313446033</v>
+        <v>220.3130477242296</v>
       </c>
     </row>
   </sheetData>
